--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="F14" t="n">
-        <v>7.79</v>
+        <v>7.83</v>
       </c>
       <c r="G14" t="n">
-        <v>308.9</v>
+        <v>307.2</v>
       </c>
       <c r="H14" t="n">
-        <v>46.1</v>
+        <v>52.1</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>38.28</v>
+        <v>87.94</v>
       </c>
       <c r="K14" t="n">
-        <v>78.97</v>
+        <v>-145.47</v>
       </c>
       <c r="L14" t="n">
-        <v>87.76000000000001</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:05</t>
+          <t>04:32:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="F15" t="n">
-        <v>7.86</v>
+        <v>7.22</v>
       </c>
       <c r="G15" t="n">
-        <v>295.6</v>
+        <v>285.6</v>
       </c>
       <c r="H15" t="n">
-        <v>51.4</v>
+        <v>57.7</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-28.47</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>9.1</v>
+        <v>-18.27</v>
       </c>
       <c r="L15" t="n">
-        <v>29.89</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:08</t>
+          <t>04:34:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="F16" t="n">
-        <v>7.73</v>
+        <v>7.98</v>
       </c>
       <c r="G16" t="n">
-        <v>305.8</v>
+        <v>292.5</v>
       </c>
       <c r="H16" t="n">
-        <v>57.6</v>
+        <v>48.5</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-89.67</v>
+        <v>-123.04</v>
       </c>
       <c r="K16" t="n">
-        <v>134.27</v>
+        <v>-19.83</v>
       </c>
       <c r="L16" t="n">
-        <v>161.46</v>
+        <v>124.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:02</t>
+          <t>04:40:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="F17" t="n">
-        <v>8.289999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="G17" t="n">
-        <v>298.3</v>
+        <v>308.2</v>
       </c>
       <c r="H17" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-221.58</v>
+        <v>-173.56</v>
       </c>
       <c r="K17" t="n">
-        <v>52.87</v>
+        <v>-74.73</v>
       </c>
       <c r="L17" t="n">
-        <v>227.8</v>
+        <v>188.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:07</t>
+          <t>04:40:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="F18" t="n">
-        <v>8.31</v>
+        <v>8.74</v>
       </c>
       <c r="G18" t="n">
-        <v>296.6</v>
+        <v>302.6</v>
       </c>
       <c r="H18" t="n">
         <v>54.2</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>60.59</v>
+        <v>-189.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-50.17</v>
+        <v>-118.81</v>
       </c>
       <c r="L18" t="n">
-        <v>78.67</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:04</t>
+          <t>04:42:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="n">
-        <v>7.33</v>
+        <v>8.1</v>
       </c>
       <c r="G19" t="n">
-        <v>285.9</v>
+        <v>310.5</v>
       </c>
       <c r="H19" t="n">
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-238.68</v>
+        <v>-40.67</v>
       </c>
       <c r="K19" t="n">
-        <v>166.03</v>
+        <v>-173.71</v>
       </c>
       <c r="L19" t="n">
-        <v>290.75</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:48:14</t>
+          <t>04:47:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="F20" t="n">
-        <v>7.56</v>
+        <v>7.86</v>
       </c>
       <c r="G20" t="n">
-        <v>300</v>
+        <v>302.4</v>
       </c>
       <c r="H20" t="n">
-        <v>56.1</v>
+        <v>48.8</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-74.69</v>
+        <v>-241.62</v>
       </c>
       <c r="K20" t="n">
-        <v>231.42</v>
+        <v>4.97</v>
       </c>
       <c r="L20" t="n">
-        <v>243.17</v>
+        <v>241.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:30</t>
+          <t>04:48:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="F21" t="n">
-        <v>8.34</v>
+        <v>8.06</v>
       </c>
       <c r="G21" t="n">
-        <v>298.8</v>
+        <v>291.7</v>
       </c>
       <c r="H21" t="n">
-        <v>49.8</v>
+        <v>46.8</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>555.41</v>
+        <v>84.92</v>
       </c>
       <c r="K21" t="n">
-        <v>75.90000000000001</v>
+        <v>-146.4</v>
       </c>
       <c r="L21" t="n">
-        <v>560.5700000000001</v>
+        <v>169.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:52:00</t>
+          <t>04:51:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="F22" t="n">
-        <v>7.8</v>
+        <v>8.18</v>
       </c>
       <c r="G22" t="n">
-        <v>283.8</v>
+        <v>291</v>
       </c>
       <c r="H22" t="n">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-377.25</v>
+        <v>-142.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-61.55</v>
+        <v>23.49</v>
       </c>
       <c r="L22" t="n">
-        <v>382.24</v>
+        <v>144.32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:57:55</t>
+          <t>04:56:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="F23" t="n">
-        <v>7.9</v>
+        <v>7.45</v>
       </c>
       <c r="G23" t="n">
-        <v>291.9</v>
+        <v>284.2</v>
       </c>
       <c r="H23" t="n">
-        <v>51.5</v>
+        <v>53.2</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>63.88</v>
+        <v>413.66</v>
       </c>
       <c r="K23" t="n">
-        <v>-45.32</v>
+        <v>397.45</v>
       </c>
       <c r="L23" t="n">
-        <v>78.31999999999999</v>
+        <v>573.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:00:25</t>
+          <t>04:58:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.13</v>
+        <v>2.61</v>
       </c>
       <c r="F24" t="n">
-        <v>7.73</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>296</v>
+        <v>296.4</v>
       </c>
       <c r="H24" t="n">
-        <v>50.7</v>
+        <v>45.6</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-173.69</v>
+        <v>-152.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-185.03</v>
+        <v>-401.47</v>
       </c>
       <c r="L24" t="n">
-        <v>253.78</v>
+        <v>429.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:01:43</t>
+          <t>05:00:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.27</v>
+        <v>3.36</v>
       </c>
       <c r="F25" t="n">
-        <v>8.52</v>
+        <v>7.98</v>
       </c>
       <c r="G25" t="n">
-        <v>299.8</v>
+        <v>297.1</v>
       </c>
       <c r="H25" t="n">
-        <v>55.3</v>
+        <v>46.7</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-19.4</v>
+        <v>205.62</v>
       </c>
       <c r="K25" t="n">
-        <v>42.01</v>
+        <v>41.74</v>
       </c>
       <c r="L25" t="n">
-        <v>46.27</v>
+        <v>209.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:06:07</t>
+          <t>05:03:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.53</v>
+        <v>2.79</v>
       </c>
       <c r="F26" t="n">
-        <v>8.140000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="G26" t="n">
-        <v>293</v>
+        <v>293.7</v>
       </c>
       <c r="H26" t="n">
-        <v>51.8</v>
+        <v>64</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-59.73</v>
+        <v>-115.3</v>
       </c>
       <c r="K26" t="n">
-        <v>212.33</v>
+        <v>-569.92</v>
       </c>
       <c r="L26" t="n">
-        <v>220.57</v>
+        <v>581.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:07:20</t>
+          <t>05:05:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>7.66</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>299.4</v>
+        <v>295.1</v>
       </c>
       <c r="H27" t="n">
-        <v>63.2</v>
+        <v>46.4</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-251.85</v>
+        <v>-417.75</v>
       </c>
       <c r="K27" t="n">
-        <v>110.67</v>
+        <v>-33.6</v>
       </c>
       <c r="L27" t="n">
-        <v>275.09</v>
+        <v>419.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:09:12</t>
+          <t>05:07:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="F28" t="n">
-        <v>7.99</v>
+        <v>7.7</v>
       </c>
       <c r="G28" t="n">
-        <v>299.5</v>
+        <v>304.8</v>
       </c>
       <c r="H28" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>27.75</v>
+        <v>103.61</v>
       </c>
       <c r="K28" t="n">
-        <v>-280.97</v>
+        <v>-304.72</v>
       </c>
       <c r="L28" t="n">
-        <v>282.34</v>
+        <v>321.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:19:32</t>
+          <t>05:17:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="F29" t="n">
-        <v>8.51</v>
+        <v>7.66</v>
       </c>
       <c r="G29" t="n">
-        <v>305.5</v>
+        <v>287.5</v>
       </c>
       <c r="H29" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.48</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>26.16</v>
+        <v>110.8</v>
       </c>
       <c r="L29" t="n">
-        <v>35.16</v>
+        <v>147.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:20:43</t>
+          <t>05:19:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="F30" t="n">
-        <v>7.45</v>
+        <v>8.07</v>
       </c>
       <c r="G30" t="n">
-        <v>297</v>
+        <v>283.4</v>
       </c>
       <c r="H30" t="n">
-        <v>50.6</v>
+        <v>47.2</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>23.07</v>
+        <v>-17.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-13.22</v>
+        <v>24.46</v>
       </c>
       <c r="L30" t="n">
-        <v>26.59</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:23:35</t>
+          <t>05:20:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="F31" t="n">
-        <v>7.4</v>
+        <v>7.94</v>
       </c>
       <c r="G31" t="n">
-        <v>298.7</v>
+        <v>294.7</v>
       </c>
       <c r="H31" t="n">
-        <v>50.6</v>
+        <v>52.6</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-140.32</v>
+        <v>-18.64</v>
       </c>
       <c r="K31" t="n">
-        <v>90.15000000000001</v>
+        <v>228.67</v>
       </c>
       <c r="L31" t="n">
-        <v>166.78</v>
+        <v>229.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:40</t>
+          <t>05:26:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="F32" t="n">
-        <v>7.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>300.6</v>
+        <v>306.4</v>
       </c>
       <c r="H32" t="n">
-        <v>51.9</v>
+        <v>49</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-11.81</v>
+        <v>20.93</v>
       </c>
       <c r="K32" t="n">
-        <v>33.32</v>
+        <v>116.76</v>
       </c>
       <c r="L32" t="n">
-        <v>35.35</v>
+        <v>118.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:49</t>
+          <t>05:28:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="F33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="G33" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="H33" t="n">
-        <v>52.7</v>
+        <v>55.4</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-35.91</v>
+        <v>-197.54</v>
       </c>
       <c r="K33" t="n">
-        <v>312.86</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>314.91</v>
+        <v>218.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:32:27</t>
+          <t>05:29:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="F34" t="n">
-        <v>8.09</v>
+        <v>7.76</v>
       </c>
       <c r="G34" t="n">
-        <v>304.2</v>
+        <v>298.5</v>
       </c>
       <c r="H34" t="n">
-        <v>55.4</v>
+        <v>50.9</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-36.75</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>157.43</v>
+        <v>-50.33</v>
       </c>
       <c r="L34" t="n">
-        <v>161.67</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:37:04</t>
+          <t>05:33:09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="F35" t="n">
-        <v>8.050000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="G35" t="n">
-        <v>300.7</v>
+        <v>294.4</v>
       </c>
       <c r="H35" t="n">
-        <v>54.1</v>
+        <v>51</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>73.68000000000001</v>
+        <v>-96.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>147.61</v>
+        <v>-13.53</v>
       </c>
       <c r="L35" t="n">
-        <v>164.98</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:38:19</t>
+          <t>05:35:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="F36" t="n">
-        <v>8.56</v>
+        <v>8.25</v>
       </c>
       <c r="G36" t="n">
-        <v>319.1</v>
+        <v>294.3</v>
       </c>
       <c r="H36" t="n">
-        <v>52.2</v>
+        <v>47.1</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>16.36</v>
+        <v>-52.26</v>
       </c>
       <c r="K36" t="n">
-        <v>170.02</v>
+        <v>7.29</v>
       </c>
       <c r="L36" t="n">
-        <v>170.81</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:33</t>
+          <t>05:36:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="F37" t="n">
-        <v>8.380000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>289</v>
+        <v>292.1</v>
       </c>
       <c r="H37" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-317.41</v>
+        <v>-108.91</v>
       </c>
       <c r="K37" t="n">
-        <v>-99.17</v>
+        <v>-5.31</v>
       </c>
       <c r="L37" t="n">
-        <v>332.54</v>
+        <v>109.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:44:20</t>
+          <t>05:41:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="F38" t="n">
-        <v>7.67</v>
+        <v>6.93</v>
       </c>
       <c r="G38" t="n">
-        <v>281</v>
+        <v>293.8</v>
       </c>
       <c r="H38" t="n">
-        <v>49.1</v>
+        <v>55.9</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>437.03</v>
+        <v>-189.91</v>
       </c>
       <c r="K38" t="n">
-        <v>91.48999999999999</v>
+        <v>-45.34</v>
       </c>
       <c r="L38" t="n">
-        <v>446.5</v>
+        <v>195.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:46:47</t>
+          <t>05:44:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="F39" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="G39" t="n">
-        <v>294.9</v>
+        <v>285.1</v>
       </c>
       <c r="H39" t="n">
-        <v>49.2</v>
+        <v>46.9</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-119.86</v>
+        <v>57.28</v>
       </c>
       <c r="K39" t="n">
-        <v>-366.78</v>
+        <v>-131.32</v>
       </c>
       <c r="L39" t="n">
-        <v>385.87</v>
+        <v>143.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:47:45</t>
+          <t>05:46:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="F40" t="n">
-        <v>7.71</v>
+        <v>8.69</v>
       </c>
       <c r="G40" t="n">
-        <v>293.8</v>
+        <v>299.5</v>
       </c>
       <c r="H40" t="n">
-        <v>52.1</v>
+        <v>53.6</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>42.81</v>
+        <v>-214.26</v>
       </c>
       <c r="K40" t="n">
-        <v>252.22</v>
+        <v>-0.61</v>
       </c>
       <c r="L40" t="n">
-        <v>255.82</v>
+        <v>214.27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:39</t>
+          <t>05:51:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="F41" t="n">
-        <v>7.91</v>
+        <v>8.01</v>
       </c>
       <c r="G41" t="n">
-        <v>299.5</v>
+        <v>285.1</v>
       </c>
       <c r="H41" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>474.67</v>
+        <v>-13.18</v>
       </c>
       <c r="K41" t="n">
-        <v>747.71</v>
+        <v>263.5</v>
       </c>
       <c r="L41" t="n">
-        <v>885.65</v>
+        <v>263.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:54:06</t>
+          <t>05:53:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="F42" t="n">
-        <v>8.01</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>294.3</v>
+        <v>299.8</v>
       </c>
       <c r="H42" t="n">
-        <v>53.6</v>
+        <v>48.5</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>235.98</v>
+        <v>231.58</v>
       </c>
       <c r="K42" t="n">
-        <v>101.27</v>
+        <v>-145.25</v>
       </c>
       <c r="L42" t="n">
-        <v>256.79</v>
+        <v>273.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:17</t>
+          <t>05:55:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="F43" t="n">
-        <v>7.93</v>
+        <v>7.91</v>
       </c>
       <c r="G43" t="n">
-        <v>296</v>
+        <v>279.4</v>
       </c>
       <c r="H43" t="n">
-        <v>53.9</v>
+        <v>56.5</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>41.48</v>
+        <v>-478.81</v>
       </c>
       <c r="K43" t="n">
-        <v>-82.84999999999999</v>
+        <v>221.43</v>
       </c>
       <c r="L43" t="n">
-        <v>92.65000000000001</v>
+        <v>527.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:03:22</t>
+          <t>06:06:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="F44" t="n">
-        <v>7.58</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>297</v>
+        <v>306.3</v>
       </c>
       <c r="H44" t="n">
-        <v>49.8</v>
+        <v>59.2</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-184.66</v>
+        <v>-16.88</v>
       </c>
       <c r="K44" t="n">
-        <v>54.12</v>
+        <v>189.07</v>
       </c>
       <c r="L44" t="n">
-        <v>192.43</v>
+        <v>189.82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:04:56</t>
+          <t>06:08:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="F45" t="n">
-        <v>7.88</v>
+        <v>7.33</v>
       </c>
       <c r="G45" t="n">
-        <v>306.6</v>
+        <v>297.8</v>
       </c>
       <c r="H45" t="n">
-        <v>46.2</v>
+        <v>54.1</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-64.81</v>
+        <v>-32.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-89.38</v>
+        <v>60.13</v>
       </c>
       <c r="L45" t="n">
-        <v>110.41</v>
+        <v>68.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:06:52</t>
+          <t>06:09:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="F46" t="n">
-        <v>7.8</v>
+        <v>7.73</v>
       </c>
       <c r="G46" t="n">
-        <v>308.4</v>
+        <v>294.2</v>
       </c>
       <c r="H46" t="n">
-        <v>44.4</v>
+        <v>54.3</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>-157.92</v>
+        <v>110.97</v>
       </c>
       <c r="K46" t="n">
-        <v>20.19</v>
+        <v>-27.15</v>
       </c>
       <c r="L46" t="n">
-        <v>159.21</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:11:34</t>
+          <t>06:13:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.54</v>
+        <v>3.04</v>
       </c>
       <c r="F47" t="n">
-        <v>7.99</v>
+        <v>7.76</v>
       </c>
       <c r="G47" t="n">
-        <v>298.3</v>
+        <v>306.6</v>
       </c>
       <c r="H47" t="n">
-        <v>49.3</v>
+        <v>40.1</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-231.86</v>
+        <v>-87.7</v>
       </c>
       <c r="K47" t="n">
-        <v>5.42</v>
+        <v>-55.63</v>
       </c>
       <c r="L47" t="n">
-        <v>231.92</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:12:51</t>
+          <t>06:13:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="F48" t="n">
-        <v>7.41</v>
+        <v>7.78</v>
       </c>
       <c r="G48" t="n">
-        <v>293.8</v>
+        <v>302.2</v>
       </c>
       <c r="H48" t="n">
-        <v>52.8</v>
+        <v>56.9</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-179.62</v>
+        <v>63.8</v>
       </c>
       <c r="K48" t="n">
-        <v>62.5</v>
+        <v>101.11</v>
       </c>
       <c r="L48" t="n">
-        <v>190.18</v>
+        <v>119.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>06:15:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="F49" t="n">
-        <v>8.1</v>
+        <v>7.45</v>
       </c>
       <c r="G49" t="n">
-        <v>290</v>
+        <v>295.1</v>
       </c>
       <c r="H49" t="n">
-        <v>53</v>
+        <v>54.1</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-107.78</v>
+        <v>-39.99</v>
       </c>
       <c r="K49" t="n">
-        <v>116.99</v>
+        <v>98.92</v>
       </c>
       <c r="L49" t="n">
-        <v>159.07</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:19:05</t>
+          <t>06:19:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="F50" t="n">
-        <v>7.93</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>294.7</v>
+        <v>295.3</v>
       </c>
       <c r="H50" t="n">
-        <v>54</v>
+        <v>49.4</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>423.55</v>
+        <v>-92.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-422.42</v>
+        <v>-256.35</v>
       </c>
       <c r="L50" t="n">
-        <v>598.1900000000001</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:20:17</t>
+          <t>06:21:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="F51" t="n">
-        <v>7.53</v>
+        <v>7.5</v>
       </c>
       <c r="G51" t="n">
-        <v>291.5</v>
+        <v>307.2</v>
       </c>
       <c r="H51" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>19.5</v>
+        <v>211.08</v>
       </c>
       <c r="K51" t="n">
-        <v>-193.13</v>
+        <v>20.79</v>
       </c>
       <c r="L51" t="n">
-        <v>194.12</v>
+        <v>212.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:49</t>
+          <t>06:22:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="F52" t="n">
-        <v>7.48</v>
+        <v>8.23</v>
       </c>
       <c r="G52" t="n">
-        <v>294</v>
+        <v>295.4</v>
       </c>
       <c r="H52" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-144.05</v>
+        <v>167.68</v>
       </c>
       <c r="K52" t="n">
-        <v>-29.91</v>
+        <v>-189.86</v>
       </c>
       <c r="L52" t="n">
-        <v>147.12</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:26:55</t>
+          <t>06:27:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="F53" t="n">
-        <v>7.74</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>292.2</v>
+        <v>304.8</v>
       </c>
       <c r="H53" t="n">
-        <v>48.1</v>
+        <v>51.1</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-137.56</v>
+        <v>192.9</v>
       </c>
       <c r="K53" t="n">
-        <v>-159.01</v>
+        <v>52.84</v>
       </c>
       <c r="L53" t="n">
-        <v>210.25</v>
+        <v>200.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:28:48</t>
+          <t>06:30:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.78</v>
+        <v>2.58</v>
       </c>
       <c r="F54" t="n">
-        <v>8.449999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="G54" t="n">
-        <v>293.4</v>
+        <v>297.5</v>
       </c>
       <c r="H54" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>407.85</v>
+        <v>-122.49</v>
       </c>
       <c r="K54" t="n">
-        <v>-149.69</v>
+        <v>354.85</v>
       </c>
       <c r="L54" t="n">
-        <v>434.45</v>
+        <v>375.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:31:01</t>
+          <t>06:31:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.97</v>
+        <v>2.37</v>
       </c>
       <c r="F55" t="n">
-        <v>8.23</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>291.2</v>
+        <v>294.3</v>
       </c>
       <c r="H55" t="n">
-        <v>54.4</v>
+        <v>47.9</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-194.98</v>
+        <v>-157.87</v>
       </c>
       <c r="K55" t="n">
-        <v>113.51</v>
+        <v>-324.74</v>
       </c>
       <c r="L55" t="n">
-        <v>225.62</v>
+        <v>361.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:35:38</t>
+          <t>06:35:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="F56" t="n">
-        <v>7.91</v>
+        <v>6.99</v>
       </c>
       <c r="G56" t="n">
-        <v>298.4</v>
+        <v>296.4</v>
       </c>
       <c r="H56" t="n">
-        <v>53.9</v>
+        <v>49.3</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-130.49</v>
+        <v>254.88</v>
       </c>
       <c r="K56" t="n">
-        <v>-345.79</v>
+        <v>460.38</v>
       </c>
       <c r="L56" t="n">
-        <v>369.6</v>
+        <v>526.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:36:51</t>
+          <t>06:36:56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="F57" t="n">
-        <v>8.41</v>
+        <v>8.57</v>
       </c>
       <c r="G57" t="n">
-        <v>283.5</v>
+        <v>288.4</v>
       </c>
       <c r="H57" t="n">
-        <v>57.2</v>
+        <v>52.4</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-355.29</v>
+        <v>-61.49</v>
       </c>
       <c r="K57" t="n">
-        <v>498.8</v>
+        <v>437.61</v>
       </c>
       <c r="L57" t="n">
-        <v>612.4</v>
+        <v>441.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:00</t>
+          <t>06:39:03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="F58" t="n">
-        <v>8.59</v>
+        <v>7.66</v>
       </c>
       <c r="G58" t="n">
-        <v>298.7</v>
+        <v>287.2</v>
       </c>
       <c r="H58" t="n">
-        <v>53.1</v>
+        <v>48.8</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-931.83</v>
+        <v>170.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-157.43</v>
+        <v>106.57</v>
       </c>
       <c r="L58" t="n">
-        <v>945.03</v>
+        <v>201.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:48:03</t>
+          <t>06:49:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.23</v>
+        <v>2.52</v>
       </c>
       <c r="F59" t="n">
-        <v>7.95</v>
+        <v>8.68</v>
       </c>
       <c r="G59" t="n">
-        <v>298.1</v>
+        <v>293.7</v>
       </c>
       <c r="H59" t="n">
-        <v>56.6</v>
+        <v>45.5</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>2.81</v>
+        <v>-49.9</v>
       </c>
       <c r="K59" t="n">
-        <v>49.51</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>49.59</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:49:06</t>
+          <t>06:51:39</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="F60" t="n">
-        <v>7.95</v>
+        <v>8.26</v>
       </c>
       <c r="G60" t="n">
-        <v>311</v>
+        <v>304.5</v>
       </c>
       <c r="H60" t="n">
-        <v>50.1</v>
+        <v>52.4</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-49.96</v>
+        <v>49.68</v>
       </c>
       <c r="K60" t="n">
-        <v>16.4</v>
+        <v>-63.35</v>
       </c>
       <c r="L60" t="n">
-        <v>52.58</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:51:04</t>
+          <t>06:53:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="F61" t="n">
-        <v>7.91</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>291.6</v>
+        <v>298.8</v>
       </c>
       <c r="H61" t="n">
-        <v>49.1</v>
+        <v>53.3</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>138.07</v>
+        <v>-109.9</v>
       </c>
       <c r="K61" t="n">
-        <v>-47.68</v>
+        <v>-26.34</v>
       </c>
       <c r="L61" t="n">
-        <v>146.07</v>
+        <v>113.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:55:12</t>
+          <t>06:57:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="F62" t="n">
-        <v>7.57</v>
+        <v>7.96</v>
       </c>
       <c r="G62" t="n">
-        <v>302.7</v>
+        <v>308.7</v>
       </c>
       <c r="H62" t="n">
-        <v>54.4</v>
+        <v>50.3</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>126.38</v>
+        <v>33.67</v>
       </c>
       <c r="K62" t="n">
-        <v>89.77</v>
+        <v>-62.52</v>
       </c>
       <c r="L62" t="n">
-        <v>155.02</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:56:25</t>
+          <t>06:59:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>7.21</v>
       </c>
       <c r="G63" t="n">
-        <v>287.4</v>
+        <v>285</v>
       </c>
       <c r="H63" t="n">
-        <v>54.9</v>
+        <v>51.3</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-106.45</v>
+        <v>-288.99</v>
       </c>
       <c r="K63" t="n">
-        <v>-187.52</v>
+        <v>219.85</v>
       </c>
       <c r="L63" t="n">
-        <v>215.63</v>
+        <v>363.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:58:17</t>
+          <t>07:00:07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="F64" t="n">
-        <v>7.96</v>
+        <v>7.49</v>
       </c>
       <c r="G64" t="n">
-        <v>305.5</v>
+        <v>289.3</v>
       </c>
       <c r="H64" t="n">
-        <v>44.1</v>
+        <v>55.9</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-162.34</v>
+        <v>11.91</v>
       </c>
       <c r="K64" t="n">
-        <v>-45.64</v>
+        <v>101.17</v>
       </c>
       <c r="L64" t="n">
-        <v>168.63</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:03:34</t>
+          <t>07:04:26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="F65" t="n">
-        <v>8.050000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="G65" t="n">
-        <v>299.4</v>
+        <v>292.8</v>
       </c>
       <c r="H65" t="n">
-        <v>52.5</v>
+        <v>55.9</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>41.87</v>
+        <v>-191.78</v>
       </c>
       <c r="K65" t="n">
-        <v>-467.56</v>
+        <v>-131.8</v>
       </c>
       <c r="L65" t="n">
-        <v>469.43</v>
+        <v>232.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:05:24</t>
+          <t>07:07:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="F66" t="n">
-        <v>7.77</v>
+        <v>7.21</v>
       </c>
       <c r="G66" t="n">
-        <v>287.9</v>
+        <v>311.9</v>
       </c>
       <c r="H66" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-201.98</v>
+        <v>-138.45</v>
       </c>
       <c r="K66" t="n">
-        <v>105.03</v>
+        <v>133.41</v>
       </c>
       <c r="L66" t="n">
-        <v>227.65</v>
+        <v>192.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:06:52</t>
+          <t>07:09:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="F67" t="n">
-        <v>8.24</v>
+        <v>7.57</v>
       </c>
       <c r="G67" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H67" t="n">
         <v>55.6</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>30.41</v>
+        <v>-69.36</v>
       </c>
       <c r="K67" t="n">
-        <v>-109.46</v>
+        <v>-49.46</v>
       </c>
       <c r="L67" t="n">
-        <v>113.61</v>
+        <v>85.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:12:52</t>
+          <t>07:13:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="F68" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="G68" t="n">
-        <v>301.4</v>
+        <v>306.5</v>
       </c>
       <c r="H68" t="n">
-        <v>56.5</v>
+        <v>52.8</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-261.32</v>
+        <v>-136.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-71.38</v>
+        <v>255.24</v>
       </c>
       <c r="L68" t="n">
-        <v>270.9</v>
+        <v>289.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:14:14</t>
+          <t>07:15:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.37</v>
+        <v>2.94</v>
       </c>
       <c r="F69" t="n">
-        <v>7.94</v>
+        <v>7.86</v>
       </c>
       <c r="G69" t="n">
-        <v>295</v>
+        <v>300.5</v>
       </c>
       <c r="H69" t="n">
-        <v>50.1</v>
+        <v>54.6</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>175.91</v>
+        <v>53.08</v>
       </c>
       <c r="K69" t="n">
-        <v>8.73</v>
+        <v>152.39</v>
       </c>
       <c r="L69" t="n">
-        <v>176.12</v>
+        <v>161.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:15:55</t>
+          <t>07:16:57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="F70" t="n">
-        <v>7.83</v>
+        <v>7.37</v>
       </c>
       <c r="G70" t="n">
-        <v>292.7</v>
+        <v>295.6</v>
       </c>
       <c r="H70" t="n">
-        <v>52.6</v>
+        <v>49.9</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-29.1</v>
+        <v>-176.9</v>
       </c>
       <c r="K70" t="n">
-        <v>-345.2</v>
+        <v>278.96</v>
       </c>
       <c r="L70" t="n">
-        <v>346.42</v>
+        <v>330.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:21:07</t>
+          <t>07:21:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="F71" t="n">
-        <v>7.05</v>
+        <v>8.59</v>
       </c>
       <c r="G71" t="n">
-        <v>299.6</v>
+        <v>290.5</v>
       </c>
       <c r="H71" t="n">
-        <v>51.6</v>
+        <v>48.6</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>61.08</v>
+        <v>331.33</v>
       </c>
       <c r="K71" t="n">
-        <v>46.35</v>
+        <v>479.48</v>
       </c>
       <c r="L71" t="n">
-        <v>76.68000000000001</v>
+        <v>582.8200000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:21:58</t>
+          <t>07:23:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="F72" t="n">
-        <v>7.55</v>
+        <v>7.83</v>
       </c>
       <c r="G72" t="n">
-        <v>296.4</v>
+        <v>288.9</v>
       </c>
       <c r="H72" t="n">
-        <v>56.6</v>
+        <v>52</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>229.5</v>
+        <v>-230.35</v>
       </c>
       <c r="K72" t="n">
-        <v>-273.74</v>
+        <v>-103.35</v>
       </c>
       <c r="L72" t="n">
-        <v>357.22</v>
+        <v>252.47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:23:57</t>
+          <t>07:24:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F73" t="n">
-        <v>8.09</v>
+        <v>7.64</v>
       </c>
       <c r="G73" t="n">
-        <v>286.9</v>
+        <v>296.2</v>
       </c>
       <c r="H73" t="n">
-        <v>57.9</v>
+        <v>53.8</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-468.07</v>
+        <v>196.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-305.97</v>
+        <v>283.26</v>
       </c>
       <c r="L73" t="n">
-        <v>559.21</v>
+        <v>344.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:35:45</t>
+          <t>07:31:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>2.9</v>
       </c>
       <c r="F74" t="n">
-        <v>7.58</v>
+        <v>7.68</v>
       </c>
       <c r="G74" t="n">
-        <v>291.2</v>
+        <v>304.7</v>
       </c>
       <c r="H74" t="n">
-        <v>46.7</v>
+        <v>56.9</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-105.78</v>
+        <v>49.72</v>
       </c>
       <c r="K74" t="n">
-        <v>-141.9</v>
+        <v>-82.95</v>
       </c>
       <c r="L74" t="n">
-        <v>176.99</v>
+        <v>96.70999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:37:17</t>
+          <t>07:33:07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.03</v>
+        <v>2.46</v>
       </c>
       <c r="F75" t="n">
-        <v>8.02</v>
+        <v>8.32</v>
       </c>
       <c r="G75" t="n">
-        <v>291.9</v>
+        <v>288.7</v>
       </c>
       <c r="H75" t="n">
-        <v>50.3</v>
+        <v>53</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-67.61</v>
+        <v>128.05</v>
       </c>
       <c r="K75" t="n">
-        <v>-142.55</v>
+        <v>36.17</v>
       </c>
       <c r="L75" t="n">
-        <v>157.77</v>
+        <v>133.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:39:39</t>
+          <t>07:34:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.06</v>
+        <v>2.59</v>
       </c>
       <c r="F76" t="n">
-        <v>7.91</v>
+        <v>7.32</v>
       </c>
       <c r="G76" t="n">
-        <v>307.9</v>
+        <v>293.8</v>
       </c>
       <c r="H76" t="n">
-        <v>49.9</v>
+        <v>54.5</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-100.23</v>
+        <v>-91.66</v>
       </c>
       <c r="K76" t="n">
-        <v>-16.32</v>
+        <v>101.58</v>
       </c>
       <c r="L76" t="n">
-        <v>101.55</v>
+        <v>136.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:44:19</t>
+          <t>07:38:05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.79</v>
+        <v>2.77</v>
       </c>
       <c r="F77" t="n">
-        <v>7.42</v>
+        <v>7.54</v>
       </c>
       <c r="G77" t="n">
-        <v>300.7</v>
+        <v>309.6</v>
       </c>
       <c r="H77" t="n">
-        <v>54.9</v>
+        <v>52.3</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-162.95</v>
+        <v>-51.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-20.83</v>
+        <v>-79.94</v>
       </c>
       <c r="L77" t="n">
-        <v>164.27</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:45:42</t>
+          <t>07:39:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.42</v>
+        <v>2.93</v>
       </c>
       <c r="F78" t="n">
-        <v>7.66</v>
+        <v>7.81</v>
       </c>
       <c r="G78" t="n">
-        <v>300.3</v>
+        <v>302.3</v>
       </c>
       <c r="H78" t="n">
-        <v>53.8</v>
+        <v>51.4</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-294.55</v>
+        <v>120.48</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.22</v>
+        <v>90.33</v>
       </c>
       <c r="L78" t="n">
-        <v>294.64</v>
+        <v>150.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:46:31</t>
+          <t>07:40:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.11</v>
+        <v>2.61</v>
       </c>
       <c r="F79" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>302.8</v>
+        <v>300.4</v>
       </c>
       <c r="H79" t="n">
-        <v>55.4</v>
+        <v>54</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-40.07</v>
+        <v>-116.67</v>
       </c>
       <c r="K79" t="n">
-        <v>10.07</v>
+        <v>114.55</v>
       </c>
       <c r="L79" t="n">
-        <v>41.32</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:50:42</t>
+          <t>07:45:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.33</v>
+        <v>2.74</v>
       </c>
       <c r="F80" t="n">
-        <v>7.82</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>286.7</v>
+        <v>293.6</v>
       </c>
       <c r="H80" t="n">
-        <v>48.3</v>
+        <v>45.6</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-42.52</v>
+        <v>134.37</v>
       </c>
       <c r="K80" t="n">
-        <v>162.38</v>
+        <v>-411.3</v>
       </c>
       <c r="L80" t="n">
-        <v>167.86</v>
+        <v>432.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:51:42</t>
+          <t>07:47:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="F81" t="n">
-        <v>7.85</v>
+        <v>8.32</v>
       </c>
       <c r="G81" t="n">
-        <v>296</v>
+        <v>303.6</v>
       </c>
       <c r="H81" t="n">
-        <v>55</v>
+        <v>47.1</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>198.61</v>
+        <v>-88.41</v>
       </c>
       <c r="K81" t="n">
-        <v>266.12</v>
+        <v>36.82</v>
       </c>
       <c r="L81" t="n">
-        <v>332.06</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:54:08</t>
+          <t>07:49:17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
       <c r="F82" t="n">
-        <v>8.07</v>
+        <v>7.84</v>
       </c>
       <c r="G82" t="n">
-        <v>306.8</v>
+        <v>302.4</v>
       </c>
       <c r="H82" t="n">
-        <v>52.2</v>
+        <v>56.9</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.37</v>
+        <v>92.77</v>
       </c>
       <c r="K82" t="n">
-        <v>93.02</v>
+        <v>141.33</v>
       </c>
       <c r="L82" t="n">
-        <v>93.17</v>
+        <v>169.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>07:53:51</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="F83" t="n">
-        <v>7.57</v>
+        <v>7.49</v>
       </c>
       <c r="G83" t="n">
-        <v>295.8</v>
+        <v>291.5</v>
       </c>
       <c r="H83" t="n">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-253.29</v>
+        <v>-6.94</v>
       </c>
       <c r="K83" t="n">
-        <v>-237.44</v>
+        <v>-353.01</v>
       </c>
       <c r="L83" t="n">
-        <v>347.18</v>
+        <v>353.08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:01:25</t>
+          <t>07:55:11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="F84" t="n">
-        <v>7.75</v>
+        <v>7.58</v>
       </c>
       <c r="G84" t="n">
-        <v>307.2</v>
+        <v>292.8</v>
       </c>
       <c r="H84" t="n">
-        <v>55.1</v>
+        <v>54.1</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>126.46</v>
+        <v>-74.55</v>
       </c>
       <c r="K84" t="n">
-        <v>-197.65</v>
+        <v>141.4</v>
       </c>
       <c r="L84" t="n">
-        <v>234.64</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:02:42</t>
+          <t>07:56:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="F85" t="n">
-        <v>7.78</v>
+        <v>7.86</v>
       </c>
       <c r="G85" t="n">
-        <v>288.6</v>
+        <v>295.3</v>
       </c>
       <c r="H85" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-87.09</v>
+        <v>219.35</v>
       </c>
       <c r="K85" t="n">
-        <v>82.53</v>
+        <v>364.17</v>
       </c>
       <c r="L85" t="n">
-        <v>119.98</v>
+        <v>425.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:08:31</t>
+          <t>08:00:10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="F86" t="n">
-        <v>8.06</v>
+        <v>8.44</v>
       </c>
       <c r="G86" t="n">
-        <v>296.2</v>
+        <v>284.3</v>
       </c>
       <c r="H86" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>333.29</v>
+        <v>125.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-64.86</v>
+        <v>248.48</v>
       </c>
       <c r="L86" t="n">
-        <v>339.54</v>
+        <v>278.43</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:09:19</t>
+          <t>08:01:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="F87" t="n">
-        <v>7.65</v>
+        <v>7.85</v>
       </c>
       <c r="G87" t="n">
-        <v>317.1</v>
+        <v>293.6</v>
       </c>
       <c r="H87" t="n">
-        <v>53.6</v>
+        <v>53</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-111.12</v>
+        <v>249.7</v>
       </c>
       <c r="K87" t="n">
-        <v>357.76</v>
+        <v>-432.41</v>
       </c>
       <c r="L87" t="n">
-        <v>374.61</v>
+        <v>499.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:11:24</t>
+          <t>08:02:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="F88" t="n">
-        <v>7.83</v>
+        <v>8.32</v>
       </c>
       <c r="G88" t="n">
-        <v>281.1</v>
+        <v>288.7</v>
       </c>
       <c r="H88" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>663.45</v>
+        <v>-571.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-503.39</v>
+        <v>-63.6</v>
       </c>
       <c r="L88" t="n">
-        <v>832.8099999999999</v>
+        <v>575.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>87.94</v>
+        <v>68.09</v>
       </c>
       <c r="K14" t="n">
-        <v>-145.47</v>
+        <v>-112.63</v>
       </c>
       <c r="L14" t="n">
-        <v>169.99</v>
+        <v>131.61</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>82.29000000000001</v>
+        <v>73.45</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.27</v>
+        <v>-16.31</v>
       </c>
       <c r="L15" t="n">
-        <v>84.29000000000001</v>
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-123.04</v>
+        <v>-109.56</v>
       </c>
       <c r="K16" t="n">
-        <v>-19.83</v>
+        <v>-17.66</v>
       </c>
       <c r="L16" t="n">
-        <v>124.62</v>
+        <v>110.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-173.56</v>
+        <v>-133.31</v>
       </c>
       <c r="K17" t="n">
-        <v>-74.73</v>
+        <v>-57.4</v>
       </c>
       <c r="L17" t="n">
-        <v>188.97</v>
+        <v>145.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-189.3</v>
+        <v>-151.25</v>
       </c>
       <c r="K18" t="n">
-        <v>-118.81</v>
+        <v>-94.93000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>223.5</v>
+        <v>178.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-40.67</v>
+        <v>-31.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-173.71</v>
+        <v>-136.1</v>
       </c>
       <c r="L19" t="n">
-        <v>178.4</v>
+        <v>139.78</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-241.62</v>
+        <v>-256.51</v>
       </c>
       <c r="K20" t="n">
-        <v>4.97</v>
+        <v>5.28</v>
       </c>
       <c r="L20" t="n">
-        <v>241.67</v>
+        <v>256.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>84.92</v>
+        <v>92.67</v>
       </c>
       <c r="K21" t="n">
-        <v>-146.4</v>
+        <v>-159.76</v>
       </c>
       <c r="L21" t="n">
-        <v>169.24</v>
+        <v>184.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-142.4</v>
+        <v>-123.8</v>
       </c>
       <c r="K22" t="n">
-        <v>23.49</v>
+        <v>20.42</v>
       </c>
       <c r="L22" t="n">
-        <v>144.32</v>
+        <v>125.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>413.66</v>
+        <v>413.73</v>
       </c>
       <c r="K23" t="n">
-        <v>397.45</v>
+        <v>397.51</v>
       </c>
       <c r="L23" t="n">
-        <v>573.65</v>
+        <v>573.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-152.37</v>
+        <v>-152.05</v>
       </c>
       <c r="K24" t="n">
-        <v>-401.47</v>
+        <v>-400.63</v>
       </c>
       <c r="L24" t="n">
-        <v>429.41</v>
+        <v>428.52</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>205.62</v>
+        <v>299.15</v>
       </c>
       <c r="K25" t="n">
-        <v>41.74</v>
+        <v>60.73</v>
       </c>
       <c r="L25" t="n">
-        <v>209.81</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-115.3</v>
+        <v>-125.96</v>
       </c>
       <c r="K26" t="n">
-        <v>-569.92</v>
+        <v>-622.59</v>
       </c>
       <c r="L26" t="n">
-        <v>581.47</v>
+        <v>635.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-417.75</v>
+        <v>-505.54</v>
       </c>
       <c r="K27" t="n">
-        <v>-33.6</v>
+        <v>-40.66</v>
       </c>
       <c r="L27" t="n">
-        <v>419.1</v>
+        <v>507.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>103.61</v>
+        <v>122.35</v>
       </c>
       <c r="K28" t="n">
-        <v>-304.72</v>
+        <v>-359.82</v>
       </c>
       <c r="L28" t="n">
-        <v>321.85</v>
+        <v>380.06</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>97.18000000000001</v>
+        <v>65.38</v>
       </c>
       <c r="K29" t="n">
-        <v>110.8</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>147.38</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.13</v>
+        <v>-33.77</v>
       </c>
       <c r="K30" t="n">
-        <v>24.46</v>
+        <v>48.21</v>
       </c>
       <c r="L30" t="n">
-        <v>29.86</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.64</v>
+        <v>-12.89</v>
       </c>
       <c r="K31" t="n">
-        <v>228.67</v>
+        <v>158.17</v>
       </c>
       <c r="L31" t="n">
-        <v>229.43</v>
+        <v>158.69</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>20.93</v>
+        <v>19.06</v>
       </c>
       <c r="K32" t="n">
-        <v>116.76</v>
+        <v>106.31</v>
       </c>
       <c r="L32" t="n">
-        <v>118.62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-197.54</v>
+        <v>-157.92</v>
       </c>
       <c r="K33" t="n">
-        <v>93.54000000000001</v>
+        <v>74.78</v>
       </c>
       <c r="L33" t="n">
-        <v>218.57</v>
+        <v>174.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.869999999999999</v>
+        <v>-11.03</v>
       </c>
       <c r="K34" t="n">
-        <v>-50.33</v>
+        <v>-56.29</v>
       </c>
       <c r="L34" t="n">
-        <v>51.29</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-96.09999999999999</v>
+        <v>-114.71</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.53</v>
+        <v>-16.15</v>
       </c>
       <c r="L35" t="n">
-        <v>97.05</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-52.26</v>
+        <v>-127.68</v>
       </c>
       <c r="K36" t="n">
-        <v>7.29</v>
+        <v>17.81</v>
       </c>
       <c r="L36" t="n">
-        <v>52.77</v>
+        <v>128.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-108.91</v>
+        <v>-121.76</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.31</v>
+        <v>-5.94</v>
       </c>
       <c r="L37" t="n">
-        <v>109.04</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-189.91</v>
+        <v>-216.5</v>
       </c>
       <c r="K38" t="n">
-        <v>-45.34</v>
+        <v>-51.68</v>
       </c>
       <c r="L38" t="n">
-        <v>195.25</v>
+        <v>222.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>57.28</v>
+        <v>91.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-131.32</v>
+        <v>-210.55</v>
       </c>
       <c r="L39" t="n">
-        <v>143.26</v>
+        <v>229.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-214.26</v>
+        <v>-223.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="L40" t="n">
-        <v>214.27</v>
+        <v>223.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.18</v>
+        <v>-16.18</v>
       </c>
       <c r="K41" t="n">
-        <v>263.5</v>
+        <v>323.48</v>
       </c>
       <c r="L41" t="n">
-        <v>263.83</v>
+        <v>323.88</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>231.58</v>
+        <v>339.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-145.25</v>
+        <v>-212.84</v>
       </c>
       <c r="L42" t="n">
-        <v>273.37</v>
+        <v>400.58</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-478.81</v>
+        <v>-533.22</v>
       </c>
       <c r="K43" t="n">
-        <v>221.43</v>
+        <v>246.59</v>
       </c>
       <c r="L43" t="n">
-        <v>527.54</v>
+        <v>587.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.88</v>
+        <v>-12.79</v>
       </c>
       <c r="K44" t="n">
-        <v>189.07</v>
+        <v>143.28</v>
       </c>
       <c r="L44" t="n">
-        <v>189.82</v>
+        <v>143.85</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-32.02</v>
+        <v>-34.13</v>
       </c>
       <c r="K45" t="n">
-        <v>60.13</v>
+        <v>64.09</v>
       </c>
       <c r="L45" t="n">
-        <v>68.13</v>
+        <v>72.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>110.97</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-27.15</v>
+        <v>-23.43</v>
       </c>
       <c r="L46" t="n">
-        <v>114.24</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.7</v>
+        <v>-102.52</v>
       </c>
       <c r="K47" t="n">
-        <v>-55.63</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>103.85</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>63.8</v>
+        <v>58.67</v>
       </c>
       <c r="K48" t="n">
-        <v>101.11</v>
+        <v>92.98</v>
       </c>
       <c r="L48" t="n">
-        <v>119.55</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-39.99</v>
+        <v>-48.58</v>
       </c>
       <c r="K49" t="n">
-        <v>98.92</v>
+        <v>120.18</v>
       </c>
       <c r="L49" t="n">
-        <v>106.7</v>
+        <v>129.62</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-92.3</v>
+        <v>-90.36</v>
       </c>
       <c r="K50" t="n">
-        <v>-256.35</v>
+        <v>-250.97</v>
       </c>
       <c r="L50" t="n">
-        <v>272.46</v>
+        <v>266.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>211.08</v>
+        <v>206.59</v>
       </c>
       <c r="K51" t="n">
-        <v>20.79</v>
+        <v>20.35</v>
       </c>
       <c r="L51" t="n">
-        <v>212.1</v>
+        <v>207.59</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>167.68</v>
+        <v>143.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-189.86</v>
+        <v>-162.29</v>
       </c>
       <c r="L52" t="n">
-        <v>253.31</v>
+        <v>216.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>192.9</v>
+        <v>243.93</v>
       </c>
       <c r="K53" t="n">
-        <v>52.84</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>200.01</v>
+        <v>252.92</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-122.49</v>
+        <v>-117.92</v>
       </c>
       <c r="K54" t="n">
-        <v>354.85</v>
+        <v>341.62</v>
       </c>
       <c r="L54" t="n">
-        <v>375.4</v>
+        <v>361.4</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-157.87</v>
+        <v>-123.79</v>
       </c>
       <c r="K55" t="n">
-        <v>-324.74</v>
+        <v>-254.64</v>
       </c>
       <c r="L55" t="n">
-        <v>361.08</v>
+        <v>283.14</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>254.88</v>
+        <v>233.4</v>
       </c>
       <c r="K56" t="n">
-        <v>460.38</v>
+        <v>421.6</v>
       </c>
       <c r="L56" t="n">
-        <v>526.23</v>
+        <v>481.9</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-61.49</v>
+        <v>-56.3</v>
       </c>
       <c r="K57" t="n">
-        <v>437.61</v>
+        <v>400.71</v>
       </c>
       <c r="L57" t="n">
-        <v>441.9</v>
+        <v>404.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>170.88</v>
+        <v>227.31</v>
       </c>
       <c r="K58" t="n">
-        <v>106.57</v>
+        <v>141.76</v>
       </c>
       <c r="L58" t="n">
-        <v>201.39</v>
+        <v>267.89</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-49.9</v>
+        <v>-48.85</v>
       </c>
       <c r="K59" t="n">
-        <v>-71.04000000000001</v>
+        <v>-69.55</v>
       </c>
       <c r="L59" t="n">
-        <v>86.81</v>
+        <v>84.98999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>49.68</v>
+        <v>41.34</v>
       </c>
       <c r="K60" t="n">
-        <v>-63.35</v>
+        <v>-52.72</v>
       </c>
       <c r="L60" t="n">
-        <v>80.51000000000001</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-109.9</v>
+        <v>-91.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.34</v>
+        <v>-21.82</v>
       </c>
       <c r="L61" t="n">
-        <v>113.01</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>33.67</v>
+        <v>35.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-62.52</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>71.01000000000001</v>
+        <v>73.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-288.99</v>
+        <v>-223.96</v>
       </c>
       <c r="K63" t="n">
-        <v>219.85</v>
+        <v>170.38</v>
       </c>
       <c r="L63" t="n">
-        <v>363.11</v>
+        <v>281.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>11.91</v>
+        <v>14.88</v>
       </c>
       <c r="K64" t="n">
-        <v>101.17</v>
+        <v>126.38</v>
       </c>
       <c r="L64" t="n">
-        <v>101.87</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-191.78</v>
+        <v>-225.61</v>
       </c>
       <c r="K65" t="n">
-        <v>-131.8</v>
+        <v>-155.04</v>
       </c>
       <c r="L65" t="n">
-        <v>232.7</v>
+        <v>273.74</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-138.45</v>
+        <v>-125.31</v>
       </c>
       <c r="K66" t="n">
-        <v>133.41</v>
+        <v>120.75</v>
       </c>
       <c r="L66" t="n">
-        <v>192.27</v>
+        <v>174.02</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.36</v>
+        <v>-108.09</v>
       </c>
       <c r="K67" t="n">
-        <v>-49.46</v>
+        <v>-77.08</v>
       </c>
       <c r="L67" t="n">
-        <v>85.19</v>
+        <v>132.76</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-136.12</v>
+        <v>-141.95</v>
       </c>
       <c r="K68" t="n">
-        <v>255.24</v>
+        <v>266.17</v>
       </c>
       <c r="L68" t="n">
-        <v>289.27</v>
+        <v>301.66</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>53.08</v>
+        <v>69.53</v>
       </c>
       <c r="K69" t="n">
-        <v>152.39</v>
+        <v>199.63</v>
       </c>
       <c r="L69" t="n">
-        <v>161.37</v>
+        <v>211.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-176.9</v>
+        <v>-209.71</v>
       </c>
       <c r="K70" t="n">
-        <v>278.96</v>
+        <v>330.7</v>
       </c>
       <c r="L70" t="n">
-        <v>330.32</v>
+        <v>391.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>331.33</v>
+        <v>344.38</v>
       </c>
       <c r="K71" t="n">
-        <v>479.48</v>
+        <v>498.36</v>
       </c>
       <c r="L71" t="n">
-        <v>582.8200000000001</v>
+        <v>605.77</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-230.35</v>
+        <v>-318.44</v>
       </c>
       <c r="K72" t="n">
-        <v>-103.35</v>
+        <v>-142.87</v>
       </c>
       <c r="L72" t="n">
-        <v>252.47</v>
+        <v>349.02</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>196.09</v>
+        <v>249.05</v>
       </c>
       <c r="K73" t="n">
-        <v>283.26</v>
+        <v>359.76</v>
       </c>
       <c r="L73" t="n">
-        <v>344.52</v>
+        <v>437.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>49.72</v>
+        <v>45.49</v>
       </c>
       <c r="K74" t="n">
-        <v>-82.95</v>
+        <v>-75.89</v>
       </c>
       <c r="L74" t="n">
-        <v>96.70999999999999</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>128.05</v>
+        <v>106.44</v>
       </c>
       <c r="K75" t="n">
-        <v>36.17</v>
+        <v>30.07</v>
       </c>
       <c r="L75" t="n">
-        <v>133.06</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-91.66</v>
+        <v>-69.09999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>101.58</v>
+        <v>76.58</v>
       </c>
       <c r="L76" t="n">
-        <v>136.82</v>
+        <v>103.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-51.84</v>
+        <v>-51.7</v>
       </c>
       <c r="K77" t="n">
-        <v>-79.94</v>
+        <v>-79.73</v>
       </c>
       <c r="L77" t="n">
-        <v>95.28</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>120.48</v>
+        <v>108.88</v>
       </c>
       <c r="K78" t="n">
-        <v>90.33</v>
+        <v>81.64</v>
       </c>
       <c r="L78" t="n">
-        <v>150.59</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-116.67</v>
+        <v>-109.37</v>
       </c>
       <c r="K79" t="n">
-        <v>114.55</v>
+        <v>107.38</v>
       </c>
       <c r="L79" t="n">
-        <v>163.5</v>
+        <v>153.27</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>134.37</v>
+        <v>119.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-411.3</v>
+        <v>-367.05</v>
       </c>
       <c r="L80" t="n">
-        <v>432.69</v>
+        <v>386.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-88.41</v>
+        <v>-120.84</v>
       </c>
       <c r="K81" t="n">
-        <v>36.82</v>
+        <v>50.33</v>
       </c>
       <c r="L81" t="n">
-        <v>95.77</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>92.77</v>
+        <v>97.62</v>
       </c>
       <c r="K82" t="n">
-        <v>141.33</v>
+        <v>148.71</v>
       </c>
       <c r="L82" t="n">
-        <v>169.06</v>
+        <v>177.89</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.94</v>
+        <v>-6.07</v>
       </c>
       <c r="K83" t="n">
-        <v>-353.01</v>
+        <v>-308.45</v>
       </c>
       <c r="L83" t="n">
-        <v>353.08</v>
+        <v>308.51</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-74.55</v>
+        <v>-113.63</v>
       </c>
       <c r="K84" t="n">
-        <v>141.4</v>
+        <v>215.53</v>
       </c>
       <c r="L84" t="n">
-        <v>159.85</v>
+        <v>243.65</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>219.35</v>
+        <v>234.93</v>
       </c>
       <c r="K85" t="n">
-        <v>364.17</v>
+        <v>390.03</v>
       </c>
       <c r="L85" t="n">
-        <v>425.13</v>
+        <v>455.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>125.62</v>
+        <v>159.71</v>
       </c>
       <c r="K86" t="n">
-        <v>248.48</v>
+        <v>315.92</v>
       </c>
       <c r="L86" t="n">
-        <v>278.43</v>
+        <v>353.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>249.7</v>
+        <v>256.32</v>
       </c>
       <c r="K87" t="n">
-        <v>-432.41</v>
+        <v>-443.87</v>
       </c>
       <c r="L87" t="n">
-        <v>499.33</v>
+        <v>512.5599999999999</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-571.5</v>
+        <v>-635.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-63.6</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>575.03</v>
+        <v>639.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>68.09</v>
+        <v>63.75</v>
       </c>
       <c r="K14" t="n">
-        <v>-112.63</v>
+        <v>-105.45</v>
       </c>
       <c r="L14" t="n">
-        <v>131.61</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>73.45</v>
+        <v>68.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.31</v>
+        <v>-15.17</v>
       </c>
       <c r="L15" t="n">
-        <v>75.23999999999999</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-109.56</v>
+        <v>-91.94</v>
       </c>
       <c r="K16" t="n">
-        <v>-17.66</v>
+        <v>-14.82</v>
       </c>
       <c r="L16" t="n">
-        <v>110.97</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-133.31</v>
+        <v>-118.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-57.4</v>
+        <v>-50.9</v>
       </c>
       <c r="L17" t="n">
-        <v>145.14</v>
+        <v>128.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-151.25</v>
+        <v>-126.33</v>
       </c>
       <c r="K18" t="n">
-        <v>-94.93000000000001</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>178.57</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-31.86</v>
+        <v>-27.56</v>
       </c>
       <c r="K19" t="n">
-        <v>-136.1</v>
+        <v>-117.72</v>
       </c>
       <c r="L19" t="n">
-        <v>139.78</v>
+        <v>120.91</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-256.51</v>
+        <v>-170.59</v>
       </c>
       <c r="K20" t="n">
-        <v>5.28</v>
+        <v>3.51</v>
       </c>
       <c r="L20" t="n">
-        <v>256.57</v>
+        <v>170.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>92.67</v>
+        <v>68.78</v>
       </c>
       <c r="K21" t="n">
-        <v>-159.76</v>
+        <v>-118.58</v>
       </c>
       <c r="L21" t="n">
-        <v>184.7</v>
+        <v>137.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-123.8</v>
+        <v>-103.12</v>
       </c>
       <c r="K22" t="n">
-        <v>20.42</v>
+        <v>17.01</v>
       </c>
       <c r="L22" t="n">
-        <v>125.47</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>413.73</v>
+        <v>244.42</v>
       </c>
       <c r="K23" t="n">
-        <v>397.51</v>
+        <v>234.84</v>
       </c>
       <c r="L23" t="n">
-        <v>573.75</v>
+        <v>338.95</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-152.05</v>
+        <v>-90.54000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-400.63</v>
+        <v>-238.57</v>
       </c>
       <c r="L24" t="n">
-        <v>428.52</v>
+        <v>255.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>299.15</v>
+        <v>180.09</v>
       </c>
       <c r="K25" t="n">
-        <v>60.73</v>
+        <v>36.56</v>
       </c>
       <c r="L25" t="n">
-        <v>305.25</v>
+        <v>183.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-125.96</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-622.59</v>
+        <v>-341.09</v>
       </c>
       <c r="L26" t="n">
-        <v>635.21</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-505.54</v>
+        <v>-271.27</v>
       </c>
       <c r="K27" t="n">
-        <v>-40.66</v>
+        <v>-21.82</v>
       </c>
       <c r="L27" t="n">
-        <v>507.17</v>
+        <v>272.15</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>122.35</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-359.82</v>
+        <v>-211.22</v>
       </c>
       <c r="L28" t="n">
-        <v>380.06</v>
+        <v>223.09</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>65.38</v>
+        <v>67.73</v>
       </c>
       <c r="K29" t="n">
-        <v>74.54000000000001</v>
+        <v>77.22</v>
       </c>
       <c r="L29" t="n">
-        <v>99.15000000000001</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-33.77</v>
+        <v>-30.81</v>
       </c>
       <c r="K30" t="n">
-        <v>48.21</v>
+        <v>43.98</v>
       </c>
       <c r="L30" t="n">
-        <v>58.87</v>
+        <v>53.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.89</v>
+        <v>-11.93</v>
       </c>
       <c r="K31" t="n">
-        <v>158.17</v>
+        <v>146.37</v>
       </c>
       <c r="L31" t="n">
-        <v>158.69</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>19.06</v>
+        <v>17.2</v>
       </c>
       <c r="K32" t="n">
-        <v>106.31</v>
+        <v>95.92</v>
       </c>
       <c r="L32" t="n">
-        <v>108</v>
+        <v>97.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-157.92</v>
+        <v>-138.91</v>
       </c>
       <c r="K33" t="n">
-        <v>74.78</v>
+        <v>65.78</v>
       </c>
       <c r="L33" t="n">
-        <v>174.73</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.03</v>
+        <v>-11.29</v>
       </c>
       <c r="K34" t="n">
-        <v>-56.29</v>
+        <v>-57.62</v>
       </c>
       <c r="L34" t="n">
-        <v>57.36</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-114.71</v>
+        <v>-92.31</v>
       </c>
       <c r="K35" t="n">
-        <v>-16.15</v>
+        <v>-13</v>
       </c>
       <c r="L35" t="n">
-        <v>115.84</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-127.68</v>
+        <v>-83.95</v>
       </c>
       <c r="K36" t="n">
-        <v>17.81</v>
+        <v>11.71</v>
       </c>
       <c r="L36" t="n">
-        <v>128.92</v>
+        <v>84.76000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-121.76</v>
+        <v>-101.05</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.94</v>
+        <v>-4.93</v>
       </c>
       <c r="L37" t="n">
-        <v>121.91</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-216.5</v>
+        <v>-141.69</v>
       </c>
       <c r="K38" t="n">
-        <v>-51.68</v>
+        <v>-33.83</v>
       </c>
       <c r="L38" t="n">
-        <v>222.58</v>
+        <v>145.67</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>91.84</v>
+        <v>56.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-210.55</v>
+        <v>-129.54</v>
       </c>
       <c r="L39" t="n">
-        <v>229.71</v>
+        <v>141.33</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-223.59</v>
+        <v>-161.51</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.63</v>
+        <v>-0.46</v>
       </c>
       <c r="L40" t="n">
-        <v>223.59</v>
+        <v>161.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.18</v>
+        <v>-10.12</v>
       </c>
       <c r="K41" t="n">
-        <v>323.48</v>
+        <v>202.34</v>
       </c>
       <c r="L41" t="n">
-        <v>323.88</v>
+        <v>202.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>339.36</v>
+        <v>184.62</v>
       </c>
       <c r="K42" t="n">
-        <v>-212.84</v>
+        <v>-115.79</v>
       </c>
       <c r="L42" t="n">
-        <v>400.58</v>
+        <v>217.92</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-533.22</v>
+        <v>-286.13</v>
       </c>
       <c r="K43" t="n">
-        <v>246.59</v>
+        <v>132.32</v>
       </c>
       <c r="L43" t="n">
-        <v>587.47</v>
+        <v>315.24</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.79</v>
+        <v>-10.87</v>
       </c>
       <c r="K44" t="n">
-        <v>143.28</v>
+        <v>121.69</v>
       </c>
       <c r="L44" t="n">
-        <v>143.85</v>
+        <v>122.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.13</v>
+        <v>-33.3</v>
       </c>
       <c r="K45" t="n">
-        <v>64.09</v>
+        <v>62.53</v>
       </c>
       <c r="L45" t="n">
-        <v>72.61</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>95.76000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.43</v>
+        <v>-22.1</v>
       </c>
       <c r="L46" t="n">
-        <v>98.59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-102.52</v>
+        <v>-82.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-65.04000000000001</v>
+        <v>-52.25</v>
       </c>
       <c r="L47" t="n">
-        <v>121.41</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>58.67</v>
+        <v>56.16</v>
       </c>
       <c r="K48" t="n">
-        <v>92.98</v>
+        <v>89</v>
       </c>
       <c r="L48" t="n">
-        <v>109.94</v>
+        <v>105.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.58</v>
+        <v>-36.65</v>
       </c>
       <c r="K49" t="n">
-        <v>120.18</v>
+        <v>90.66</v>
       </c>
       <c r="L49" t="n">
-        <v>129.62</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-90.36</v>
+        <v>-65.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-250.97</v>
+        <v>-181.62</v>
       </c>
       <c r="L50" t="n">
-        <v>266.74</v>
+        <v>193.03</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>206.59</v>
+        <v>158.46</v>
       </c>
       <c r="K51" t="n">
-        <v>20.35</v>
+        <v>15.61</v>
       </c>
       <c r="L51" t="n">
-        <v>207.59</v>
+        <v>159.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>143.34</v>
+        <v>120.13</v>
       </c>
       <c r="K52" t="n">
-        <v>-162.29</v>
+        <v>-136.02</v>
       </c>
       <c r="L52" t="n">
-        <v>216.53</v>
+        <v>181.48</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>243.93</v>
+        <v>162.5</v>
       </c>
       <c r="K53" t="n">
-        <v>66.81999999999999</v>
+        <v>44.51</v>
       </c>
       <c r="L53" t="n">
-        <v>252.92</v>
+        <v>168.49</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-117.92</v>
+        <v>-75.55</v>
       </c>
       <c r="K54" t="n">
-        <v>341.62</v>
+        <v>218.87</v>
       </c>
       <c r="L54" t="n">
-        <v>361.4</v>
+        <v>231.54</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-123.79</v>
+        <v>-96.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-254.64</v>
+        <v>-198.72</v>
       </c>
       <c r="L55" t="n">
-        <v>283.14</v>
+        <v>220.96</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>233.4</v>
+        <v>149.1</v>
       </c>
       <c r="K56" t="n">
-        <v>421.6</v>
+        <v>269.33</v>
       </c>
       <c r="L56" t="n">
-        <v>481.9</v>
+        <v>307.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-56.3</v>
+        <v>-37.75</v>
       </c>
       <c r="K57" t="n">
-        <v>400.71</v>
+        <v>268.67</v>
       </c>
       <c r="L57" t="n">
-        <v>404.65</v>
+        <v>271.3</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>227.31</v>
+        <v>154.1</v>
       </c>
       <c r="K58" t="n">
-        <v>141.76</v>
+        <v>96.11</v>
       </c>
       <c r="L58" t="n">
-        <v>267.89</v>
+        <v>181.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-48.85</v>
+        <v>-42.69</v>
       </c>
       <c r="K59" t="n">
-        <v>-69.55</v>
+        <v>-60.78</v>
       </c>
       <c r="L59" t="n">
-        <v>84.98999999999999</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>41.34</v>
+        <v>41.84</v>
       </c>
       <c r="K60" t="n">
-        <v>-52.72</v>
+        <v>-53.35</v>
       </c>
       <c r="L60" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-91.06</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.82</v>
+        <v>-22.27</v>
       </c>
       <c r="L61" t="n">
-        <v>93.64</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>35.03</v>
+        <v>33.82</v>
       </c>
       <c r="K62" t="n">
-        <v>-65.04000000000001</v>
+        <v>-62.81</v>
       </c>
       <c r="L62" t="n">
-        <v>73.87</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-223.96</v>
+        <v>-176.68</v>
       </c>
       <c r="K63" t="n">
-        <v>170.38</v>
+        <v>134.41</v>
       </c>
       <c r="L63" t="n">
-        <v>281.41</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>14.88</v>
+        <v>12.1</v>
       </c>
       <c r="K64" t="n">
-        <v>126.38</v>
+        <v>102.82</v>
       </c>
       <c r="L64" t="n">
-        <v>127.25</v>
+        <v>103.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-225.61</v>
+        <v>-145.51</v>
       </c>
       <c r="K65" t="n">
-        <v>-155.04</v>
+        <v>-100</v>
       </c>
       <c r="L65" t="n">
-        <v>273.74</v>
+        <v>176.56</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-125.31</v>
+        <v>-103.38</v>
       </c>
       <c r="K66" t="n">
-        <v>120.75</v>
+        <v>99.62</v>
       </c>
       <c r="L66" t="n">
-        <v>174.02</v>
+        <v>143.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-108.09</v>
+        <v>-80.06999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-77.08</v>
+        <v>-57.1</v>
       </c>
       <c r="L67" t="n">
-        <v>132.76</v>
+        <v>98.34</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-141.95</v>
+        <v>-93.51000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>266.17</v>
+        <v>175.33</v>
       </c>
       <c r="L68" t="n">
-        <v>301.66</v>
+        <v>198.71</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>69.53</v>
+        <v>48.85</v>
       </c>
       <c r="K69" t="n">
-        <v>199.63</v>
+        <v>140.27</v>
       </c>
       <c r="L69" t="n">
-        <v>211.4</v>
+        <v>148.53</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-209.71</v>
+        <v>-123.71</v>
       </c>
       <c r="K70" t="n">
-        <v>330.7</v>
+        <v>195.09</v>
       </c>
       <c r="L70" t="n">
-        <v>391.59</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>344.38</v>
+        <v>201.92</v>
       </c>
       <c r="K71" t="n">
-        <v>498.36</v>
+        <v>292.21</v>
       </c>
       <c r="L71" t="n">
-        <v>605.77</v>
+        <v>355.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-318.44</v>
+        <v>-188.65</v>
       </c>
       <c r="K72" t="n">
-        <v>-142.87</v>
+        <v>-84.64</v>
       </c>
       <c r="L72" t="n">
-        <v>349.02</v>
+        <v>206.77</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>249.05</v>
+        <v>141.38</v>
       </c>
       <c r="K73" t="n">
-        <v>359.76</v>
+        <v>204.22</v>
       </c>
       <c r="L73" t="n">
-        <v>437.55</v>
+        <v>248.38</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>45.49</v>
+        <v>44.28</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.89</v>
+        <v>-73.87</v>
       </c>
       <c r="L74" t="n">
-        <v>88.48</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>106.44</v>
+        <v>90.89</v>
       </c>
       <c r="K75" t="n">
-        <v>30.07</v>
+        <v>25.68</v>
       </c>
       <c r="L75" t="n">
-        <v>110.6</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-69.09999999999999</v>
+        <v>-67.06999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>76.58</v>
+        <v>74.33</v>
       </c>
       <c r="L76" t="n">
-        <v>103.14</v>
+        <v>100.12</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-51.7</v>
+        <v>-48.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-79.73</v>
+        <v>-74.23</v>
       </c>
       <c r="L77" t="n">
-        <v>95.02</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>108.88</v>
+        <v>95.62</v>
       </c>
       <c r="K78" t="n">
-        <v>81.64</v>
+        <v>71.69</v>
       </c>
       <c r="L78" t="n">
-        <v>136.09</v>
+        <v>119.51</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-109.37</v>
+        <v>-85.08</v>
       </c>
       <c r="K79" t="n">
-        <v>107.38</v>
+        <v>83.53</v>
       </c>
       <c r="L79" t="n">
-        <v>153.27</v>
+        <v>119.23</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>119.91</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-367.05</v>
+        <v>-244.34</v>
       </c>
       <c r="L80" t="n">
-        <v>386.14</v>
+        <v>257.04</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-120.84</v>
+        <v>-93.5</v>
       </c>
       <c r="K81" t="n">
-        <v>50.33</v>
+        <v>38.94</v>
       </c>
       <c r="L81" t="n">
-        <v>130.9</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>97.62</v>
+        <v>71.48</v>
       </c>
       <c r="K82" t="n">
-        <v>148.71</v>
+        <v>108.9</v>
       </c>
       <c r="L82" t="n">
-        <v>177.89</v>
+        <v>130.27</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.07</v>
+        <v>-4.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-308.45</v>
+        <v>-231</v>
       </c>
       <c r="L83" t="n">
-        <v>308.51</v>
+        <v>231.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-113.63</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>215.53</v>
+        <v>132.7</v>
       </c>
       <c r="L84" t="n">
-        <v>243.65</v>
+        <v>150.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>234.93</v>
+        <v>139.29</v>
       </c>
       <c r="K85" t="n">
-        <v>390.03</v>
+        <v>231.26</v>
       </c>
       <c r="L85" t="n">
-        <v>455.31</v>
+        <v>269.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>159.71</v>
+        <v>101.36</v>
       </c>
       <c r="K86" t="n">
-        <v>315.92</v>
+        <v>200.49</v>
       </c>
       <c r="L86" t="n">
-        <v>353.99</v>
+        <v>224.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>256.32</v>
+        <v>153.35</v>
       </c>
       <c r="K87" t="n">
-        <v>-443.87</v>
+        <v>-265.56</v>
       </c>
       <c r="L87" t="n">
-        <v>512.5599999999999</v>
+        <v>306.66</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-635.83</v>
+        <v>-364.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-70.76000000000001</v>
+        <v>-40.53</v>
       </c>
       <c r="L88" t="n">
-        <v>639.75</v>
+        <v>366.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>63.75</v>
+        <v>62</v>
       </c>
       <c r="K14" t="n">
-        <v>-105.45</v>
+        <v>-102.56</v>
       </c>
       <c r="L14" t="n">
-        <v>123.23</v>
+        <v>119.84</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>68.31</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.17</v>
+        <v>-15.03</v>
       </c>
       <c r="L15" t="n">
-        <v>69.98</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-91.94</v>
+        <v>-90.83</v>
       </c>
       <c r="K16" t="n">
-        <v>-14.82</v>
+        <v>-14.64</v>
       </c>
       <c r="L16" t="n">
-        <v>93.13</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-118.21</v>
+        <v>-119.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-50.9</v>
+        <v>-51.25</v>
       </c>
       <c r="L17" t="n">
-        <v>128.71</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-126.33</v>
+        <v>-129.12</v>
       </c>
       <c r="K18" t="n">
-        <v>-79.29000000000001</v>
+        <v>-81.04000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>149.15</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.56</v>
+        <v>-28.12</v>
       </c>
       <c r="K19" t="n">
-        <v>-117.72</v>
+        <v>-120.1</v>
       </c>
       <c r="L19" t="n">
-        <v>120.91</v>
+        <v>123.34</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-170.59</v>
+        <v>-181.49</v>
       </c>
       <c r="K20" t="n">
-        <v>3.51</v>
+        <v>3.73</v>
       </c>
       <c r="L20" t="n">
-        <v>170.62</v>
+        <v>181.53</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>68.78</v>
+        <v>71.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-118.58</v>
+        <v>-123.9</v>
       </c>
       <c r="L21" t="n">
-        <v>137.08</v>
+        <v>143.23</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-103.12</v>
+        <v>-106.47</v>
       </c>
       <c r="K22" t="n">
-        <v>17.01</v>
+        <v>17.56</v>
       </c>
       <c r="L22" t="n">
-        <v>104.51</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>244.42</v>
+        <v>265.68</v>
       </c>
       <c r="K23" t="n">
-        <v>234.84</v>
+        <v>255.27</v>
       </c>
       <c r="L23" t="n">
-        <v>338.95</v>
+        <v>368.44</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-90.54000000000001</v>
+        <v>-98.34</v>
       </c>
       <c r="K24" t="n">
-        <v>-238.57</v>
+        <v>-259.11</v>
       </c>
       <c r="L24" t="n">
-        <v>255.18</v>
+        <v>277.15</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>180.09</v>
+        <v>193.01</v>
       </c>
       <c r="K25" t="n">
-        <v>36.56</v>
+        <v>39.18</v>
       </c>
       <c r="L25" t="n">
-        <v>183.77</v>
+        <v>196.95</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-69.01000000000001</v>
+        <v>-77.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-341.09</v>
+        <v>-381.97</v>
       </c>
       <c r="L26" t="n">
-        <v>348</v>
+        <v>389.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-271.27</v>
+        <v>-298.47</v>
       </c>
       <c r="K27" t="n">
-        <v>-21.82</v>
+        <v>-24</v>
       </c>
       <c r="L27" t="n">
-        <v>272.15</v>
+        <v>299.44</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>71.81999999999999</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-211.22</v>
+        <v>-231.47</v>
       </c>
       <c r="L28" t="n">
-        <v>223.09</v>
+        <v>244.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>67.73</v>
+        <v>64.87</v>
       </c>
       <c r="K29" t="n">
-        <v>77.22</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>102.72</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-30.81</v>
+        <v>-29.76</v>
       </c>
       <c r="K30" t="n">
-        <v>43.98</v>
+        <v>42.48</v>
       </c>
       <c r="L30" t="n">
-        <v>53.69</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.93</v>
+        <v>-11.67</v>
       </c>
       <c r="K31" t="n">
-        <v>146.37</v>
+        <v>143.22</v>
       </c>
       <c r="L31" t="n">
-        <v>146.85</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.27</v>
       </c>
       <c r="K32" t="n">
-        <v>95.92</v>
+        <v>96.34</v>
       </c>
       <c r="L32" t="n">
-        <v>97.45</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-138.91</v>
+        <v>-141.34</v>
       </c>
       <c r="K33" t="n">
-        <v>65.78</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>153.7</v>
+        <v>156.39</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.29</v>
+        <v>-11.19</v>
       </c>
       <c r="K34" t="n">
-        <v>-57.62</v>
+        <v>-57.06</v>
       </c>
       <c r="L34" t="n">
-        <v>58.72</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-92.31</v>
+        <v>-96.48999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-13</v>
+        <v>-13.59</v>
       </c>
       <c r="L35" t="n">
-        <v>93.22</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-83.95</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>11.71</v>
+        <v>12.43</v>
       </c>
       <c r="L36" t="n">
-        <v>84.76000000000001</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-101.05</v>
+        <v>-105.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.93</v>
+        <v>-5.14</v>
       </c>
       <c r="L37" t="n">
-        <v>101.17</v>
+        <v>105.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-141.69</v>
+        <v>-154.97</v>
       </c>
       <c r="K38" t="n">
-        <v>-33.83</v>
+        <v>-37</v>
       </c>
       <c r="L38" t="n">
-        <v>145.67</v>
+        <v>159.32</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="K39" t="n">
-        <v>-129.54</v>
+        <v>-138.95</v>
       </c>
       <c r="L39" t="n">
-        <v>141.33</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-161.51</v>
+        <v>-172.72</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="L40" t="n">
-        <v>161.51</v>
+        <v>172.72</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.12</v>
+        <v>-10.92</v>
       </c>
       <c r="K41" t="n">
-        <v>202.34</v>
+        <v>218.27</v>
       </c>
       <c r="L41" t="n">
-        <v>202.6</v>
+        <v>218.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>184.62</v>
+        <v>202.19</v>
       </c>
       <c r="K42" t="n">
-        <v>-115.79</v>
+        <v>-126.81</v>
       </c>
       <c r="L42" t="n">
-        <v>217.92</v>
+        <v>238.66</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-286.13</v>
+        <v>-319.26</v>
       </c>
       <c r="K43" t="n">
-        <v>132.32</v>
+        <v>147.65</v>
       </c>
       <c r="L43" t="n">
-        <v>315.24</v>
+        <v>351.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.87</v>
+        <v>-10.89</v>
       </c>
       <c r="K44" t="n">
-        <v>121.69</v>
+        <v>122.01</v>
       </c>
       <c r="L44" t="n">
-        <v>122.17</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-33.3</v>
+        <v>-32.29</v>
       </c>
       <c r="K45" t="n">
-        <v>62.53</v>
+        <v>60.64</v>
       </c>
       <c r="L45" t="n">
-        <v>70.84</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>90.34</v>
+        <v>88.12</v>
       </c>
       <c r="K46" t="n">
-        <v>-22.1</v>
+        <v>-21.56</v>
       </c>
       <c r="L46" t="n">
-        <v>93</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-82.37</v>
+        <v>-83.06999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.25</v>
+        <v>-52.7</v>
       </c>
       <c r="L47" t="n">
-        <v>97.55</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>56.16</v>
+        <v>56.68</v>
       </c>
       <c r="K48" t="n">
-        <v>89</v>
+        <v>89.83</v>
       </c>
       <c r="L48" t="n">
-        <v>105.23</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-36.65</v>
+        <v>-38.02</v>
       </c>
       <c r="K49" t="n">
-        <v>90.66</v>
+        <v>94.06</v>
       </c>
       <c r="L49" t="n">
-        <v>97.78</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-65.39</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-181.62</v>
+        <v>-190.46</v>
       </c>
       <c r="L50" t="n">
-        <v>193.03</v>
+        <v>202.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>158.46</v>
+        <v>165.58</v>
       </c>
       <c r="K51" t="n">
-        <v>15.61</v>
+        <v>16.31</v>
       </c>
       <c r="L51" t="n">
-        <v>159.22</v>
+        <v>166.39</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>120.13</v>
+        <v>124.25</v>
       </c>
       <c r="K52" t="n">
-        <v>-136.02</v>
+        <v>-140.68</v>
       </c>
       <c r="L52" t="n">
-        <v>181.48</v>
+        <v>187.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>162.5</v>
+        <v>173.43</v>
       </c>
       <c r="K53" t="n">
-        <v>44.51</v>
+        <v>47.51</v>
       </c>
       <c r="L53" t="n">
-        <v>168.49</v>
+        <v>179.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-75.55</v>
+        <v>-82.15000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>218.87</v>
+        <v>238</v>
       </c>
       <c r="L54" t="n">
-        <v>231.54</v>
+        <v>251.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-96.61</v>
+        <v>-102.22</v>
       </c>
       <c r="K55" t="n">
-        <v>-198.72</v>
+        <v>-210.26</v>
       </c>
       <c r="L55" t="n">
-        <v>220.96</v>
+        <v>233.79</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>149.1</v>
+        <v>161.84</v>
       </c>
       <c r="K56" t="n">
-        <v>269.33</v>
+        <v>292.32</v>
       </c>
       <c r="L56" t="n">
-        <v>307.85</v>
+        <v>334.13</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-37.75</v>
+        <v>-40.93</v>
       </c>
       <c r="K57" t="n">
-        <v>268.67</v>
+        <v>291.33</v>
       </c>
       <c r="L57" t="n">
-        <v>271.3</v>
+        <v>294.2</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>154.1</v>
+        <v>164.5</v>
       </c>
       <c r="K58" t="n">
-        <v>96.11</v>
+        <v>102.59</v>
       </c>
       <c r="L58" t="n">
-        <v>181.61</v>
+        <v>193.87</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.69</v>
+        <v>-41.8</v>
       </c>
       <c r="K59" t="n">
-        <v>-60.78</v>
+        <v>-59.51</v>
       </c>
       <c r="L59" t="n">
-        <v>74.28</v>
+        <v>72.72</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>41.84</v>
+        <v>40.7</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.35</v>
+        <v>-51.91</v>
       </c>
       <c r="L60" t="n">
-        <v>67.8</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-92.93000000000001</v>
+        <v>-89.48</v>
       </c>
       <c r="K61" t="n">
-        <v>-22.27</v>
+        <v>-21.44</v>
       </c>
       <c r="L61" t="n">
-        <v>95.56</v>
+        <v>92.02</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>33.82</v>
+        <v>33.72</v>
       </c>
       <c r="K62" t="n">
-        <v>-62.81</v>
+        <v>-62.61</v>
       </c>
       <c r="L62" t="n">
-        <v>71.33</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-176.68</v>
+        <v>-181.39</v>
       </c>
       <c r="K63" t="n">
-        <v>134.41</v>
+        <v>138</v>
       </c>
       <c r="L63" t="n">
-        <v>222</v>
+        <v>227.92</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>12.1</v>
+        <v>12.42</v>
       </c>
       <c r="K64" t="n">
-        <v>102.82</v>
+        <v>105.53</v>
       </c>
       <c r="L64" t="n">
-        <v>103.53</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-145.51</v>
+        <v>-156.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-100</v>
+        <v>-107.44</v>
       </c>
       <c r="L65" t="n">
-        <v>176.56</v>
+        <v>189.7</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-103.38</v>
+        <v>-107.94</v>
       </c>
       <c r="K66" t="n">
-        <v>99.62</v>
+        <v>104.01</v>
       </c>
       <c r="L66" t="n">
-        <v>143.57</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-80.06999999999999</v>
+        <v>-84.69</v>
       </c>
       <c r="K67" t="n">
-        <v>-57.1</v>
+        <v>-60.39</v>
       </c>
       <c r="L67" t="n">
-        <v>98.34</v>
+        <v>104.02</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-93.51000000000001</v>
+        <v>-100.93</v>
       </c>
       <c r="K68" t="n">
-        <v>175.33</v>
+        <v>189.26</v>
       </c>
       <c r="L68" t="n">
-        <v>198.71</v>
+        <v>214.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>48.85</v>
+        <v>52.15</v>
       </c>
       <c r="K69" t="n">
-        <v>140.27</v>
+        <v>149.73</v>
       </c>
       <c r="L69" t="n">
-        <v>148.53</v>
+        <v>158.55</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-123.71</v>
+        <v>-133.84</v>
       </c>
       <c r="K70" t="n">
-        <v>195.09</v>
+        <v>211.06</v>
       </c>
       <c r="L70" t="n">
-        <v>231</v>
+        <v>249.92</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>201.92</v>
+        <v>218.89</v>
       </c>
       <c r="K71" t="n">
-        <v>292.21</v>
+        <v>316.76</v>
       </c>
       <c r="L71" t="n">
-        <v>355.18</v>
+        <v>385.03</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-188.65</v>
+        <v>-205.76</v>
       </c>
       <c r="K72" t="n">
-        <v>-84.64</v>
+        <v>-92.31</v>
       </c>
       <c r="L72" t="n">
-        <v>206.77</v>
+        <v>225.51</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>141.38</v>
+        <v>155.31</v>
       </c>
       <c r="K73" t="n">
-        <v>204.22</v>
+        <v>224.35</v>
       </c>
       <c r="L73" t="n">
-        <v>248.38</v>
+        <v>272.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>44.28</v>
+        <v>43.11</v>
       </c>
       <c r="K74" t="n">
-        <v>-73.87</v>
+        <v>-71.91</v>
       </c>
       <c r="L74" t="n">
-        <v>86.13</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>90.89</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>25.68</v>
+        <v>25.53</v>
       </c>
       <c r="L75" t="n">
-        <v>94.44</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-67.06999999999999</v>
+        <v>-65.45</v>
       </c>
       <c r="K76" t="n">
-        <v>74.33</v>
+        <v>72.53</v>
       </c>
       <c r="L76" t="n">
-        <v>100.12</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-48.14</v>
+        <v>-48.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.23</v>
+        <v>-74.64</v>
       </c>
       <c r="L77" t="n">
-        <v>88.48</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>95.62</v>
+        <v>96.78</v>
       </c>
       <c r="K78" t="n">
-        <v>71.69</v>
+        <v>72.56</v>
       </c>
       <c r="L78" t="n">
-        <v>119.51</v>
+        <v>120.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-85.08</v>
+        <v>-87.83</v>
       </c>
       <c r="K79" t="n">
-        <v>83.53</v>
+        <v>86.23</v>
       </c>
       <c r="L79" t="n">
-        <v>119.23</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>79.81999999999999</v>
+        <v>84.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-244.34</v>
+        <v>-258.8</v>
       </c>
       <c r="L80" t="n">
-        <v>257.04</v>
+        <v>272.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-93.5</v>
+        <v>-97.2</v>
       </c>
       <c r="K81" t="n">
-        <v>38.94</v>
+        <v>40.48</v>
       </c>
       <c r="L81" t="n">
-        <v>101.28</v>
+        <v>105.29</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>71.48</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>108.9</v>
+        <v>116.01</v>
       </c>
       <c r="L82" t="n">
-        <v>130.27</v>
+        <v>138.77</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.54</v>
+        <v>-4.83</v>
       </c>
       <c r="K83" t="n">
-        <v>-231</v>
+        <v>-245.53</v>
       </c>
       <c r="L83" t="n">
-        <v>231.05</v>
+        <v>245.58</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-69.95999999999999</v>
+        <v>-75.81</v>
       </c>
       <c r="K84" t="n">
-        <v>132.7</v>
+        <v>143.78</v>
       </c>
       <c r="L84" t="n">
-        <v>150.02</v>
+        <v>162.54</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>139.29</v>
+        <v>151.38</v>
       </c>
       <c r="K85" t="n">
-        <v>231.26</v>
+        <v>251.32</v>
       </c>
       <c r="L85" t="n">
-        <v>269.97</v>
+        <v>293.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>101.36</v>
+        <v>108.89</v>
       </c>
       <c r="K86" t="n">
-        <v>200.49</v>
+        <v>215.38</v>
       </c>
       <c r="L86" t="n">
-        <v>224.66</v>
+        <v>241.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>153.35</v>
+        <v>167.7</v>
       </c>
       <c r="K87" t="n">
-        <v>-265.56</v>
+        <v>-290.41</v>
       </c>
       <c r="L87" t="n">
-        <v>306.66</v>
+        <v>335.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-364.19</v>
+        <v>-395.89</v>
       </c>
       <c r="K88" t="n">
-        <v>-40.53</v>
+        <v>-44.06</v>
       </c>
       <c r="L88" t="n">
-        <v>366.44</v>
+        <v>398.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>62</v>
+        <v>35.93</v>
       </c>
       <c r="K14" t="n">
-        <v>-102.56</v>
+        <v>-59.44</v>
       </c>
       <c r="L14" t="n">
-        <v>119.84</v>
+        <v>69.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>67.68000000000001</v>
+        <v>43.15</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.03</v>
+        <v>-9.58</v>
       </c>
       <c r="L15" t="n">
-        <v>69.33</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-90.83</v>
+        <v>-55.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-14.64</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>92.01000000000001</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-119.03</v>
+        <v>-76.12</v>
       </c>
       <c r="K17" t="n">
-        <v>-51.25</v>
+        <v>-32.77</v>
       </c>
       <c r="L17" t="n">
-        <v>129.59</v>
+        <v>82.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-129.12</v>
+        <v>-79</v>
       </c>
       <c r="K18" t="n">
-        <v>-81.04000000000001</v>
+        <v>-49.58</v>
       </c>
       <c r="L18" t="n">
-        <v>152.45</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.12</v>
+        <v>-18.48</v>
       </c>
       <c r="K19" t="n">
-        <v>-120.1</v>
+        <v>-78.95</v>
       </c>
       <c r="L19" t="n">
-        <v>123.34</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-181.49</v>
+        <v>-104.13</v>
       </c>
       <c r="K20" t="n">
-        <v>3.73</v>
+        <v>2.14</v>
       </c>
       <c r="L20" t="n">
-        <v>181.53</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>71.87</v>
+        <v>41.33</v>
       </c>
       <c r="K21" t="n">
-        <v>-123.9</v>
+        <v>-71.26000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>143.23</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-106.47</v>
+        <v>-77.27</v>
       </c>
       <c r="K22" t="n">
-        <v>17.56</v>
+        <v>12.74</v>
       </c>
       <c r="L22" t="n">
-        <v>107.91</v>
+        <v>78.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>265.68</v>
+        <v>156.91</v>
       </c>
       <c r="K23" t="n">
-        <v>255.27</v>
+        <v>150.76</v>
       </c>
       <c r="L23" t="n">
-        <v>368.44</v>
+        <v>217.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.34</v>
+        <v>-62.73</v>
       </c>
       <c r="K24" t="n">
-        <v>-259.11</v>
+        <v>-165.29</v>
       </c>
       <c r="L24" t="n">
-        <v>277.15</v>
+        <v>176.79</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>193.01</v>
+        <v>108.86</v>
       </c>
       <c r="K25" t="n">
-        <v>39.18</v>
+        <v>22.1</v>
       </c>
       <c r="L25" t="n">
-        <v>196.95</v>
+        <v>111.08</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-77.28</v>
+        <v>-47.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-381.97</v>
+        <v>-234.57</v>
       </c>
       <c r="L26" t="n">
-        <v>389.71</v>
+        <v>239.32</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-298.47</v>
+        <v>-190.01</v>
       </c>
       <c r="K27" t="n">
-        <v>-24</v>
+        <v>-15.28</v>
       </c>
       <c r="L27" t="n">
-        <v>299.44</v>
+        <v>190.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>78.70999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="K28" t="n">
-        <v>-231.47</v>
+        <v>-154.98</v>
       </c>
       <c r="L28" t="n">
-        <v>244.49</v>
+        <v>163.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>64.87</v>
+        <v>40.51</v>
       </c>
       <c r="K29" t="n">
-        <v>73.95999999999999</v>
+        <v>46.18</v>
       </c>
       <c r="L29" t="n">
-        <v>98.38</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.76</v>
+        <v>-8.69</v>
       </c>
       <c r="K30" t="n">
-        <v>42.48</v>
+        <v>12.41</v>
       </c>
       <c r="L30" t="n">
-        <v>51.86</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.67</v>
+        <v>-7.05</v>
       </c>
       <c r="K31" t="n">
-        <v>143.22</v>
+        <v>86.45</v>
       </c>
       <c r="L31" t="n">
-        <v>143.7</v>
+        <v>86.73999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>17.27</v>
+        <v>10.5</v>
       </c>
       <c r="K32" t="n">
-        <v>96.34</v>
+        <v>58.56</v>
       </c>
       <c r="L32" t="n">
-        <v>97.88</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-141.34</v>
+        <v>-81.12</v>
       </c>
       <c r="K33" t="n">
-        <v>66.93000000000001</v>
+        <v>38.41</v>
       </c>
       <c r="L33" t="n">
-        <v>156.39</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.19</v>
+        <v>-7.28</v>
       </c>
       <c r="K34" t="n">
-        <v>-57.06</v>
+        <v>-37.13</v>
       </c>
       <c r="L34" t="n">
-        <v>58.15</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-96.48999999999999</v>
+        <v>-60.57</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.59</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>97.44</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-89.09999999999999</v>
+        <v>-24.23</v>
       </c>
       <c r="K36" t="n">
-        <v>12.43</v>
+        <v>3.38</v>
       </c>
       <c r="L36" t="n">
-        <v>89.97</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-105.4</v>
+        <v>-64.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.14</v>
+        <v>-3.13</v>
       </c>
       <c r="L37" t="n">
-        <v>105.53</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-154.97</v>
+        <v>-102.95</v>
       </c>
       <c r="K38" t="n">
-        <v>-37</v>
+        <v>-24.58</v>
       </c>
       <c r="L38" t="n">
-        <v>159.32</v>
+        <v>105.84</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>60.6</v>
+        <v>36.1</v>
       </c>
       <c r="K39" t="n">
-        <v>-138.95</v>
+        <v>-82.77</v>
       </c>
       <c r="L39" t="n">
-        <v>151.59</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-172.72</v>
+        <v>-109.79</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="L40" t="n">
-        <v>172.72</v>
+        <v>109.79</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.92</v>
+        <v>-7.01</v>
       </c>
       <c r="K41" t="n">
-        <v>218.27</v>
+        <v>140.04</v>
       </c>
       <c r="L41" t="n">
-        <v>218.54</v>
+        <v>140.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>202.19</v>
+        <v>121.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-126.81</v>
+        <v>-76.34</v>
       </c>
       <c r="L42" t="n">
-        <v>238.66</v>
+        <v>143.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-319.26</v>
+        <v>-203.24</v>
       </c>
       <c r="K43" t="n">
-        <v>147.65</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>351.74</v>
+        <v>223.92</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.89</v>
+        <v>-6.77</v>
       </c>
       <c r="K44" t="n">
-        <v>122.01</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>122.5</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-32.29</v>
+        <v>-18.62</v>
       </c>
       <c r="K45" t="n">
-        <v>60.64</v>
+        <v>34.96</v>
       </c>
       <c r="L45" t="n">
-        <v>68.7</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>88.12</v>
+        <v>51.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-21.56</v>
+        <v>-12.63</v>
       </c>
       <c r="L46" t="n">
-        <v>90.72</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-83.06999999999999</v>
+        <v>-46.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.7</v>
+        <v>-29.52</v>
       </c>
       <c r="L47" t="n">
-        <v>98.38</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>56.68</v>
+        <v>31.86</v>
       </c>
       <c r="K48" t="n">
-        <v>89.83</v>
+        <v>50.5</v>
       </c>
       <c r="L48" t="n">
-        <v>106.22</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-38.02</v>
+        <v>-21.65</v>
       </c>
       <c r="K49" t="n">
-        <v>94.06</v>
+        <v>53.57</v>
       </c>
       <c r="L49" t="n">
-        <v>101.45</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-68.56999999999999</v>
+        <v>-37.04</v>
       </c>
       <c r="K50" t="n">
-        <v>-190.46</v>
+        <v>-102.87</v>
       </c>
       <c r="L50" t="n">
-        <v>202.43</v>
+        <v>109.34</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>165.58</v>
+        <v>93.25</v>
       </c>
       <c r="K51" t="n">
-        <v>16.31</v>
+        <v>9.19</v>
       </c>
       <c r="L51" t="n">
-        <v>166.39</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>124.25</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-140.68</v>
+        <v>-78.33</v>
       </c>
       <c r="L52" t="n">
-        <v>187.69</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>173.43</v>
+        <v>103.16</v>
       </c>
       <c r="K53" t="n">
-        <v>47.51</v>
+        <v>28.26</v>
       </c>
       <c r="L53" t="n">
-        <v>179.82</v>
+        <v>106.96</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-82.15000000000001</v>
+        <v>-52.68</v>
       </c>
       <c r="K54" t="n">
-        <v>238</v>
+        <v>152.62</v>
       </c>
       <c r="L54" t="n">
-        <v>251.78</v>
+        <v>161.46</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-102.22</v>
+        <v>-68.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-210.26</v>
+        <v>-140.23</v>
       </c>
       <c r="L55" t="n">
-        <v>233.79</v>
+        <v>155.92</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>161.84</v>
+        <v>109.5</v>
       </c>
       <c r="K56" t="n">
-        <v>292.32</v>
+        <v>197.79</v>
       </c>
       <c r="L56" t="n">
-        <v>334.13</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-40.93</v>
+        <v>-27.94</v>
       </c>
       <c r="K57" t="n">
-        <v>291.33</v>
+        <v>198.82</v>
       </c>
       <c r="L57" t="n">
-        <v>294.2</v>
+        <v>200.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>164.5</v>
+        <v>101.96</v>
       </c>
       <c r="K58" t="n">
-        <v>102.59</v>
+        <v>63.59</v>
       </c>
       <c r="L58" t="n">
-        <v>193.87</v>
+        <v>120.17</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-41.8</v>
+        <v>-25.81</v>
       </c>
       <c r="K59" t="n">
-        <v>-59.51</v>
+        <v>-36.75</v>
       </c>
       <c r="L59" t="n">
-        <v>72.72</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>40.7</v>
+        <v>26.08</v>
       </c>
       <c r="K60" t="n">
-        <v>-51.91</v>
+        <v>-33.26</v>
       </c>
       <c r="L60" t="n">
-        <v>65.97</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-89.48</v>
+        <v>-51.34</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.44</v>
+        <v>-12.3</v>
       </c>
       <c r="L61" t="n">
-        <v>92.02</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>33.72</v>
+        <v>21.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-62.61</v>
+        <v>-39.94</v>
       </c>
       <c r="L62" t="n">
-        <v>71.11</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-181.39</v>
+        <v>-105.95</v>
       </c>
       <c r="K63" t="n">
-        <v>138</v>
+        <v>80.61</v>
       </c>
       <c r="L63" t="n">
-        <v>227.92</v>
+        <v>133.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>12.42</v>
+        <v>6.5</v>
       </c>
       <c r="K64" t="n">
-        <v>105.53</v>
+        <v>55.19</v>
       </c>
       <c r="L64" t="n">
-        <v>106.26</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-156.34</v>
+        <v>-83.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-107.44</v>
+        <v>-57.07</v>
       </c>
       <c r="L65" t="n">
-        <v>189.7</v>
+        <v>100.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-107.94</v>
+        <v>-64.92</v>
       </c>
       <c r="K66" t="n">
-        <v>104.01</v>
+        <v>62.55</v>
       </c>
       <c r="L66" t="n">
-        <v>149.9</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-84.69</v>
+        <v>-48.48</v>
       </c>
       <c r="K67" t="n">
-        <v>-60.39</v>
+        <v>-34.57</v>
       </c>
       <c r="L67" t="n">
-        <v>104.02</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-100.93</v>
+        <v>-63.51</v>
       </c>
       <c r="K68" t="n">
-        <v>189.26</v>
+        <v>119.08</v>
       </c>
       <c r="L68" t="n">
-        <v>214.5</v>
+        <v>134.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>52.15</v>
+        <v>31.53</v>
       </c>
       <c r="K69" t="n">
-        <v>149.73</v>
+        <v>90.52</v>
       </c>
       <c r="L69" t="n">
-        <v>158.55</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-133.84</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>211.06</v>
+        <v>124.3</v>
       </c>
       <c r="L70" t="n">
-        <v>249.92</v>
+        <v>147.18</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>218.89</v>
+        <v>131.76</v>
       </c>
       <c r="K71" t="n">
-        <v>316.76</v>
+        <v>190.68</v>
       </c>
       <c r="L71" t="n">
-        <v>385.03</v>
+        <v>231.78</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-205.76</v>
+        <v>-127.53</v>
       </c>
       <c r="K72" t="n">
-        <v>-92.31</v>
+        <v>-57.22</v>
       </c>
       <c r="L72" t="n">
-        <v>225.51</v>
+        <v>139.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>155.31</v>
+        <v>95.2</v>
       </c>
       <c r="K73" t="n">
-        <v>224.35</v>
+        <v>137.53</v>
       </c>
       <c r="L73" t="n">
-        <v>272.87</v>
+        <v>167.26</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>43.11</v>
+        <v>24.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-71.91</v>
+        <v>-41.33</v>
       </c>
       <c r="L74" t="n">
-        <v>83.84</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>90.34999999999999</v>
+        <v>56.55</v>
       </c>
       <c r="K75" t="n">
-        <v>25.53</v>
+        <v>15.97</v>
       </c>
       <c r="L75" t="n">
-        <v>93.89</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.45</v>
+        <v>-39.83</v>
       </c>
       <c r="K76" t="n">
-        <v>72.53</v>
+        <v>44.14</v>
       </c>
       <c r="L76" t="n">
-        <v>97.69</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-48.4</v>
+        <v>-28.56</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.64</v>
+        <v>-44.04</v>
       </c>
       <c r="L77" t="n">
-        <v>88.95999999999999</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>96.78</v>
+        <v>55.33</v>
       </c>
       <c r="K78" t="n">
-        <v>72.56</v>
+        <v>41.48</v>
       </c>
       <c r="L78" t="n">
-        <v>120.96</v>
+        <v>69.16</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-87.83</v>
+        <v>-53.62</v>
       </c>
       <c r="K79" t="n">
-        <v>86.23</v>
+        <v>52.64</v>
       </c>
       <c r="L79" t="n">
-        <v>123.08</v>
+        <v>75.14</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>84.55</v>
+        <v>48.62</v>
       </c>
       <c r="K80" t="n">
-        <v>-258.8</v>
+        <v>-148.84</v>
       </c>
       <c r="L80" t="n">
-        <v>272.26</v>
+        <v>156.58</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-97.2</v>
+        <v>-55.9</v>
       </c>
       <c r="K81" t="n">
-        <v>40.48</v>
+        <v>23.28</v>
       </c>
       <c r="L81" t="n">
-        <v>105.29</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>76.15000000000001</v>
+        <v>46.4</v>
       </c>
       <c r="K82" t="n">
-        <v>116.01</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>138.77</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.83</v>
+        <v>-3</v>
       </c>
       <c r="K83" t="n">
-        <v>-245.53</v>
+        <v>-152.7</v>
       </c>
       <c r="L83" t="n">
-        <v>245.58</v>
+        <v>152.73</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-75.81</v>
+        <v>-45.22</v>
       </c>
       <c r="K84" t="n">
-        <v>143.78</v>
+        <v>85.77</v>
       </c>
       <c r="L84" t="n">
-        <v>162.54</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>151.38</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>251.32</v>
+        <v>149.49</v>
       </c>
       <c r="L85" t="n">
-        <v>293.38</v>
+        <v>174.51</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>108.89</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>215.38</v>
+        <v>126.95</v>
       </c>
       <c r="L86" t="n">
-        <v>241.34</v>
+        <v>142.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>167.7</v>
+        <v>106.76</v>
       </c>
       <c r="K87" t="n">
-        <v>-290.41</v>
+        <v>-184.87</v>
       </c>
       <c r="L87" t="n">
-        <v>335.35</v>
+        <v>213.48</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-395.89</v>
+        <v>-223.43</v>
       </c>
       <c r="K88" t="n">
-        <v>-44.06</v>
+        <v>-24.86</v>
       </c>
       <c r="L88" t="n">
-        <v>398.34</v>
+        <v>224.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>35.93</v>
+        <v>35.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-59.44</v>
+        <v>-58.19</v>
       </c>
       <c r="L14" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>43.15</v>
+        <v>44.27</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.58</v>
+        <v>-9.83</v>
       </c>
       <c r="L15" t="n">
-        <v>44.21</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.62</v>
+        <v>-55.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="L16" t="n">
-        <v>56.34</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-76.12</v>
+        <v>-74.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.77</v>
+        <v>-32.02</v>
       </c>
       <c r="L17" t="n">
-        <v>82.87</v>
+        <v>80.97</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-79</v>
+        <v>-76.68000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-49.58</v>
+        <v>-48.13</v>
       </c>
       <c r="L18" t="n">
-        <v>93.27</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.48</v>
+        <v>-18.13</v>
       </c>
       <c r="K19" t="n">
-        <v>-78.95</v>
+        <v>-77.44</v>
       </c>
       <c r="L19" t="n">
-        <v>81.08</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-104.13</v>
+        <v>-104.22</v>
       </c>
       <c r="K20" t="n">
         <v>2.14</v>
       </c>
       <c r="L20" t="n">
-        <v>104.15</v>
+        <v>104.24</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>41.33</v>
+        <v>42.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.26000000000001</v>
+        <v>-72.95</v>
       </c>
       <c r="L21" t="n">
-        <v>82.38</v>
+        <v>84.34</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-77.27</v>
+        <v>-78.25</v>
       </c>
       <c r="K22" t="n">
-        <v>12.74</v>
+        <v>12.91</v>
       </c>
       <c r="L22" t="n">
-        <v>78.31</v>
+        <v>79.31</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>156.91</v>
+        <v>150.92</v>
       </c>
       <c r="K23" t="n">
-        <v>150.76</v>
+        <v>145.01</v>
       </c>
       <c r="L23" t="n">
-        <v>217.6</v>
+        <v>209.29</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-62.73</v>
+        <v>-61.12</v>
       </c>
       <c r="K24" t="n">
-        <v>-165.29</v>
+        <v>-161.04</v>
       </c>
       <c r="L24" t="n">
-        <v>176.79</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>108.86</v>
+        <v>113.67</v>
       </c>
       <c r="K25" t="n">
-        <v>22.1</v>
+        <v>23.07</v>
       </c>
       <c r="L25" t="n">
-        <v>111.08</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-47.46</v>
+        <v>-46.48</v>
       </c>
       <c r="K26" t="n">
-        <v>-234.57</v>
+        <v>-229.73</v>
       </c>
       <c r="L26" t="n">
-        <v>239.32</v>
+        <v>234.38</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-190.01</v>
+        <v>-190.61</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.28</v>
+        <v>-15.33</v>
       </c>
       <c r="L27" t="n">
-        <v>190.62</v>
+        <v>191.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>52.7</v>
+        <v>53.55</v>
       </c>
       <c r="K28" t="n">
-        <v>-154.98</v>
+        <v>-157.49</v>
       </c>
       <c r="L28" t="n">
-        <v>163.69</v>
+        <v>166.34</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>40.51</v>
+        <v>39.45</v>
       </c>
       <c r="K29" t="n">
-        <v>46.18</v>
+        <v>44.98</v>
       </c>
       <c r="L29" t="n">
-        <v>61.43</v>
+        <v>59.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.69</v>
+        <v>-8.51</v>
       </c>
       <c r="K30" t="n">
-        <v>12.41</v>
+        <v>12.15</v>
       </c>
       <c r="L30" t="n">
-        <v>15.15</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.05</v>
+        <v>-6.71</v>
       </c>
       <c r="K31" t="n">
-        <v>86.45</v>
+        <v>82.36</v>
       </c>
       <c r="L31" t="n">
-        <v>86.73999999999999</v>
+        <v>82.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>10.5</v>
+        <v>10.61</v>
       </c>
       <c r="K32" t="n">
-        <v>58.56</v>
+        <v>59.21</v>
       </c>
       <c r="L32" t="n">
-        <v>59.49</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.12</v>
+        <v>-78.68000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>38.41</v>
+        <v>37.26</v>
       </c>
       <c r="L33" t="n">
-        <v>89.75</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.28</v>
+        <v>-7.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-37.13</v>
+        <v>-39.8</v>
       </c>
       <c r="L34" t="n">
-        <v>37.84</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-60.57</v>
+        <v>-64</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.529999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="L35" t="n">
-        <v>61.17</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-24.23</v>
+        <v>-23.73</v>
       </c>
       <c r="K36" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="L36" t="n">
-        <v>24.46</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-64.22</v>
+        <v>-67.23</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.13</v>
+        <v>-3.28</v>
       </c>
       <c r="L37" t="n">
-        <v>64.3</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-102.95</v>
+        <v>-105.31</v>
       </c>
       <c r="K38" t="n">
-        <v>-24.58</v>
+        <v>-25.14</v>
       </c>
       <c r="L38" t="n">
-        <v>105.84</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>36.1</v>
+        <v>38.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-82.77</v>
+        <v>-88.14</v>
       </c>
       <c r="L39" t="n">
-        <v>90.3</v>
+        <v>96.16</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-109.79</v>
+        <v>-111.34</v>
       </c>
       <c r="K40" t="n">
         <v>-0.31</v>
       </c>
       <c r="L40" t="n">
-        <v>109.79</v>
+        <v>111.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.01</v>
+        <v>-7.2</v>
       </c>
       <c r="K41" t="n">
-        <v>140.04</v>
+        <v>143.93</v>
       </c>
       <c r="L41" t="n">
-        <v>140.21</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>121.71</v>
+        <v>126.3</v>
       </c>
       <c r="K42" t="n">
-        <v>-76.34</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>143.67</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-203.24</v>
+        <v>-199.42</v>
       </c>
       <c r="K43" t="n">
-        <v>93.98999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="L43" t="n">
-        <v>223.92</v>
+        <v>219.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.77</v>
+        <v>-6.56</v>
       </c>
       <c r="K44" t="n">
-        <v>75.84999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="L44" t="n">
-        <v>76.15000000000001</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-18.62</v>
+        <v>-19.56</v>
       </c>
       <c r="K45" t="n">
-        <v>34.96</v>
+        <v>36.73</v>
       </c>
       <c r="L45" t="n">
-        <v>39.61</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>51.61</v>
+        <v>51.94</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.63</v>
+        <v>-12.71</v>
       </c>
       <c r="L46" t="n">
-        <v>53.13</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-46.53</v>
+        <v>-48.3</v>
       </c>
       <c r="K47" t="n">
-        <v>-29.52</v>
+        <v>-30.64</v>
       </c>
       <c r="L47" t="n">
-        <v>55.1</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>31.86</v>
+        <v>32.39</v>
       </c>
       <c r="K48" t="n">
-        <v>50.5</v>
+        <v>51.33</v>
       </c>
       <c r="L48" t="n">
-        <v>59.71</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-21.65</v>
+        <v>-22.48</v>
       </c>
       <c r="K49" t="n">
-        <v>53.57</v>
+        <v>55.62</v>
       </c>
       <c r="L49" t="n">
-        <v>57.78</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-37.04</v>
+        <v>-36.64</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.87</v>
+        <v>-101.75</v>
       </c>
       <c r="L50" t="n">
-        <v>109.34</v>
+        <v>108.15</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>93.25</v>
+        <v>93.52</v>
       </c>
       <c r="K51" t="n">
-        <v>9.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>93.7</v>
+        <v>93.98</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>69.18000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-78.33</v>
+        <v>-77.22</v>
       </c>
       <c r="L52" t="n">
-        <v>104.51</v>
+        <v>103.03</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>103.16</v>
+        <v>106.71</v>
       </c>
       <c r="K53" t="n">
-        <v>28.26</v>
+        <v>29.23</v>
       </c>
       <c r="L53" t="n">
-        <v>106.96</v>
+        <v>110.64</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-52.68</v>
+        <v>-51.53</v>
       </c>
       <c r="K54" t="n">
-        <v>152.62</v>
+        <v>149.28</v>
       </c>
       <c r="L54" t="n">
-        <v>161.46</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-68.17</v>
+        <v>-66.06</v>
       </c>
       <c r="K55" t="n">
-        <v>-140.23</v>
+        <v>-135.9</v>
       </c>
       <c r="L55" t="n">
-        <v>155.92</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>109.5</v>
+        <v>106.4</v>
       </c>
       <c r="K56" t="n">
-        <v>197.79</v>
+        <v>192.19</v>
       </c>
       <c r="L56" t="n">
-        <v>226.08</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-27.94</v>
+        <v>-27.42</v>
       </c>
       <c r="K57" t="n">
-        <v>198.82</v>
+        <v>195.14</v>
       </c>
       <c r="L57" t="n">
-        <v>200.77</v>
+        <v>197.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>101.96</v>
+        <v>107.32</v>
       </c>
       <c r="K58" t="n">
-        <v>63.59</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>120.17</v>
+        <v>126.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.81</v>
+        <v>-26.6</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.75</v>
+        <v>-37.88</v>
       </c>
       <c r="L59" t="n">
-        <v>44.91</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>26.08</v>
+        <v>26.74</v>
       </c>
       <c r="K60" t="n">
-        <v>-33.26</v>
+        <v>-34.1</v>
       </c>
       <c r="L60" t="n">
-        <v>42.27</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-51.34</v>
+        <v>-51.76</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.3</v>
+        <v>-12.4</v>
       </c>
       <c r="L61" t="n">
-        <v>52.79</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>21.51</v>
+        <v>22.66</v>
       </c>
       <c r="K62" t="n">
-        <v>-39.94</v>
+        <v>-42.07</v>
       </c>
       <c r="L62" t="n">
-        <v>45.36</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-105.95</v>
+        <v>-100.23</v>
       </c>
       <c r="K63" t="n">
-        <v>80.61</v>
+        <v>76.25</v>
       </c>
       <c r="L63" t="n">
-        <v>133.13</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>6.5</v>
+        <v>6.78</v>
       </c>
       <c r="K64" t="n">
-        <v>55.19</v>
+        <v>57.55</v>
       </c>
       <c r="L64" t="n">
-        <v>55.57</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-83.05</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-57.07</v>
+        <v>-57.74</v>
       </c>
       <c r="L65" t="n">
-        <v>100.77</v>
+        <v>101.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-64.92</v>
+        <v>-65.25</v>
       </c>
       <c r="K66" t="n">
-        <v>62.55</v>
+        <v>62.88</v>
       </c>
       <c r="L66" t="n">
-        <v>90.15000000000001</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-48.48</v>
+        <v>-52.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-34.57</v>
+        <v>-37.47</v>
       </c>
       <c r="L67" t="n">
-        <v>59.54</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.51</v>
+        <v>-63.53</v>
       </c>
       <c r="K68" t="n">
-        <v>119.08</v>
+        <v>119.13</v>
       </c>
       <c r="L68" t="n">
-        <v>134.96</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>31.53</v>
+        <v>33.13</v>
       </c>
       <c r="K69" t="n">
-        <v>90.52</v>
+        <v>95.12</v>
       </c>
       <c r="L69" t="n">
-        <v>95.86</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-78.81999999999999</v>
+        <v>-79.04000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>124.3</v>
+        <v>124.64</v>
       </c>
       <c r="L70" t="n">
-        <v>147.18</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>131.76</v>
+        <v>128.81</v>
       </c>
       <c r="K71" t="n">
-        <v>190.68</v>
+        <v>186.41</v>
       </c>
       <c r="L71" t="n">
-        <v>231.78</v>
+        <v>226.58</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-127.53</v>
+        <v>-132.97</v>
       </c>
       <c r="K72" t="n">
-        <v>-57.22</v>
+        <v>-59.66</v>
       </c>
       <c r="L72" t="n">
-        <v>139.78</v>
+        <v>145.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>95.2</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>137.53</v>
+        <v>140.17</v>
       </c>
       <c r="L73" t="n">
-        <v>167.26</v>
+        <v>170.48</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>24.77</v>
+        <v>25.28</v>
       </c>
       <c r="K74" t="n">
-        <v>-41.33</v>
+        <v>-42.18</v>
       </c>
       <c r="L74" t="n">
-        <v>48.18</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>56.55</v>
+        <v>56.16</v>
       </c>
       <c r="K75" t="n">
-        <v>15.97</v>
+        <v>15.86</v>
       </c>
       <c r="L75" t="n">
-        <v>58.76</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.83</v>
+        <v>-39.3</v>
       </c>
       <c r="K76" t="n">
-        <v>44.14</v>
+        <v>43.55</v>
       </c>
       <c r="L76" t="n">
-        <v>59.45</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-28.56</v>
+        <v>-29.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.04</v>
+        <v>-45.49</v>
       </c>
       <c r="L77" t="n">
-        <v>52.49</v>
+        <v>54.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>55.33</v>
+        <v>55.34</v>
       </c>
       <c r="K78" t="n">
-        <v>41.48</v>
+        <v>41.49</v>
       </c>
       <c r="L78" t="n">
-        <v>69.16</v>
+        <v>69.17</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.62</v>
+        <v>-53.38</v>
       </c>
       <c r="K79" t="n">
-        <v>52.64</v>
+        <v>52.41</v>
       </c>
       <c r="L79" t="n">
-        <v>75.14</v>
+        <v>74.81</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>48.62</v>
+        <v>46.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-148.84</v>
+        <v>-142.49</v>
       </c>
       <c r="L80" t="n">
-        <v>156.58</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.9</v>
+        <v>-59.73</v>
       </c>
       <c r="K81" t="n">
-        <v>23.28</v>
+        <v>24.88</v>
       </c>
       <c r="L81" t="n">
-        <v>60.56</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>46.4</v>
+        <v>47.26</v>
       </c>
       <c r="K82" t="n">
-        <v>70.68000000000001</v>
+        <v>72</v>
       </c>
       <c r="L82" t="n">
-        <v>84.55</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-3</v>
+        <v>-2.94</v>
       </c>
       <c r="K83" t="n">
-        <v>-152.7</v>
+        <v>-149.35</v>
       </c>
       <c r="L83" t="n">
-        <v>152.73</v>
+        <v>149.38</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.22</v>
+        <v>-47.84</v>
       </c>
       <c r="K84" t="n">
-        <v>85.77</v>
+        <v>90.73</v>
       </c>
       <c r="L84" t="n">
-        <v>96.97</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>90.04000000000001</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>149.49</v>
+        <v>146.46</v>
       </c>
       <c r="L85" t="n">
-        <v>174.51</v>
+        <v>170.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>64.18000000000001</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>126.95</v>
+        <v>130.97</v>
       </c>
       <c r="L86" t="n">
-        <v>142.25</v>
+        <v>146.76</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>106.76</v>
+        <v>104.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-184.87</v>
+        <v>-181.52</v>
       </c>
       <c r="L87" t="n">
-        <v>213.48</v>
+        <v>209.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-223.43</v>
+        <v>-220.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.86</v>
+        <v>-24.54</v>
       </c>
       <c r="L88" t="n">
-        <v>224.8</v>
+        <v>221.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>35.18</v>
+        <v>34.32</v>
       </c>
       <c r="K14" t="n">
-        <v>-58.19</v>
+        <v>-56.77</v>
       </c>
       <c r="L14" t="n">
-        <v>68</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>44.27</v>
+        <v>45.56</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.83</v>
+        <v>-10.12</v>
       </c>
       <c r="L15" t="n">
-        <v>45.35</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.8</v>
+        <v>-55.99</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.99</v>
+        <v>-9.02</v>
       </c>
       <c r="L16" t="n">
-        <v>56.52</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.37</v>
+        <v>-72.38</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.02</v>
+        <v>-31.16</v>
       </c>
       <c r="L17" t="n">
-        <v>80.97</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.68000000000001</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-48.13</v>
+        <v>-46.47</v>
       </c>
       <c r="L18" t="n">
-        <v>90.54000000000001</v>
+        <v>87.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.13</v>
+        <v>-17.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-77.44</v>
+        <v>-75.72</v>
       </c>
       <c r="L19" t="n">
-        <v>79.53</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-104.22</v>
+        <v>-104.32</v>
       </c>
       <c r="K20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="L20" t="n">
-        <v>104.24</v>
+        <v>104.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>42.32</v>
+        <v>43.44</v>
       </c>
       <c r="K21" t="n">
-        <v>-72.95</v>
+        <v>-74.89</v>
       </c>
       <c r="L21" t="n">
-        <v>84.34</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-78.25</v>
+        <v>-79.38</v>
       </c>
       <c r="K22" t="n">
-        <v>12.91</v>
+        <v>13.09</v>
       </c>
       <c r="L22" t="n">
-        <v>79.31</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>150.92</v>
+        <v>144.08</v>
       </c>
       <c r="K23" t="n">
-        <v>145.01</v>
+        <v>138.43</v>
       </c>
       <c r="L23" t="n">
-        <v>209.29</v>
+        <v>199.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-61.12</v>
+        <v>-59.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-161.04</v>
+        <v>-156.19</v>
       </c>
       <c r="L24" t="n">
-        <v>172.25</v>
+        <v>167.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>113.67</v>
+        <v>119.07</v>
       </c>
       <c r="K25" t="n">
-        <v>23.07</v>
+        <v>24.17</v>
       </c>
       <c r="L25" t="n">
-        <v>115.99</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-46.48</v>
+        <v>-45.36</v>
       </c>
       <c r="K26" t="n">
-        <v>-229.73</v>
+        <v>-224.19</v>
       </c>
       <c r="L26" t="n">
-        <v>234.38</v>
+        <v>228.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-190.61</v>
+        <v>-191.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.33</v>
+        <v>-15.39</v>
       </c>
       <c r="L27" t="n">
-        <v>191.23</v>
+        <v>191.92</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>53.55</v>
+        <v>54.53</v>
       </c>
       <c r="K28" t="n">
-        <v>-157.49</v>
+        <v>-160.36</v>
       </c>
       <c r="L28" t="n">
-        <v>166.34</v>
+        <v>169.37</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>39.45</v>
+        <v>38.25</v>
       </c>
       <c r="K29" t="n">
-        <v>44.98</v>
+        <v>43.61</v>
       </c>
       <c r="L29" t="n">
-        <v>59.83</v>
+        <v>58.01</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.51</v>
+        <v>-9.23</v>
       </c>
       <c r="K30" t="n">
-        <v>12.15</v>
+        <v>13.17</v>
       </c>
       <c r="L30" t="n">
-        <v>14.83</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.71</v>
+        <v>-6.33</v>
       </c>
       <c r="K31" t="n">
-        <v>82.36</v>
+        <v>77.67</v>
       </c>
       <c r="L31" t="n">
-        <v>82.63</v>
+        <v>77.93000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>10.61</v>
+        <v>10.75</v>
       </c>
       <c r="K32" t="n">
-        <v>59.21</v>
+        <v>59.96</v>
       </c>
       <c r="L32" t="n">
-        <v>60.16</v>
+        <v>60.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.68000000000001</v>
+        <v>-75.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>37.26</v>
+        <v>35.94</v>
       </c>
       <c r="L33" t="n">
-        <v>87.06</v>
+        <v>83.98</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.8</v>
+        <v>-8.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-39.8</v>
+        <v>-42.85</v>
       </c>
       <c r="L34" t="n">
-        <v>40.55</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-64</v>
+        <v>-67.93000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.01</v>
+        <v>-9.57</v>
       </c>
       <c r="L35" t="n">
-        <v>64.64</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.73</v>
+        <v>-25.68</v>
       </c>
       <c r="K36" t="n">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="L36" t="n">
-        <v>23.96</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-67.23</v>
+        <v>-70.67</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.28</v>
+        <v>-3.45</v>
       </c>
       <c r="L37" t="n">
-        <v>67.31</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-105.31</v>
+        <v>-108</v>
       </c>
       <c r="K38" t="n">
-        <v>-25.14</v>
+        <v>-25.78</v>
       </c>
       <c r="L38" t="n">
-        <v>108.27</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>38.44</v>
+        <v>41.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-88.14</v>
+        <v>-94.28</v>
       </c>
       <c r="L39" t="n">
-        <v>96.16</v>
+        <v>102.86</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-111.34</v>
+        <v>-113.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="L40" t="n">
-        <v>111.34</v>
+        <v>113.11</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.2</v>
+        <v>-7.42</v>
       </c>
       <c r="K41" t="n">
-        <v>143.93</v>
+        <v>148.39</v>
       </c>
       <c r="L41" t="n">
-        <v>144.12</v>
+        <v>148.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>126.3</v>
+        <v>131.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-79.20999999999999</v>
+        <v>-82.5</v>
       </c>
       <c r="L42" t="n">
-        <v>149.08</v>
+        <v>155.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-199.42</v>
+        <v>-195.06</v>
       </c>
       <c r="K43" t="n">
-        <v>92.22</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>219.71</v>
+        <v>214.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.56</v>
+        <v>-6.31</v>
       </c>
       <c r="K44" t="n">
-        <v>73.45</v>
+        <v>70.7</v>
       </c>
       <c r="L44" t="n">
-        <v>73.73999999999999</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-19.56</v>
+        <v>-20.63</v>
       </c>
       <c r="K45" t="n">
-        <v>36.73</v>
+        <v>38.75</v>
       </c>
       <c r="L45" t="n">
-        <v>41.61</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>51.94</v>
+        <v>52.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.71</v>
+        <v>-12.8</v>
       </c>
       <c r="L46" t="n">
-        <v>53.47</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-48.3</v>
+        <v>-50.33</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.64</v>
+        <v>-31.93</v>
       </c>
       <c r="L47" t="n">
-        <v>57.2</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>32.39</v>
+        <v>32.99</v>
       </c>
       <c r="K48" t="n">
-        <v>51.33</v>
+        <v>52.28</v>
       </c>
       <c r="L48" t="n">
-        <v>60.69</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-22.48</v>
+        <v>-23.43</v>
       </c>
       <c r="K49" t="n">
-        <v>55.62</v>
+        <v>57.96</v>
       </c>
       <c r="L49" t="n">
-        <v>59.99</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-36.64</v>
+        <v>-36.18</v>
       </c>
       <c r="K50" t="n">
-        <v>-101.75</v>
+        <v>-100.47</v>
       </c>
       <c r="L50" t="n">
-        <v>108.15</v>
+        <v>106.79</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>93.52</v>
+        <v>93.83</v>
       </c>
       <c r="K51" t="n">
-        <v>9.210000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="L51" t="n">
-        <v>93.98</v>
+        <v>94.29000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>68.2</v>
+        <v>67.08</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.22</v>
+        <v>-75.95</v>
       </c>
       <c r="L52" t="n">
-        <v>103.03</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>106.71</v>
+        <v>110.76</v>
       </c>
       <c r="K53" t="n">
-        <v>29.23</v>
+        <v>30.34</v>
       </c>
       <c r="L53" t="n">
-        <v>110.64</v>
+        <v>114.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.53</v>
+        <v>-50.21</v>
       </c>
       <c r="K54" t="n">
-        <v>149.28</v>
+        <v>145.46</v>
       </c>
       <c r="L54" t="n">
-        <v>157.92</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-66.06</v>
+        <v>-63.66</v>
       </c>
       <c r="K55" t="n">
-        <v>-135.9</v>
+        <v>-130.94</v>
       </c>
       <c r="L55" t="n">
-        <v>151.1</v>
+        <v>145.59</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>106.4</v>
+        <v>102.86</v>
       </c>
       <c r="K56" t="n">
-        <v>192.19</v>
+        <v>185.79</v>
       </c>
       <c r="L56" t="n">
-        <v>219.68</v>
+        <v>212.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-27.42</v>
+        <v>-26.83</v>
       </c>
       <c r="K57" t="n">
-        <v>195.14</v>
+        <v>190.93</v>
       </c>
       <c r="L57" t="n">
-        <v>197.05</v>
+        <v>192.81</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>107.32</v>
+        <v>113.45</v>
       </c>
       <c r="K58" t="n">
-        <v>66.93000000000001</v>
+        <v>70.75</v>
       </c>
       <c r="L58" t="n">
-        <v>126.48</v>
+        <v>133.7</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.6</v>
+        <v>-27.51</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.88</v>
+        <v>-39.16</v>
       </c>
       <c r="L59" t="n">
-        <v>46.28</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>26.74</v>
+        <v>27.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-34.1</v>
+        <v>-35.06</v>
       </c>
       <c r="L60" t="n">
-        <v>43.34</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-51.76</v>
+        <v>-52.25</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.4</v>
+        <v>-12.52</v>
       </c>
       <c r="L61" t="n">
-        <v>53.23</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>22.66</v>
+        <v>23.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-42.07</v>
+        <v>-44.51</v>
       </c>
       <c r="L62" t="n">
-        <v>47.78</v>
+        <v>50.55</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-100.23</v>
+        <v>-93.69</v>
       </c>
       <c r="K63" t="n">
-        <v>76.25</v>
+        <v>71.28</v>
       </c>
       <c r="L63" t="n">
-        <v>125.94</v>
+        <v>117.72</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>6.78</v>
+        <v>7.12</v>
       </c>
       <c r="K64" t="n">
-        <v>57.55</v>
+        <v>60.51</v>
       </c>
       <c r="L64" t="n">
-        <v>57.95</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-84.01000000000001</v>
+        <v>-85.11</v>
       </c>
       <c r="K65" t="n">
-        <v>-57.74</v>
+        <v>-58.49</v>
       </c>
       <c r="L65" t="n">
-        <v>101.94</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-65.25</v>
+        <v>-65.64</v>
       </c>
       <c r="K66" t="n">
-        <v>62.88</v>
+        <v>63.25</v>
       </c>
       <c r="L66" t="n">
-        <v>90.62</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.55</v>
+        <v>-57.2</v>
       </c>
       <c r="K67" t="n">
-        <v>-37.47</v>
+        <v>-40.79</v>
       </c>
       <c r="L67" t="n">
-        <v>64.54000000000001</v>
+        <v>70.26000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.53</v>
+        <v>-63.56</v>
       </c>
       <c r="K68" t="n">
-        <v>119.13</v>
+        <v>119.19</v>
       </c>
       <c r="L68" t="n">
-        <v>135.01</v>
+        <v>135.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>33.13</v>
+        <v>34.96</v>
       </c>
       <c r="K69" t="n">
-        <v>95.12</v>
+        <v>100.37</v>
       </c>
       <c r="L69" t="n">
-        <v>100.72</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-79.04000000000001</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>124.64</v>
+        <v>125.04</v>
       </c>
       <c r="L70" t="n">
-        <v>147.59</v>
+        <v>148.06</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>128.81</v>
+        <v>125.44</v>
       </c>
       <c r="K71" t="n">
-        <v>186.41</v>
+        <v>181.52</v>
       </c>
       <c r="L71" t="n">
-        <v>226.58</v>
+        <v>220.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-132.97</v>
+        <v>-139.18</v>
       </c>
       <c r="K72" t="n">
-        <v>-59.66</v>
+        <v>-62.44</v>
       </c>
       <c r="L72" t="n">
-        <v>145.74</v>
+        <v>152.55</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>97.04000000000001</v>
+        <v>99.13</v>
       </c>
       <c r="K73" t="n">
-        <v>140.17</v>
+        <v>143.2</v>
       </c>
       <c r="L73" t="n">
-        <v>170.48</v>
+        <v>174.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>25.28</v>
+        <v>25.87</v>
       </c>
       <c r="K74" t="n">
-        <v>-42.18</v>
+        <v>-43.16</v>
       </c>
       <c r="L74" t="n">
-        <v>49.18</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>56.16</v>
+        <v>55.71</v>
       </c>
       <c r="K75" t="n">
-        <v>15.86</v>
+        <v>15.74</v>
       </c>
       <c r="L75" t="n">
-        <v>58.36</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.3</v>
+        <v>-38.69</v>
       </c>
       <c r="K76" t="n">
-        <v>43.55</v>
+        <v>42.88</v>
       </c>
       <c r="L76" t="n">
-        <v>58.66</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-29.5</v>
+        <v>-30.57</v>
       </c>
       <c r="K77" t="n">
-        <v>-45.49</v>
+        <v>-47.15</v>
       </c>
       <c r="L77" t="n">
-        <v>54.22</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>55.34</v>
+        <v>55.36</v>
       </c>
       <c r="K78" t="n">
-        <v>41.49</v>
+        <v>41.5</v>
       </c>
       <c r="L78" t="n">
-        <v>69.17</v>
+        <v>69.19</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.38</v>
+        <v>-53.11</v>
       </c>
       <c r="K79" t="n">
-        <v>52.41</v>
+        <v>52.15</v>
       </c>
       <c r="L79" t="n">
-        <v>74.81</v>
+        <v>74.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>46.55</v>
+        <v>44.18</v>
       </c>
       <c r="K80" t="n">
-        <v>-142.49</v>
+        <v>-135.23</v>
       </c>
       <c r="L80" t="n">
-        <v>149.9</v>
+        <v>142.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-59.73</v>
+        <v>-64.12</v>
       </c>
       <c r="K81" t="n">
-        <v>24.88</v>
+        <v>26.7</v>
       </c>
       <c r="L81" t="n">
-        <v>64.70999999999999</v>
+        <v>69.45</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>47.26</v>
+        <v>48.25</v>
       </c>
       <c r="K82" t="n">
-        <v>72</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>86.13</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.94</v>
+        <v>-2.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-149.35</v>
+        <v>-145.53</v>
       </c>
       <c r="L83" t="n">
-        <v>149.38</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-47.84</v>
+        <v>-50.82</v>
       </c>
       <c r="K84" t="n">
-        <v>90.73</v>
+        <v>96.39</v>
       </c>
       <c r="L84" t="n">
-        <v>102.57</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>88.20999999999999</v>
+        <v>86.13</v>
       </c>
       <c r="K85" t="n">
-        <v>146.46</v>
+        <v>142.99</v>
       </c>
       <c r="L85" t="n">
-        <v>170.97</v>
+        <v>166.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>66.20999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>130.97</v>
+        <v>135.58</v>
       </c>
       <c r="L86" t="n">
-        <v>146.76</v>
+        <v>151.92</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>104.82</v>
+        <v>102.61</v>
       </c>
       <c r="K87" t="n">
-        <v>-181.52</v>
+        <v>-177.7</v>
       </c>
       <c r="L87" t="n">
-        <v>209.62</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-220.52</v>
+        <v>-216.09</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.54</v>
+        <v>-24.05</v>
       </c>
       <c r="L88" t="n">
-        <v>221.88</v>
+        <v>217.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="F14" t="n">
-        <v>7.83</v>
+        <v>6.28</v>
       </c>
       <c r="G14" t="n">
-        <v>307.2</v>
+        <v>308.2</v>
       </c>
       <c r="H14" t="n">
-        <v>52.1</v>
+        <v>49.6</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>34.32</v>
+        <v>-14.1</v>
       </c>
       <c r="K14" t="n">
-        <v>-56.77</v>
+        <v>-70.12</v>
       </c>
       <c r="L14" t="n">
-        <v>66.33</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:32:47</t>
+          <t>04:33:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="F15" t="n">
-        <v>7.22</v>
+        <v>6.56</v>
       </c>
       <c r="G15" t="n">
-        <v>285.6</v>
+        <v>314.9</v>
       </c>
       <c r="H15" t="n">
-        <v>57.7</v>
+        <v>54</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>45.56</v>
+        <v>-69.39</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.12</v>
+        <v>-43.57</v>
       </c>
       <c r="L15" t="n">
-        <v>46.67</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:34:33</t>
+          <t>04:34:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="F16" t="n">
-        <v>7.98</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>292.5</v>
+        <v>310.5</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>56.8</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.99</v>
+        <v>84.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.02</v>
+        <v>-13.43</v>
       </c>
       <c r="L16" t="n">
-        <v>56.72</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:03</t>
+          <t>04:38:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="F17" t="n">
-        <v>7.68</v>
+        <v>2.35</v>
       </c>
       <c r="G17" t="n">
-        <v>308.2</v>
+        <v>297.4</v>
       </c>
       <c r="H17" t="n">
-        <v>49.6</v>
+        <v>53.9</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-72.38</v>
+        <v>-73.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.16</v>
+        <v>0.76</v>
       </c>
       <c r="L17" t="n">
-        <v>78.8</v>
+        <v>73.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:33</t>
+          <t>04:40:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="F18" t="n">
-        <v>8.74</v>
+        <v>5.81</v>
       </c>
       <c r="G18" t="n">
-        <v>302.6</v>
+        <v>291.7</v>
       </c>
       <c r="H18" t="n">
-        <v>54.2</v>
+        <v>46.8</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-74.04000000000001</v>
+        <v>26.12</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.47</v>
+        <v>-72.22</v>
       </c>
       <c r="L18" t="n">
-        <v>87.41</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:44</t>
+          <t>04:42:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="F19" t="n">
-        <v>8.1</v>
+        <v>2.71</v>
       </c>
       <c r="G19" t="n">
-        <v>310.5</v>
+        <v>292.2</v>
       </c>
       <c r="H19" t="n">
-        <v>56.8</v>
+        <v>54.6</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.73</v>
+        <v>4.58</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.72</v>
+        <v>99.77</v>
       </c>
       <c r="L19" t="n">
-        <v>77.76000000000001</v>
+        <v>99.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:06</t>
+          <t>04:45:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="F20" t="n">
-        <v>7.86</v>
+        <v>7.74</v>
       </c>
       <c r="G20" t="n">
-        <v>302.4</v>
+        <v>289.2</v>
       </c>
       <c r="H20" t="n">
-        <v>48.8</v>
+        <v>44.8</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-104.32</v>
+        <v>115.26</v>
       </c>
       <c r="K20" t="n">
-        <v>2.15</v>
+        <v>115.75</v>
       </c>
       <c r="L20" t="n">
-        <v>104.34</v>
+        <v>163.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:48:57</t>
+          <t>04:47:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="F21" t="n">
-        <v>8.06</v>
+        <v>4.26</v>
       </c>
       <c r="G21" t="n">
-        <v>291.7</v>
+        <v>299.3</v>
       </c>
       <c r="H21" t="n">
-        <v>46.8</v>
+        <v>59</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>43.44</v>
+        <v>-125.21</v>
       </c>
       <c r="K21" t="n">
-        <v>-74.89</v>
+        <v>96.25</v>
       </c>
       <c r="L21" t="n">
-        <v>86.58</v>
+        <v>157.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:28</t>
+          <t>04:49:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="F22" t="n">
-        <v>8.18</v>
+        <v>5.02</v>
       </c>
       <c r="G22" t="n">
-        <v>291</v>
+        <v>297.1</v>
       </c>
       <c r="H22" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-79.38</v>
+        <v>-67.65000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>13.09</v>
+        <v>89.66</v>
       </c>
       <c r="L22" t="n">
-        <v>80.45</v>
+        <v>112.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:20</t>
+          <t>04:53:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="F23" t="n">
-        <v>7.45</v>
+        <v>6.15</v>
       </c>
       <c r="G23" t="n">
-        <v>284.2</v>
+        <v>291</v>
       </c>
       <c r="H23" t="n">
-        <v>53.2</v>
+        <v>49.5</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>144.08</v>
+        <v>-50.55</v>
       </c>
       <c r="K23" t="n">
-        <v>138.43</v>
+        <v>-180.11</v>
       </c>
       <c r="L23" t="n">
-        <v>199.8</v>
+        <v>187.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:58:33</t>
+          <t>04:54:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="F24" t="n">
-        <v>8.619999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G24" t="n">
-        <v>296.4</v>
+        <v>295.1</v>
       </c>
       <c r="H24" t="n">
-        <v>45.6</v>
+        <v>46.4</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-59.28</v>
+        <v>199.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-156.19</v>
+        <v>-93.23999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>167.06</v>
+        <v>220.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:00:04</t>
+          <t>04:56:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.36</v>
+        <v>2.47</v>
       </c>
       <c r="F25" t="n">
-        <v>7.98</v>
+        <v>5.15</v>
       </c>
       <c r="G25" t="n">
-        <v>297.1</v>
+        <v>294.3</v>
       </c>
       <c r="H25" t="n">
-        <v>46.7</v>
+        <v>55.1</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>119.07</v>
+        <v>26.94</v>
       </c>
       <c r="K25" t="n">
-        <v>24.17</v>
+        <v>-134.33</v>
       </c>
       <c r="L25" t="n">
-        <v>121.5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:03:15</t>
+          <t>05:00:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
       <c r="F26" t="n">
-        <v>7.54</v>
+        <v>7.92</v>
       </c>
       <c r="G26" t="n">
-        <v>293.7</v>
+        <v>287.5</v>
       </c>
       <c r="H26" t="n">
-        <v>64</v>
+        <v>45.2</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-45.36</v>
+        <v>59.63</v>
       </c>
       <c r="K26" t="n">
-        <v>-224.19</v>
+        <v>241.52</v>
       </c>
       <c r="L26" t="n">
-        <v>228.73</v>
+        <v>248.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:30</t>
+          <t>05:01:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="F27" t="n">
-        <v>8.140000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G27" t="n">
-        <v>295.1</v>
+        <v>283.4</v>
       </c>
       <c r="H27" t="n">
-        <v>46.4</v>
+        <v>47.2</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-191.3</v>
+        <v>-253.45</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.39</v>
+        <v>4.98</v>
       </c>
       <c r="L27" t="n">
-        <v>191.92</v>
+        <v>253.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:35</t>
+          <t>05:04:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.35</v>
+        <v>3.43</v>
       </c>
       <c r="F28" t="n">
-        <v>7.7</v>
+        <v>9.08</v>
       </c>
       <c r="G28" t="n">
-        <v>304.8</v>
+        <v>294.7</v>
       </c>
       <c r="H28" t="n">
-        <v>48.9</v>
+        <v>52.6</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>54.53</v>
+        <v>-243.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-160.36</v>
+        <v>-7.44</v>
       </c>
       <c r="L28" t="n">
-        <v>169.37</v>
+        <v>243.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:17:12</t>
+          <t>05:16:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.47</v>
+        <v>3.22</v>
       </c>
       <c r="F29" t="n">
-        <v>7.66</v>
+        <v>9.08</v>
       </c>
       <c r="G29" t="n">
-        <v>287.5</v>
+        <v>304.3</v>
       </c>
       <c r="H29" t="n">
-        <v>45.2</v>
+        <v>55.9</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>38.25</v>
+        <v>13.77</v>
       </c>
       <c r="K29" t="n">
-        <v>43.61</v>
+        <v>80.62</v>
       </c>
       <c r="L29" t="n">
-        <v>58.01</v>
+        <v>81.79000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:19:07</t>
+          <t>05:17:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="F30" t="n">
-        <v>8.07</v>
+        <v>7.65</v>
       </c>
       <c r="G30" t="n">
-        <v>283.4</v>
+        <v>291</v>
       </c>
       <c r="H30" t="n">
-        <v>47.2</v>
+        <v>55.4</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.23</v>
+        <v>-4.47</v>
       </c>
       <c r="K30" t="n">
-        <v>13.17</v>
+        <v>-87.95999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>16.08</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:20:09</t>
+          <t>05:19:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="F31" t="n">
-        <v>7.94</v>
+        <v>6.7</v>
       </c>
       <c r="G31" t="n">
-        <v>294.7</v>
+        <v>296.5</v>
       </c>
       <c r="H31" t="n">
-        <v>52.6</v>
+        <v>49.9</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.33</v>
+        <v>-54.6</v>
       </c>
       <c r="K31" t="n">
-        <v>77.67</v>
+        <v>-7.48</v>
       </c>
       <c r="L31" t="n">
-        <v>77.93000000000001</v>
+        <v>55.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:26:13</t>
+          <t>05:23:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="F32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.67</v>
       </c>
       <c r="G32" t="n">
-        <v>306.4</v>
+        <v>281.4</v>
       </c>
       <c r="H32" t="n">
-        <v>49</v>
+        <v>56.1</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>10.75</v>
+        <v>-55.81</v>
       </c>
       <c r="K32" t="n">
-        <v>59.96</v>
+        <v>45.29</v>
       </c>
       <c r="L32" t="n">
-        <v>60.92</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:28:14</t>
+          <t>05:26:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.91</v>
+        <v>2.21</v>
       </c>
       <c r="F33" t="n">
-        <v>7.61</v>
+        <v>5.87</v>
       </c>
       <c r="G33" t="n">
-        <v>291</v>
+        <v>288.7</v>
       </c>
       <c r="H33" t="n">
-        <v>55.4</v>
+        <v>53.1</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.90000000000001</v>
+        <v>50.21</v>
       </c>
       <c r="K33" t="n">
-        <v>35.94</v>
+        <v>-71.25</v>
       </c>
       <c r="L33" t="n">
-        <v>83.98</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:29:10</t>
+          <t>05:28:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="F34" t="n">
-        <v>7.76</v>
+        <v>6.35</v>
       </c>
       <c r="G34" t="n">
-        <v>298.5</v>
+        <v>294.9</v>
       </c>
       <c r="H34" t="n">
-        <v>50.9</v>
+        <v>62.6</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.4</v>
+        <v>-107.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-42.85</v>
+        <v>-38.39</v>
       </c>
       <c r="L34" t="n">
-        <v>43.66</v>
+        <v>114.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:33:09</t>
+          <t>05:32:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="F35" t="n">
-        <v>8.07</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>294.4</v>
+        <v>289</v>
       </c>
       <c r="H35" t="n">
-        <v>51</v>
+        <v>48.2</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.93000000000001</v>
+        <v>-49.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.57</v>
+        <v>-164.58</v>
       </c>
       <c r="L35" t="n">
-        <v>68.59999999999999</v>
+        <v>171.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:35:23</t>
+          <t>05:33:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="F36" t="n">
-        <v>8.25</v>
+        <v>7.93</v>
       </c>
       <c r="G36" t="n">
-        <v>294.3</v>
+        <v>297.1</v>
       </c>
       <c r="H36" t="n">
-        <v>47.1</v>
+        <v>58.4</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-25.68</v>
+        <v>-114.77</v>
       </c>
       <c r="K36" t="n">
-        <v>3.58</v>
+        <v>-127.51</v>
       </c>
       <c r="L36" t="n">
-        <v>25.93</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:36:55</t>
+          <t>05:34:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="F37" t="n">
-        <v>8.109999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="G37" t="n">
-        <v>292.1</v>
+        <v>283.5</v>
       </c>
       <c r="H37" t="n">
-        <v>53.6</v>
+        <v>51.9</v>
       </c>
       <c r="I37" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-70.67</v>
+        <v>0.62</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.45</v>
+        <v>152.72</v>
       </c>
       <c r="L37" t="n">
-        <v>70.76000000000001</v>
+        <v>152.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:41:44</t>
+          <t>05:37:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="F38" t="n">
-        <v>6.93</v>
+        <v>7.11</v>
       </c>
       <c r="G38" t="n">
-        <v>293.8</v>
+        <v>301.7</v>
       </c>
       <c r="H38" t="n">
-        <v>55.9</v>
+        <v>50.5</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-108</v>
+        <v>-158.56</v>
       </c>
       <c r="K38" t="n">
-        <v>-25.78</v>
+        <v>-158.7</v>
       </c>
       <c r="L38" t="n">
-        <v>111.04</v>
+        <v>224.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:44:28</t>
+          <t>05:40:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="F39" t="n">
-        <v>7.83</v>
+        <v>7.54</v>
       </c>
       <c r="G39" t="n">
-        <v>285.1</v>
+        <v>300.3</v>
       </c>
       <c r="H39" t="n">
-        <v>46.9</v>
+        <v>55.9</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>41.12</v>
+        <v>-5.99</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.28</v>
+        <v>175.99</v>
       </c>
       <c r="L39" t="n">
-        <v>102.86</v>
+        <v>176.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:46:53</t>
+          <t>05:42:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="F40" t="n">
-        <v>8.69</v>
+        <v>6.81</v>
       </c>
       <c r="G40" t="n">
-        <v>299.5</v>
+        <v>297.3</v>
       </c>
       <c r="H40" t="n">
-        <v>53.6</v>
+        <v>51</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-113.11</v>
+        <v>91.39</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.32</v>
+        <v>-221.73</v>
       </c>
       <c r="L40" t="n">
-        <v>113.11</v>
+        <v>239.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:08</t>
+          <t>05:46:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="F41" t="n">
-        <v>8.01</v>
+        <v>4.93</v>
       </c>
       <c r="G41" t="n">
-        <v>285.1</v>
+        <v>295.3</v>
       </c>
       <c r="H41" t="n">
-        <v>46.8</v>
+        <v>48.9</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.42</v>
+        <v>140.07</v>
       </c>
       <c r="K41" t="n">
-        <v>148.39</v>
+        <v>160.57</v>
       </c>
       <c r="L41" t="n">
-        <v>148.57</v>
+        <v>213.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:53:48</t>
+          <t>05:47:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="F42" t="n">
-        <v>8.380000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G42" t="n">
-        <v>299.8</v>
+        <v>292.2</v>
       </c>
       <c r="H42" t="n">
-        <v>48.5</v>
+        <v>55</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>131.54</v>
+        <v>112.21</v>
       </c>
       <c r="K42" t="n">
-        <v>-82.5</v>
+        <v>54.4</v>
       </c>
       <c r="L42" t="n">
-        <v>155.27</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:00</t>
+          <t>05:49:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="F43" t="n">
-        <v>7.91</v>
+        <v>5.84</v>
       </c>
       <c r="G43" t="n">
-        <v>279.4</v>
+        <v>293.3</v>
       </c>
       <c r="H43" t="n">
-        <v>56.5</v>
+        <v>53.6</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-195.06</v>
+        <v>-198.03</v>
       </c>
       <c r="K43" t="n">
-        <v>90.20999999999999</v>
+        <v>-72.23</v>
       </c>
       <c r="L43" t="n">
-        <v>214.91</v>
+        <v>210.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:09</t>
+          <t>05:56:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="F44" t="n">
-        <v>8.130000000000001</v>
+        <v>6.54</v>
       </c>
       <c r="G44" t="n">
-        <v>306.3</v>
+        <v>312.5</v>
       </c>
       <c r="H44" t="n">
-        <v>59.2</v>
+        <v>57.3</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.31</v>
+        <v>-102.23</v>
       </c>
       <c r="K44" t="n">
-        <v>70.7</v>
+        <v>37.02</v>
       </c>
       <c r="L44" t="n">
-        <v>70.98</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:08:10</t>
+          <t>05:57:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="F45" t="n">
-        <v>7.33</v>
+        <v>6.16</v>
       </c>
       <c r="G45" t="n">
-        <v>297.8</v>
+        <v>299.5</v>
       </c>
       <c r="H45" t="n">
-        <v>54.1</v>
+        <v>57</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-20.63</v>
+        <v>45.81</v>
       </c>
       <c r="K45" t="n">
-        <v>38.75</v>
+        <v>-28.83</v>
       </c>
       <c r="L45" t="n">
-        <v>43.9</v>
+        <v>54.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:40</t>
+          <t>05:59:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="F46" t="n">
-        <v>7.73</v>
+        <v>8.56</v>
       </c>
       <c r="G46" t="n">
-        <v>294.2</v>
+        <v>296.1</v>
       </c>
       <c r="H46" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
       <c r="I46" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>52.31</v>
+        <v>52.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.8</v>
+        <v>-35.15</v>
       </c>
       <c r="L46" t="n">
-        <v>53.86</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:13:03</t>
+          <t>06:02:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="F47" t="n">
-        <v>7.76</v>
+        <v>6.24</v>
       </c>
       <c r="G47" t="n">
-        <v>306.6</v>
+        <v>287.4</v>
       </c>
       <c r="H47" t="n">
-        <v>40.1</v>
+        <v>56.8</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-50.33</v>
+        <v>-36.32</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.93</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>59.6</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:13:59</t>
+          <t>06:04:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="F48" t="n">
-        <v>7.78</v>
+        <v>4.69</v>
       </c>
       <c r="G48" t="n">
-        <v>302.2</v>
+        <v>296.9</v>
       </c>
       <c r="H48" t="n">
-        <v>56.9</v>
+        <v>53.7</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>32.99</v>
+        <v>-22.6</v>
       </c>
       <c r="K48" t="n">
-        <v>52.28</v>
+        <v>82.61</v>
       </c>
       <c r="L48" t="n">
-        <v>61.82</v>
+        <v>85.65000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:15:11</t>
+          <t>06:06:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="F49" t="n">
-        <v>7.45</v>
+        <v>8.93</v>
       </c>
       <c r="G49" t="n">
-        <v>295.1</v>
+        <v>301.4</v>
       </c>
       <c r="H49" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-23.43</v>
+        <v>-36.04</v>
       </c>
       <c r="K49" t="n">
-        <v>57.96</v>
+        <v>77.78</v>
       </c>
       <c r="L49" t="n">
-        <v>62.52</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:19:51</t>
+          <t>06:11:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="F50" t="n">
-        <v>8.220000000000001</v>
+        <v>6.34</v>
       </c>
       <c r="G50" t="n">
         <v>295.3</v>
       </c>
       <c r="H50" t="n">
-        <v>49.4</v>
+        <v>57</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-36.18</v>
+        <v>-41.26</v>
       </c>
       <c r="K50" t="n">
-        <v>-100.47</v>
+        <v>111.98</v>
       </c>
       <c r="L50" t="n">
-        <v>106.79</v>
+        <v>119.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:21:41</t>
+          <t>06:12:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="F51" t="n">
-        <v>7.5</v>
+        <v>9.08</v>
       </c>
       <c r="G51" t="n">
-        <v>307.2</v>
+        <v>292.5</v>
       </c>
       <c r="H51" t="n">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>93.83</v>
+        <v>-26.56</v>
       </c>
       <c r="K51" t="n">
-        <v>9.24</v>
+        <v>-143.18</v>
       </c>
       <c r="L51" t="n">
-        <v>94.29000000000001</v>
+        <v>145.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:30</t>
+          <t>06:14:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="F52" t="n">
-        <v>8.23</v>
+        <v>9.08</v>
       </c>
       <c r="G52" t="n">
-        <v>295.4</v>
+        <v>296.8</v>
       </c>
       <c r="H52" t="n">
-        <v>51.7</v>
+        <v>46.2</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>67.08</v>
+        <v>-131.61</v>
       </c>
       <c r="K52" t="n">
-        <v>-75.95</v>
+        <v>-47.07</v>
       </c>
       <c r="L52" t="n">
-        <v>101.33</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:27:43</t>
+          <t>06:18:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="F53" t="n">
-        <v>8.119999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="G53" t="n">
-        <v>304.8</v>
+        <v>293.9</v>
       </c>
       <c r="H53" t="n">
-        <v>51.1</v>
+        <v>44.9</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>110.76</v>
+        <v>-58.09</v>
       </c>
       <c r="K53" t="n">
-        <v>30.34</v>
+        <v>-237.03</v>
       </c>
       <c r="L53" t="n">
-        <v>114.84</v>
+        <v>244.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:01</t>
+          <t>06:19:52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="F54" t="n">
-        <v>7.35</v>
+        <v>6.85</v>
       </c>
       <c r="G54" t="n">
-        <v>297.5</v>
+        <v>311.2</v>
       </c>
       <c r="H54" t="n">
-        <v>53.4</v>
+        <v>55.9</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.21</v>
+        <v>-147.56</v>
       </c>
       <c r="K54" t="n">
-        <v>145.46</v>
+        <v>-97.76000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>153.88</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:31:08</t>
+          <t>06:22:41</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="F55" t="n">
-        <v>8.609999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="G55" t="n">
-        <v>294.3</v>
+        <v>310.9</v>
       </c>
       <c r="H55" t="n">
-        <v>47.9</v>
+        <v>51.3</v>
       </c>
       <c r="I55" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-63.66</v>
+        <v>48.79</v>
       </c>
       <c r="K55" t="n">
-        <v>-130.94</v>
+        <v>-149.63</v>
       </c>
       <c r="L55" t="n">
-        <v>145.59</v>
+        <v>157.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:35:46</t>
+          <t>06:28:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="F56" t="n">
-        <v>6.99</v>
+        <v>9.08</v>
       </c>
       <c r="G56" t="n">
-        <v>296.4</v>
+        <v>300.4</v>
       </c>
       <c r="H56" t="n">
-        <v>49.3</v>
+        <v>54.3</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>102.86</v>
+        <v>118.92</v>
       </c>
       <c r="K56" t="n">
-        <v>185.79</v>
+        <v>-232.85</v>
       </c>
       <c r="L56" t="n">
-        <v>212.36</v>
+        <v>261.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:36:56</t>
+          <t>06:30:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="F57" t="n">
-        <v>8.57</v>
+        <v>9.08</v>
       </c>
       <c r="G57" t="n">
-        <v>288.4</v>
+        <v>292.8</v>
       </c>
       <c r="H57" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-26.83</v>
+        <v>-125.92</v>
       </c>
       <c r="K57" t="n">
-        <v>190.93</v>
+        <v>152.07</v>
       </c>
       <c r="L57" t="n">
-        <v>192.81</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:03</t>
+          <t>06:32:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="F58" t="n">
-        <v>7.66</v>
+        <v>7.99</v>
       </c>
       <c r="G58" t="n">
-        <v>287.2</v>
+        <v>292.6</v>
       </c>
       <c r="H58" t="n">
-        <v>48.8</v>
+        <v>54</v>
       </c>
       <c r="I58" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>113.45</v>
+        <v>-195.12</v>
       </c>
       <c r="K58" t="n">
-        <v>70.75</v>
+        <v>136.5</v>
       </c>
       <c r="L58" t="n">
-        <v>133.7</v>
+        <v>238.13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:49:32</t>
+          <t>06:40:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="F59" t="n">
-        <v>8.68</v>
+        <v>9.08</v>
       </c>
       <c r="G59" t="n">
-        <v>293.7</v>
+        <v>296</v>
       </c>
       <c r="H59" t="n">
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.51</v>
+        <v>-46.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.16</v>
+        <v>-37.57</v>
       </c>
       <c r="L59" t="n">
-        <v>47.86</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:51:39</t>
+          <t>06:42:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.36</v>
+        <v>3.08</v>
       </c>
       <c r="F60" t="n">
-        <v>8.26</v>
+        <v>9.08</v>
       </c>
       <c r="G60" t="n">
-        <v>304.5</v>
+        <v>293.9</v>
       </c>
       <c r="H60" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>27.5</v>
+        <v>42.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.06</v>
+        <v>74.16</v>
       </c>
       <c r="L60" t="n">
-        <v>44.56</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:53:12</t>
+          <t>06:44:25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="F61" t="n">
-        <v>8.220000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="G61" t="n">
-        <v>298.8</v>
+        <v>312.6</v>
       </c>
       <c r="H61" t="n">
-        <v>53.3</v>
+        <v>42.4</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.25</v>
+        <v>-35.4</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.52</v>
+        <v>-58.12</v>
       </c>
       <c r="L61" t="n">
-        <v>53.73</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:57:47</t>
+          <t>06:47:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="F62" t="n">
-        <v>7.96</v>
+        <v>6.9</v>
       </c>
       <c r="G62" t="n">
-        <v>308.7</v>
+        <v>299.1</v>
       </c>
       <c r="H62" t="n">
-        <v>50.3</v>
+        <v>48.7</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>23.97</v>
+        <v>68.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.51</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>50.55</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:59:08</t>
+          <t>06:48:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="F63" t="n">
-        <v>7.21</v>
+        <v>6.79</v>
       </c>
       <c r="G63" t="n">
-        <v>285</v>
+        <v>291.7</v>
       </c>
       <c r="H63" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-93.69</v>
+        <v>-77.13</v>
       </c>
       <c r="K63" t="n">
-        <v>71.28</v>
+        <v>-32.81</v>
       </c>
       <c r="L63" t="n">
-        <v>117.72</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:00:07</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.39</v>
+        <v>2.93</v>
       </c>
       <c r="F64" t="n">
-        <v>7.49</v>
+        <v>5.44</v>
       </c>
       <c r="G64" t="n">
-        <v>289.3</v>
+        <v>291.9</v>
       </c>
       <c r="H64" t="n">
-        <v>55.9</v>
+        <v>46.6</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>7.12</v>
+        <v>-26.56</v>
       </c>
       <c r="K64" t="n">
-        <v>60.51</v>
+        <v>-67.81</v>
       </c>
       <c r="L64" t="n">
-        <v>60.93</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:04:26</t>
+          <t>06:54:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="F65" t="n">
-        <v>7.17</v>
+        <v>8.48</v>
       </c>
       <c r="G65" t="n">
-        <v>292.8</v>
+        <v>296.3</v>
       </c>
       <c r="H65" t="n">
-        <v>55.9</v>
+        <v>52.9</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-85.11</v>
+        <v>-74.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-58.49</v>
+        <v>110.76</v>
       </c>
       <c r="L65" t="n">
-        <v>103.28</v>
+        <v>133.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:07:15</t>
+          <t>06:56:28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="F66" t="n">
-        <v>7.21</v>
+        <v>9.08</v>
       </c>
       <c r="G66" t="n">
-        <v>311.9</v>
+        <v>294.1</v>
       </c>
       <c r="H66" t="n">
-        <v>54.3</v>
+        <v>53.6</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-65.64</v>
+        <v>21.09</v>
       </c>
       <c r="K66" t="n">
-        <v>63.25</v>
+        <v>184.61</v>
       </c>
       <c r="L66" t="n">
-        <v>91.15000000000001</v>
+        <v>185.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:09:27</t>
+          <t>06:57:31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="F67" t="n">
-        <v>7.57</v>
+        <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>298</v>
+        <v>300.6</v>
       </c>
       <c r="H67" t="n">
-        <v>55.6</v>
+        <v>50.8</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-57.2</v>
+        <v>119.54</v>
       </c>
       <c r="K67" t="n">
-        <v>-40.79</v>
+        <v>47.49</v>
       </c>
       <c r="L67" t="n">
-        <v>70.26000000000001</v>
+        <v>128.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:13:15</t>
+          <t>07:01:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="F68" t="n">
-        <v>8.43</v>
+        <v>5.46</v>
       </c>
       <c r="G68" t="n">
-        <v>306.5</v>
+        <v>293.9</v>
       </c>
       <c r="H68" t="n">
-        <v>52.8</v>
+        <v>58.4</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.56</v>
+        <v>6.27</v>
       </c>
       <c r="K68" t="n">
-        <v>119.19</v>
+        <v>123.77</v>
       </c>
       <c r="L68" t="n">
-        <v>135.08</v>
+        <v>123.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:15:30</t>
+          <t>07:03:56</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="F69" t="n">
-        <v>7.86</v>
+        <v>9.08</v>
       </c>
       <c r="G69" t="n">
-        <v>300.5</v>
+        <v>309.3</v>
       </c>
       <c r="H69" t="n">
-        <v>54.6</v>
+        <v>56.3</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>34.96</v>
+        <v>56.69</v>
       </c>
       <c r="K69" t="n">
-        <v>100.37</v>
+        <v>127.81</v>
       </c>
       <c r="L69" t="n">
-        <v>106.28</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:16:57</t>
+          <t>07:05:56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="F70" t="n">
-        <v>7.37</v>
+        <v>8.27</v>
       </c>
       <c r="G70" t="n">
         <v>295.6</v>
       </c>
       <c r="H70" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-79.29000000000001</v>
+        <v>183.21</v>
       </c>
       <c r="K70" t="n">
-        <v>125.04</v>
+        <v>-168.11</v>
       </c>
       <c r="L70" t="n">
-        <v>148.06</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:21:11</t>
+          <t>07:11:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="F71" t="n">
-        <v>8.59</v>
+        <v>7.42</v>
       </c>
       <c r="G71" t="n">
-        <v>290.5</v>
+        <v>304</v>
       </c>
       <c r="H71" t="n">
-        <v>48.6</v>
+        <v>54.5</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>125.44</v>
+        <v>125.82</v>
       </c>
       <c r="K71" t="n">
-        <v>181.52</v>
+        <v>246.73</v>
       </c>
       <c r="L71" t="n">
-        <v>220.65</v>
+        <v>276.96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:23:25</t>
+          <t>07:12:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="F72" t="n">
-        <v>7.83</v>
+        <v>9.08</v>
       </c>
       <c r="G72" t="n">
-        <v>288.9</v>
+        <v>291.7</v>
       </c>
       <c r="H72" t="n">
-        <v>52</v>
+        <v>53.8</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-139.18</v>
+        <v>-344.54</v>
       </c>
       <c r="K72" t="n">
-        <v>-62.44</v>
+        <v>31.33</v>
       </c>
       <c r="L72" t="n">
-        <v>152.55</v>
+        <v>345.96</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:24:56</t>
+          <t>07:13:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F73" t="n">
-        <v>7.64</v>
+        <v>9.08</v>
       </c>
       <c r="G73" t="n">
-        <v>296.2</v>
+        <v>301.2</v>
       </c>
       <c r="H73" t="n">
-        <v>53.8</v>
+        <v>57.2</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>99.13</v>
+        <v>29.37</v>
       </c>
       <c r="K73" t="n">
-        <v>143.2</v>
+        <v>221.88</v>
       </c>
       <c r="L73" t="n">
-        <v>174.17</v>
+        <v>223.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:31:53</t>
+          <t>07:21:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F74" t="n">
-        <v>7.68</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>304.7</v>
+        <v>307.2</v>
       </c>
       <c r="H74" t="n">
-        <v>56.9</v>
+        <v>47.8</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>25.87</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.16</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>50.31</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:33:07</t>
+          <t>07:23:02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.46</v>
+        <v>2.87</v>
       </c>
       <c r="F75" t="n">
-        <v>8.32</v>
+        <v>9.08</v>
       </c>
       <c r="G75" t="n">
-        <v>288.7</v>
+        <v>296.9</v>
       </c>
       <c r="H75" t="n">
-        <v>53</v>
+        <v>48.2</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>55.71</v>
+        <v>-64.7</v>
       </c>
       <c r="K75" t="n">
-        <v>15.74</v>
+        <v>23.59</v>
       </c>
       <c r="L75" t="n">
-        <v>57.89</v>
+        <v>68.87</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:34:40</t>
+          <t>07:24:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="F76" t="n">
-        <v>7.32</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>293.8</v>
+        <v>290.2</v>
       </c>
       <c r="H76" t="n">
-        <v>54.5</v>
+        <v>50.9</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-38.69</v>
+        <v>39.53</v>
       </c>
       <c r="K76" t="n">
-        <v>42.88</v>
+        <v>-58.17</v>
       </c>
       <c r="L76" t="n">
-        <v>57.76</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:38:05</t>
+          <t>07:29:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="F77" t="n">
-        <v>7.54</v>
+        <v>8.31</v>
       </c>
       <c r="G77" t="n">
-        <v>309.6</v>
+        <v>295.6</v>
       </c>
       <c r="H77" t="n">
-        <v>52.3</v>
+        <v>55</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-30.57</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.15</v>
+        <v>-46.96</v>
       </c>
       <c r="L77" t="n">
-        <v>56.19</v>
+        <v>90.14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:39:08</t>
+          <t>07:31:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F78" t="n">
-        <v>7.81</v>
+        <v>7.51</v>
       </c>
       <c r="G78" t="n">
-        <v>302.3</v>
+        <v>292.5</v>
       </c>
       <c r="H78" t="n">
-        <v>51.4</v>
+        <v>55.8</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>55.36</v>
+        <v>-124.71</v>
       </c>
       <c r="K78" t="n">
-        <v>41.5</v>
+        <v>-27.65</v>
       </c>
       <c r="L78" t="n">
-        <v>69.19</v>
+        <v>127.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:40:01</t>
+          <t>07:33:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="F79" t="n">
-        <v>8.220000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="G79" t="n">
-        <v>300.4</v>
+        <v>292.4</v>
       </c>
       <c r="H79" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.11</v>
+        <v>4.76</v>
       </c>
       <c r="K79" t="n">
-        <v>52.15</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>74.43000000000001</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:45:30</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="F80" t="n">
-        <v>8.300000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G80" t="n">
-        <v>293.6</v>
+        <v>299.1</v>
       </c>
       <c r="H80" t="n">
-        <v>45.6</v>
+        <v>51.2</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>44.18</v>
+        <v>95.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-135.23</v>
+        <v>-72.52</v>
       </c>
       <c r="L80" t="n">
-        <v>142.27</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:47:30</t>
+          <t>07:39:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.74</v>
+        <v>3.26</v>
       </c>
       <c r="F81" t="n">
-        <v>8.32</v>
+        <v>9.08</v>
       </c>
       <c r="G81" t="n">
-        <v>303.6</v>
+        <v>295.6</v>
       </c>
       <c r="H81" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-64.12</v>
+        <v>-153.62</v>
       </c>
       <c r="K81" t="n">
-        <v>26.7</v>
+        <v>45.82</v>
       </c>
       <c r="L81" t="n">
-        <v>69.45</v>
+        <v>160.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:49:17</t>
+          <t>07:41:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="F82" t="n">
-        <v>7.84</v>
+        <v>8.25</v>
       </c>
       <c r="G82" t="n">
-        <v>302.4</v>
+        <v>300.6</v>
       </c>
       <c r="H82" t="n">
-        <v>56.9</v>
+        <v>48.6</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>48.25</v>
+        <v>42.29</v>
       </c>
       <c r="K82" t="n">
-        <v>73.51000000000001</v>
+        <v>108.52</v>
       </c>
       <c r="L82" t="n">
-        <v>87.93000000000001</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:53:51</t>
+          <t>07:45:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.76</v>
+        <v>3.16</v>
       </c>
       <c r="F83" t="n">
-        <v>7.49</v>
+        <v>9.08</v>
       </c>
       <c r="G83" t="n">
-        <v>291.5</v>
+        <v>305.1</v>
       </c>
       <c r="H83" t="n">
-        <v>54.5</v>
+        <v>51.4</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.86</v>
+        <v>174.63</v>
       </c>
       <c r="K83" t="n">
-        <v>-145.53</v>
+        <v>95.13</v>
       </c>
       <c r="L83" t="n">
-        <v>145.55</v>
+        <v>198.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:55:11</t>
+          <t>07:46:53</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="F84" t="n">
-        <v>7.58</v>
+        <v>5.45</v>
       </c>
       <c r="G84" t="n">
-        <v>292.8</v>
+        <v>295.6</v>
       </c>
       <c r="H84" t="n">
-        <v>54.1</v>
+        <v>57.2</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-50.82</v>
+        <v>58.61</v>
       </c>
       <c r="K84" t="n">
-        <v>96.39</v>
+        <v>-159.55</v>
       </c>
       <c r="L84" t="n">
-        <v>108.97</v>
+        <v>169.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:56:04</t>
+          <t>07:47:47</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="F85" t="n">
-        <v>7.86</v>
+        <v>8.32</v>
       </c>
       <c r="G85" t="n">
-        <v>295.3</v>
+        <v>306.9</v>
       </c>
       <c r="H85" t="n">
-        <v>52.7</v>
+        <v>51.3</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>86.13</v>
+        <v>-166.55</v>
       </c>
       <c r="K85" t="n">
-        <v>142.99</v>
+        <v>177.72</v>
       </c>
       <c r="L85" t="n">
-        <v>166.92</v>
+        <v>243.56</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:00:10</t>
+          <t>07:51:43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="F86" t="n">
-        <v>8.44</v>
+        <v>7.23</v>
       </c>
       <c r="G86" t="n">
-        <v>284.3</v>
+        <v>302</v>
       </c>
       <c r="H86" t="n">
-        <v>50.8</v>
+        <v>56</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>68.54000000000001</v>
+        <v>-65.15000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>135.58</v>
+        <v>380.65</v>
       </c>
       <c r="L86" t="n">
-        <v>151.92</v>
+        <v>386.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:01:56</t>
+          <t>07:53:06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F87" t="n">
-        <v>7.85</v>
+        <v>6.84</v>
       </c>
       <c r="G87" t="n">
-        <v>293.6</v>
+        <v>309.5</v>
       </c>
       <c r="H87" t="n">
-        <v>53</v>
+        <v>55.2</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>102.61</v>
+        <v>200.55</v>
       </c>
       <c r="K87" t="n">
-        <v>-177.7</v>
+        <v>-125.98</v>
       </c>
       <c r="L87" t="n">
-        <v>205.2</v>
+        <v>236.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:02:27</t>
+          <t>07:54:41</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,25 +3736,25 @@
         <v>3.33</v>
       </c>
       <c r="F88" t="n">
-        <v>8.32</v>
+        <v>9.08</v>
       </c>
       <c r="G88" t="n">
-        <v>288.7</v>
+        <v>298.7</v>
       </c>
       <c r="H88" t="n">
-        <v>51.2</v>
+        <v>49.3</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-216.09</v>
+        <v>-363.78</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.05</v>
+        <v>139.34</v>
       </c>
       <c r="L88" t="n">
-        <v>217.42</v>
+        <v>389.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.1</v>
+        <v>-15.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-70.12</v>
+        <v>-76.5</v>
       </c>
       <c r="L14" t="n">
-        <v>71.53</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-69.39</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-43.57</v>
+        <v>-49.58</v>
       </c>
       <c r="L15" t="n">
-        <v>81.93000000000001</v>
+        <v>93.23</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>84.36</v>
+        <v>96</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.43</v>
+        <v>-15.28</v>
       </c>
       <c r="L16" t="n">
-        <v>85.42</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-73.16</v>
+        <v>-81</v>
       </c>
       <c r="K17" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="L17" t="n">
-        <v>73.17</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>26.12</v>
+        <v>29.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-72.22</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>76.8</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>4.58</v>
+        <v>5.21</v>
       </c>
       <c r="K19" t="n">
-        <v>99.77</v>
+        <v>113.53</v>
       </c>
       <c r="L19" t="n">
-        <v>99.87</v>
+        <v>113.65</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>115.26</v>
+        <v>127.61</v>
       </c>
       <c r="K20" t="n">
-        <v>115.75</v>
+        <v>128.16</v>
       </c>
       <c r="L20" t="n">
-        <v>163.35</v>
+        <v>180.86</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-125.21</v>
+        <v>-142.48</v>
       </c>
       <c r="K21" t="n">
-        <v>96.25</v>
+        <v>109.53</v>
       </c>
       <c r="L21" t="n">
-        <v>157.93</v>
+        <v>179.71</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-67.65000000000001</v>
+        <v>-76.98</v>
       </c>
       <c r="K22" t="n">
-        <v>89.66</v>
+        <v>102.02</v>
       </c>
       <c r="L22" t="n">
-        <v>112.31</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-50.55</v>
+        <v>-56.76</v>
       </c>
       <c r="K23" t="n">
-        <v>-180.11</v>
+        <v>-202.23</v>
       </c>
       <c r="L23" t="n">
-        <v>187.07</v>
+        <v>210.04</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>199.3</v>
+        <v>220.66</v>
       </c>
       <c r="K24" t="n">
-        <v>-93.23999999999999</v>
+        <v>-103.23</v>
       </c>
       <c r="L24" t="n">
-        <v>220.03</v>
+        <v>243.61</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>26.94</v>
+        <v>28.93</v>
       </c>
       <c r="K25" t="n">
-        <v>-134.33</v>
+        <v>-144.28</v>
       </c>
       <c r="L25" t="n">
-        <v>137</v>
+        <v>147.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>59.63</v>
+        <v>65.05</v>
       </c>
       <c r="K26" t="n">
-        <v>241.52</v>
+        <v>263.48</v>
       </c>
       <c r="L26" t="n">
-        <v>248.77</v>
+        <v>271.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-253.45</v>
+        <v>-284.57</v>
       </c>
       <c r="K27" t="n">
-        <v>4.98</v>
+        <v>5.59</v>
       </c>
       <c r="L27" t="n">
-        <v>253.49</v>
+        <v>284.63</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-243.8</v>
+        <v>-277.86</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.44</v>
+        <v>-8.48</v>
       </c>
       <c r="L28" t="n">
-        <v>243.91</v>
+        <v>277.99</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>13.77</v>
+        <v>15.46</v>
       </c>
       <c r="K29" t="n">
-        <v>80.62</v>
+        <v>90.52</v>
       </c>
       <c r="L29" t="n">
-        <v>81.79000000000001</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.47</v>
+        <v>-4.95</v>
       </c>
       <c r="K30" t="n">
-        <v>-87.95999999999999</v>
+        <v>-97.38</v>
       </c>
       <c r="L30" t="n">
-        <v>88.06999999999999</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-54.6</v>
+        <v>-61.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.48</v>
+        <v>-8.4</v>
       </c>
       <c r="L31" t="n">
-        <v>55.11</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-55.81</v>
+        <v>-61.79</v>
       </c>
       <c r="K32" t="n">
-        <v>45.29</v>
+        <v>50.15</v>
       </c>
       <c r="L32" t="n">
-        <v>71.88</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>50.21</v>
+        <v>53.93</v>
       </c>
       <c r="K33" t="n">
-        <v>-71.25</v>
+        <v>-76.53</v>
       </c>
       <c r="L33" t="n">
-        <v>87.17</v>
+        <v>93.62</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-107.69</v>
+        <v>-119.23</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.39</v>
+        <v>-42.5</v>
       </c>
       <c r="L34" t="n">
-        <v>114.33</v>
+        <v>126.58</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>-49.74</v>
+        <v>-55.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-164.58</v>
+        <v>-184.8</v>
       </c>
       <c r="L35" t="n">
-        <v>171.93</v>
+        <v>193.05</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-114.77</v>
+        <v>-130.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-127.51</v>
+        <v>-145.1</v>
       </c>
       <c r="L36" t="n">
-        <v>171.55</v>
+        <v>195.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="K37" t="n">
-        <v>152.72</v>
+        <v>164.04</v>
       </c>
       <c r="L37" t="n">
-        <v>152.72</v>
+        <v>164.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-158.56</v>
+        <v>-180.43</v>
       </c>
       <c r="K38" t="n">
-        <v>-158.7</v>
+        <v>-180.59</v>
       </c>
       <c r="L38" t="n">
-        <v>224.34</v>
+        <v>255.28</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.99</v>
+        <v>-6.44</v>
       </c>
       <c r="K39" t="n">
-        <v>175.99</v>
+        <v>189.03</v>
       </c>
       <c r="L39" t="n">
-        <v>176.09</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>91.39</v>
+        <v>103.99</v>
       </c>
       <c r="K40" t="n">
-        <v>-221.73</v>
+        <v>-252.32</v>
       </c>
       <c r="L40" t="n">
-        <v>239.83</v>
+        <v>272.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>140.07</v>
+        <v>159.39</v>
       </c>
       <c r="K41" t="n">
-        <v>160.57</v>
+        <v>182.72</v>
       </c>
       <c r="L41" t="n">
-        <v>213.08</v>
+        <v>242.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>112.21</v>
+        <v>120.52</v>
       </c>
       <c r="K42" t="n">
-        <v>54.4</v>
+        <v>58.43</v>
       </c>
       <c r="L42" t="n">
-        <v>124.7</v>
+        <v>133.94</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-198.03</v>
+        <v>-222.35</v>
       </c>
       <c r="K43" t="n">
-        <v>-72.23</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>210.79</v>
+        <v>236.68</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-102.23</v>
+        <v>-111.52</v>
       </c>
       <c r="K44" t="n">
-        <v>37.02</v>
+        <v>40.39</v>
       </c>
       <c r="L44" t="n">
-        <v>108.73</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>45.81</v>
+        <v>49.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-28.83</v>
+        <v>-30.97</v>
       </c>
       <c r="L45" t="n">
-        <v>54.13</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>52.74</v>
+        <v>58.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.15</v>
+        <v>-38.91</v>
       </c>
       <c r="L46" t="n">
-        <v>63.38</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-36.32</v>
+        <v>-40.22</v>
       </c>
       <c r="K47" t="n">
-        <v>71.18000000000001</v>
+        <v>78.81</v>
       </c>
       <c r="L47" t="n">
-        <v>79.92</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.6</v>
+        <v>-25.71</v>
       </c>
       <c r="K48" t="n">
-        <v>82.61</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>85.65000000000001</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-36.04</v>
+        <v>-38.71</v>
       </c>
       <c r="K49" t="n">
-        <v>77.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>85.73</v>
+        <v>92.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-41.26</v>
+        <v>-46.33</v>
       </c>
       <c r="K50" t="n">
-        <v>111.98</v>
+        <v>125.73</v>
       </c>
       <c r="L50" t="n">
-        <v>119.34</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.56</v>
+        <v>-30.22</v>
       </c>
       <c r="K51" t="n">
-        <v>-143.18</v>
+        <v>-162.93</v>
       </c>
       <c r="L51" t="n">
-        <v>145.62</v>
+        <v>165.71</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-131.61</v>
+        <v>-149.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.07</v>
+        <v>-53.56</v>
       </c>
       <c r="L52" t="n">
-        <v>139.77</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-58.09</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-237.03</v>
+        <v>-269.72</v>
       </c>
       <c r="L53" t="n">
-        <v>244.04</v>
+        <v>277.7</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-147.56</v>
+        <v>-165.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-97.76000000000001</v>
+        <v>-109.76</v>
       </c>
       <c r="L54" t="n">
-        <v>177</v>
+        <v>198.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>48.79</v>
+        <v>55.52</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.63</v>
+        <v>-170.27</v>
       </c>
       <c r="L55" t="n">
-        <v>157.38</v>
+        <v>179.09</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>118.92</v>
+        <v>127.73</v>
       </c>
       <c r="K56" t="n">
-        <v>-232.85</v>
+        <v>-250.1</v>
       </c>
       <c r="L56" t="n">
-        <v>261.46</v>
+        <v>280.83</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-125.92</v>
+        <v>-139.41</v>
       </c>
       <c r="K57" t="n">
-        <v>152.07</v>
+        <v>168.37</v>
       </c>
       <c r="L57" t="n">
-        <v>197.44</v>
+        <v>218.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-195.12</v>
+        <v>-216.03</v>
       </c>
       <c r="K58" t="n">
-        <v>136.5</v>
+        <v>151.12</v>
       </c>
       <c r="L58" t="n">
-        <v>238.13</v>
+        <v>263.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.08</v>
+        <v>-49.5</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.57</v>
+        <v>-40.35</v>
       </c>
       <c r="L59" t="n">
-        <v>59.46</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>42.5</v>
+        <v>47.72</v>
       </c>
       <c r="K60" t="n">
-        <v>74.16</v>
+        <v>83.27</v>
       </c>
       <c r="L60" t="n">
-        <v>85.48</v>
+        <v>95.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-35.4</v>
+        <v>-40.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-58.12</v>
+        <v>-66.13</v>
       </c>
       <c r="L61" t="n">
-        <v>68.05</v>
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>68.64</v>
+        <v>74.88</v>
       </c>
       <c r="K62" t="n">
-        <v>65.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="L62" t="n">
-        <v>95.16</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.13</v>
+        <v>-85.40000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-32.81</v>
+        <v>-36.33</v>
       </c>
       <c r="L63" t="n">
-        <v>83.81999999999999</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.56</v>
+        <v>-29.82</v>
       </c>
       <c r="K64" t="n">
-        <v>-67.81</v>
+        <v>-76.14</v>
       </c>
       <c r="L64" t="n">
-        <v>72.83</v>
+        <v>81.77</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.42</v>
+        <v>-84.68000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>110.76</v>
+        <v>126.04</v>
       </c>
       <c r="L65" t="n">
-        <v>133.44</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>21.09</v>
+        <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>184.61</v>
+        <v>201.39</v>
       </c>
       <c r="L66" t="n">
-        <v>185.81</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>119.54</v>
+        <v>136.02</v>
       </c>
       <c r="K67" t="n">
-        <v>47.49</v>
+        <v>54.04</v>
       </c>
       <c r="L67" t="n">
-        <v>128.62</v>
+        <v>146.37</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>6.27</v>
+        <v>7.04</v>
       </c>
       <c r="K68" t="n">
-        <v>123.77</v>
+        <v>138.97</v>
       </c>
       <c r="L68" t="n">
-        <v>123.93</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>56.69</v>
+        <v>63.68</v>
       </c>
       <c r="K69" t="n">
-        <v>127.81</v>
+        <v>143.58</v>
       </c>
       <c r="L69" t="n">
-        <v>139.82</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>183.21</v>
+        <v>208.48</v>
       </c>
       <c r="K70" t="n">
-        <v>-168.11</v>
+        <v>-191.3</v>
       </c>
       <c r="L70" t="n">
-        <v>248.65</v>
+        <v>282.95</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>125.82</v>
+        <v>143.18</v>
       </c>
       <c r="K71" t="n">
-        <v>246.73</v>
+        <v>280.76</v>
       </c>
       <c r="L71" t="n">
-        <v>276.96</v>
+        <v>315.16</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-344.54</v>
+        <v>-392.06</v>
       </c>
       <c r="K72" t="n">
-        <v>31.33</v>
+        <v>35.65</v>
       </c>
       <c r="L72" t="n">
-        <v>345.96</v>
+        <v>393.68</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>29.37</v>
+        <v>32.52</v>
       </c>
       <c r="K73" t="n">
-        <v>221.88</v>
+        <v>245.66</v>
       </c>
       <c r="L73" t="n">
-        <v>223.82</v>
+        <v>247.8</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>65.68000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-81.40000000000001</v>
+        <v>-88.8</v>
       </c>
       <c r="L74" t="n">
-        <v>104.59</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.7</v>
+        <v>-72.65000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>23.59</v>
+        <v>26.49</v>
       </c>
       <c r="L75" t="n">
-        <v>68.87</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>39.53</v>
+        <v>42.46</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.17</v>
+        <v>-62.48</v>
       </c>
       <c r="L76" t="n">
-        <v>70.33</v>
+        <v>75.54000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>76.93000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="K77" t="n">
-        <v>-46.96</v>
+        <v>-53.44</v>
       </c>
       <c r="L77" t="n">
-        <v>90.14</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-124.71</v>
+        <v>-140.02</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.65</v>
+        <v>-31.04</v>
       </c>
       <c r="L78" t="n">
-        <v>127.73</v>
+        <v>143.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>4.76</v>
+        <v>5.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-90.48999999999999</v>
+        <v>-97.2</v>
       </c>
       <c r="L79" t="n">
-        <v>90.62</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>95.53</v>
+        <v>108.71</v>
       </c>
       <c r="K80" t="n">
-        <v>-72.52</v>
+        <v>-82.52</v>
       </c>
       <c r="L80" t="n">
-        <v>119.94</v>
+        <v>136.48</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-153.62</v>
+        <v>-165</v>
       </c>
       <c r="K81" t="n">
-        <v>45.82</v>
+        <v>49.21</v>
       </c>
       <c r="L81" t="n">
-        <v>160.31</v>
+        <v>172.18</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>42.29</v>
+        <v>48.12</v>
       </c>
       <c r="K82" t="n">
-        <v>108.52</v>
+        <v>123.49</v>
       </c>
       <c r="L82" t="n">
-        <v>116.47</v>
+        <v>132.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>174.63</v>
+        <v>198.71</v>
       </c>
       <c r="K83" t="n">
-        <v>95.13</v>
+        <v>108.25</v>
       </c>
       <c r="L83" t="n">
-        <v>198.86</v>
+        <v>226.29</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>58.61</v>
+        <v>66.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-159.55</v>
+        <v>-181.55</v>
       </c>
       <c r="L84" t="n">
-        <v>169.97</v>
+        <v>193.42</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-166.55</v>
+        <v>-184.39</v>
       </c>
       <c r="K85" t="n">
-        <v>177.72</v>
+        <v>196.76</v>
       </c>
       <c r="L85" t="n">
-        <v>243.56</v>
+        <v>269.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-65.15000000000001</v>
+        <v>-71.06999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>380.65</v>
+        <v>415.25</v>
       </c>
       <c r="L86" t="n">
-        <v>386.18</v>
+        <v>421.29</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>200.55</v>
+        <v>228.21</v>
       </c>
       <c r="K87" t="n">
-        <v>-125.98</v>
+        <v>-143.36</v>
       </c>
       <c r="L87" t="n">
-        <v>236.84</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-363.78</v>
+        <v>-414.25</v>
       </c>
       <c r="K88" t="n">
-        <v>139.34</v>
+        <v>158.68</v>
       </c>
       <c r="L88" t="n">
-        <v>389.55</v>
+        <v>443.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>6.28</v>
+        <v>5.81</v>
       </c>
       <c r="G14" t="n">
-        <v>308.2</v>
+        <v>294.9</v>
       </c>
       <c r="H14" t="n">
-        <v>49.6</v>
+        <v>11.3</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.38</v>
+        <v>-30.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-76.5</v>
+        <v>-34.42</v>
       </c>
       <c r="L14" t="n">
-        <v>78.03</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:06</t>
+          <t>04:33:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="F15" t="n">
-        <v>6.56</v>
+        <v>5.52</v>
       </c>
       <c r="G15" t="n">
-        <v>314.9</v>
+        <v>289.1</v>
       </c>
       <c r="H15" t="n">
-        <v>54</v>
+        <v>49.4</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-78.95999999999999</v>
+        <v>-28.05</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.58</v>
+        <v>37.67</v>
       </c>
       <c r="L15" t="n">
-        <v>93.23</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:34:24</t>
+          <t>04:35:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>310.5</v>
+        <v>296</v>
       </c>
       <c r="H16" t="n">
-        <v>56.8</v>
+        <v>53.7</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>96</v>
+        <v>-48.03</v>
       </c>
       <c r="K16" t="n">
-        <v>-15.28</v>
+        <v>-0.64</v>
       </c>
       <c r="L16" t="n">
-        <v>97.2</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:38:53</t>
+          <t>04:41:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="F17" t="n">
-        <v>2.35</v>
+        <v>5.08</v>
       </c>
       <c r="G17" t="n">
-        <v>297.4</v>
+        <v>301.9</v>
       </c>
       <c r="H17" t="n">
-        <v>53.9</v>
+        <v>56.8</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-81</v>
+        <v>11.53</v>
       </c>
       <c r="K17" t="n">
-        <v>0.84</v>
+        <v>-64.94</v>
       </c>
       <c r="L17" t="n">
-        <v>81.01000000000001</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:40:05</t>
+          <t>04:42:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="F18" t="n">
-        <v>5.81</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>291.7</v>
+        <v>301.5</v>
       </c>
       <c r="H18" t="n">
-        <v>46.8</v>
+        <v>43</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>29.72</v>
+        <v>-42.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-82.18000000000001</v>
+        <v>-22.63</v>
       </c>
       <c r="L18" t="n">
-        <v>87.39</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:01</t>
+          <t>04:44:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="F19" t="n">
-        <v>2.71</v>
+        <v>5.88</v>
       </c>
       <c r="G19" t="n">
-        <v>292.2</v>
+        <v>293.6</v>
       </c>
       <c r="H19" t="n">
-        <v>54.6</v>
+        <v>24.8</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>5.21</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>113.53</v>
+        <v>61.43</v>
       </c>
       <c r="L19" t="n">
-        <v>113.65</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:45:42</t>
+          <t>04:48:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -880,31 +880,31 @@
         <v>2.67</v>
       </c>
       <c r="F20" t="n">
-        <v>7.74</v>
+        <v>7.24</v>
       </c>
       <c r="G20" t="n">
-        <v>289.2</v>
+        <v>291.6</v>
       </c>
       <c r="H20" t="n">
-        <v>44.8</v>
+        <v>55.3</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>127.61</v>
+        <v>-68.23</v>
       </c>
       <c r="K20" t="n">
-        <v>128.16</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>180.86</v>
+        <v>108.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:47:33</t>
+          <t>04:50:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="F21" t="n">
-        <v>4.26</v>
+        <v>9.08</v>
       </c>
       <c r="G21" t="n">
-        <v>299.3</v>
+        <v>291</v>
       </c>
       <c r="H21" t="n">
-        <v>59</v>
+        <v>33.3</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-142.48</v>
+        <v>-78.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>109.53</v>
+        <v>-43.68</v>
       </c>
       <c r="L21" t="n">
-        <v>179.71</v>
+        <v>89.73999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:49:34</t>
+          <t>04:51:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="F22" t="n">
-        <v>5.02</v>
+        <v>9.08</v>
       </c>
       <c r="G22" t="n">
-        <v>297.1</v>
+        <v>298.1</v>
       </c>
       <c r="H22" t="n">
-        <v>46.7</v>
+        <v>49.7</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>-76.98</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>102.02</v>
+        <v>-53.45</v>
       </c>
       <c r="L22" t="n">
-        <v>127.8</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:53:35</t>
+          <t>04:55:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="F23" t="n">
-        <v>6.15</v>
+        <v>5.6</v>
       </c>
       <c r="G23" t="n">
-        <v>291</v>
+        <v>309.4</v>
       </c>
       <c r="H23" t="n">
-        <v>49.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-56.76</v>
+        <v>-113.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-202.23</v>
+        <v>42.49</v>
       </c>
       <c r="L23" t="n">
-        <v>210.04</v>
+        <v>121.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:54:20</t>
+          <t>04:56:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="G24" t="n">
-        <v>295.1</v>
+        <v>290.8</v>
       </c>
       <c r="H24" t="n">
-        <v>46.4</v>
+        <v>43.9</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>220.66</v>
+        <v>-54.31</v>
       </c>
       <c r="K24" t="n">
-        <v>-103.23</v>
+        <v>120.43</v>
       </c>
       <c r="L24" t="n">
-        <v>243.61</v>
+        <v>132.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:56:35</t>
+          <t>04:57:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="F25" t="n">
-        <v>5.15</v>
+        <v>6.26</v>
       </c>
       <c r="G25" t="n">
-        <v>294.3</v>
+        <v>301.9</v>
       </c>
       <c r="H25" t="n">
-        <v>55.1</v>
+        <v>57.1</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>28.93</v>
+        <v>-248.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-144.28</v>
+        <v>151.79</v>
       </c>
       <c r="L25" t="n">
-        <v>147.15</v>
+        <v>291.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:00:38</t>
+          <t>05:00:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="F26" t="n">
-        <v>7.92</v>
+        <v>9.08</v>
       </c>
       <c r="G26" t="n">
-        <v>287.5</v>
+        <v>304</v>
       </c>
       <c r="H26" t="n">
-        <v>45.2</v>
+        <v>40.3</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>65.05</v>
+        <v>-35.38</v>
       </c>
       <c r="K26" t="n">
-        <v>263.48</v>
+        <v>-209.21</v>
       </c>
       <c r="L26" t="n">
-        <v>271.39</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:01:20</t>
+          <t>05:02:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="F27" t="n">
-        <v>7.6</v>
+        <v>5.74</v>
       </c>
       <c r="G27" t="n">
-        <v>283.4</v>
+        <v>297.6</v>
       </c>
       <c r="H27" t="n">
-        <v>47.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-284.57</v>
+        <v>-206.39</v>
       </c>
       <c r="K27" t="n">
-        <v>5.59</v>
+        <v>24.66</v>
       </c>
       <c r="L27" t="n">
-        <v>284.63</v>
+        <v>207.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:04:03</t>
+          <t>05:03:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.43</v>
+        <v>2.64</v>
       </c>
       <c r="F28" t="n">
-        <v>9.08</v>
+        <v>6.4</v>
       </c>
       <c r="G28" t="n">
-        <v>294.7</v>
+        <v>285.8</v>
       </c>
       <c r="H28" t="n">
-        <v>52.6</v>
+        <v>21.3</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-277.86</v>
+        <v>96.81</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.48</v>
+        <v>-218.93</v>
       </c>
       <c r="L28" t="n">
-        <v>277.99</v>
+        <v>239.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:16:12</t>
+          <t>05:14:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.22</v>
+        <v>2.22</v>
       </c>
       <c r="F29" t="n">
-        <v>9.08</v>
+        <v>8.31</v>
       </c>
       <c r="G29" t="n">
-        <v>304.3</v>
+        <v>295.7</v>
       </c>
       <c r="H29" t="n">
-        <v>55.9</v>
+        <v>31</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>15.46</v>
+        <v>-42.31</v>
       </c>
       <c r="K29" t="n">
-        <v>90.52</v>
+        <v>0.92</v>
       </c>
       <c r="L29" t="n">
-        <v>91.83</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:54</t>
+          <t>05:16:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="F30" t="n">
-        <v>7.65</v>
+        <v>4.56</v>
       </c>
       <c r="G30" t="n">
-        <v>291</v>
+        <v>297.3</v>
       </c>
       <c r="H30" t="n">
-        <v>55.4</v>
+        <v>19.2</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.95</v>
+        <v>42.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-97.38</v>
+        <v>17.04</v>
       </c>
       <c r="L30" t="n">
-        <v>97.51000000000001</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:19:53</t>
+          <t>05:18:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="F31" t="n">
-        <v>6.7</v>
+        <v>4.91</v>
       </c>
       <c r="G31" t="n">
-        <v>296.5</v>
+        <v>303.7</v>
       </c>
       <c r="H31" t="n">
-        <v>49.9</v>
+        <v>35.5</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-61.3</v>
+        <v>-40.95</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.4</v>
+        <v>11.48</v>
       </c>
       <c r="L31" t="n">
-        <v>61.88</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:23:55</t>
+          <t>05:23:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.56</v>
+        <v>3.54</v>
       </c>
       <c r="F32" t="n">
-        <v>5.67</v>
+        <v>9.08</v>
       </c>
       <c r="G32" t="n">
-        <v>281.4</v>
+        <v>285.3</v>
       </c>
       <c r="H32" t="n">
-        <v>56.1</v>
+        <v>54</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-61.79</v>
+        <v>30.91</v>
       </c>
       <c r="K32" t="n">
-        <v>50.15</v>
+        <v>94.81</v>
       </c>
       <c r="L32" t="n">
-        <v>79.58</v>
+        <v>99.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:26:01</t>
+          <t>05:23:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="F33" t="n">
-        <v>5.87</v>
+        <v>7.04</v>
       </c>
       <c r="G33" t="n">
-        <v>288.7</v>
+        <v>308.1</v>
       </c>
       <c r="H33" t="n">
-        <v>53.1</v>
+        <v>58.5</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>53.93</v>
+        <v>-37.21</v>
       </c>
       <c r="K33" t="n">
-        <v>-76.53</v>
+        <v>-54.13</v>
       </c>
       <c r="L33" t="n">
-        <v>93.62</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:28:03</t>
+          <t>05:25:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="F34" t="n">
-        <v>6.35</v>
+        <v>8.99</v>
       </c>
       <c r="G34" t="n">
-        <v>294.9</v>
+        <v>313.4</v>
       </c>
       <c r="H34" t="n">
-        <v>62.6</v>
+        <v>37.3</v>
       </c>
       <c r="I34" t="n">
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-119.23</v>
+        <v>-42.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-42.5</v>
+        <v>-24.25</v>
       </c>
       <c r="L34" t="n">
-        <v>126.58</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:32:22</t>
+          <t>05:29:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="F35" t="n">
-        <v>6.49</v>
+        <v>5.65</v>
       </c>
       <c r="G35" t="n">
-        <v>289</v>
+        <v>311.3</v>
       </c>
       <c r="H35" t="n">
-        <v>48.2</v>
+        <v>76</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-55.84</v>
+        <v>-115.67</v>
       </c>
       <c r="K35" t="n">
-        <v>-184.8</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>193.05</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:33:17</t>
+          <t>05:32:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="F36" t="n">
-        <v>7.93</v>
+        <v>5.31</v>
       </c>
       <c r="G36" t="n">
-        <v>297.1</v>
+        <v>313.5</v>
       </c>
       <c r="H36" t="n">
-        <v>58.4</v>
+        <v>78.8</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-130.6</v>
+        <v>-68.16</v>
       </c>
       <c r="K36" t="n">
-        <v>-145.1</v>
+        <v>64.62</v>
       </c>
       <c r="L36" t="n">
-        <v>195.22</v>
+        <v>93.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:34:13</t>
+          <t>05:33:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="F37" t="n">
-        <v>7.57</v>
+        <v>7.1</v>
       </c>
       <c r="G37" t="n">
-        <v>283.5</v>
+        <v>294.7</v>
       </c>
       <c r="H37" t="n">
-        <v>51.9</v>
+        <v>44.1</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>0.67</v>
+        <v>-123.08</v>
       </c>
       <c r="K37" t="n">
-        <v>164.04</v>
+        <v>-61.89</v>
       </c>
       <c r="L37" t="n">
-        <v>164.04</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:37:52</t>
+          <t>05:37:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="F38" t="n">
-        <v>7.11</v>
+        <v>4.93</v>
       </c>
       <c r="G38" t="n">
-        <v>301.7</v>
+        <v>303.8</v>
       </c>
       <c r="H38" t="n">
-        <v>50.5</v>
+        <v>45.5</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-180.43</v>
+        <v>46.89</v>
       </c>
       <c r="K38" t="n">
-        <v>-180.59</v>
+        <v>84.56</v>
       </c>
       <c r="L38" t="n">
-        <v>255.28</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:40:21</t>
+          <t>05:40:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="F39" t="n">
-        <v>7.54</v>
+        <v>2.7</v>
       </c>
       <c r="G39" t="n">
-        <v>300.3</v>
+        <v>293.5</v>
       </c>
       <c r="H39" t="n">
-        <v>55.9</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.44</v>
+        <v>-111.17</v>
       </c>
       <c r="K39" t="n">
-        <v>189.03</v>
+        <v>18.23</v>
       </c>
       <c r="L39" t="n">
-        <v>189.14</v>
+        <v>112.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:42:12</t>
+          <t>05:41:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="F40" t="n">
-        <v>6.81</v>
+        <v>4.74</v>
       </c>
       <c r="G40" t="n">
-        <v>297.3</v>
+        <v>296.9</v>
       </c>
       <c r="H40" t="n">
-        <v>51</v>
+        <v>10.4</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>103.99</v>
+        <v>-170.35</v>
       </c>
       <c r="K40" t="n">
-        <v>-252.32</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>272.91</v>
+        <v>170.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:46:09</t>
+          <t>05:45:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="F41" t="n">
-        <v>4.93</v>
+        <v>3.81</v>
       </c>
       <c r="G41" t="n">
-        <v>295.3</v>
+        <v>286.3</v>
       </c>
       <c r="H41" t="n">
-        <v>48.9</v>
+        <v>57</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J41" t="n">
-        <v>159.39</v>
+        <v>-170.9</v>
       </c>
       <c r="K41" t="n">
-        <v>182.72</v>
+        <v>-119.42</v>
       </c>
       <c r="L41" t="n">
-        <v>242.47</v>
+        <v>208.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:47:36</t>
+          <t>05:46:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="F42" t="n">
-        <v>9.08</v>
+        <v>5.76</v>
       </c>
       <c r="G42" t="n">
-        <v>292.2</v>
+        <v>296.8</v>
       </c>
       <c r="H42" t="n">
-        <v>55</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>120.52</v>
+        <v>169.47</v>
       </c>
       <c r="K42" t="n">
-        <v>58.43</v>
+        <v>92.34</v>
       </c>
       <c r="L42" t="n">
-        <v>133.94</v>
+        <v>192.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:49:54</t>
+          <t>05:49:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.27</v>
+        <v>2.69</v>
       </c>
       <c r="F43" t="n">
-        <v>5.84</v>
+        <v>8.93</v>
       </c>
       <c r="G43" t="n">
-        <v>293.3</v>
+        <v>285.3</v>
       </c>
       <c r="H43" t="n">
-        <v>53.6</v>
+        <v>58.7</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-222.35</v>
+        <v>-121.39</v>
       </c>
       <c r="K43" t="n">
-        <v>-81.09999999999999</v>
+        <v>124.37</v>
       </c>
       <c r="L43" t="n">
-        <v>236.68</v>
+        <v>173.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:56:52</t>
+          <t>05:57:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="F44" t="n">
-        <v>6.54</v>
+        <v>5.28</v>
       </c>
       <c r="G44" t="n">
-        <v>312.5</v>
+        <v>295.5</v>
       </c>
       <c r="H44" t="n">
-        <v>57.3</v>
+        <v>54.5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-111.52</v>
+        <v>-9.76</v>
       </c>
       <c r="K44" t="n">
-        <v>40.39</v>
+        <v>-40.07</v>
       </c>
       <c r="L44" t="n">
-        <v>118.61</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:57:54</t>
+          <t>05:58:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="F45" t="n">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="G45" t="n">
-        <v>299.5</v>
+        <v>310.3</v>
       </c>
       <c r="H45" t="n">
         <v>57</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>49.2</v>
+        <v>25.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-30.97</v>
+        <v>-36.84</v>
       </c>
       <c r="L45" t="n">
-        <v>58.13</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05:59:59</t>
+          <t>06:00:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="F46" t="n">
-        <v>8.56</v>
+        <v>8.65</v>
       </c>
       <c r="G46" t="n">
-        <v>296.1</v>
+        <v>305.2</v>
       </c>
       <c r="H46" t="n">
-        <v>55.8</v>
+        <v>53</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>58.39</v>
+        <v>-48.24</v>
       </c>
       <c r="K46" t="n">
-        <v>-38.91</v>
+        <v>-7</v>
       </c>
       <c r="L46" t="n">
-        <v>70.17</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:02:41</t>
+          <t>06:05:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="F47" t="n">
-        <v>6.24</v>
+        <v>7.24</v>
       </c>
       <c r="G47" t="n">
-        <v>287.4</v>
+        <v>294.8</v>
       </c>
       <c r="H47" t="n">
-        <v>56.8</v>
+        <v>25.5</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.22</v>
+        <v>-26.62</v>
       </c>
       <c r="K47" t="n">
-        <v>78.81</v>
+        <v>19.4</v>
       </c>
       <c r="L47" t="n">
-        <v>88.48</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:04:41</t>
+          <t>06:05:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="F48" t="n">
-        <v>4.69</v>
+        <v>5.61</v>
       </c>
       <c r="G48" t="n">
-        <v>296.9</v>
+        <v>297.3</v>
       </c>
       <c r="H48" t="n">
-        <v>53.7</v>
+        <v>96.2</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.71</v>
+        <v>-49.68</v>
       </c>
       <c r="K48" t="n">
-        <v>94.01000000000001</v>
+        <v>20.13</v>
       </c>
       <c r="L48" t="n">
-        <v>97.45999999999999</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:06:48</t>
+          <t>06:07:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="F49" t="n">
-        <v>8.93</v>
+        <v>5.82</v>
       </c>
       <c r="G49" t="n">
-        <v>301.4</v>
+        <v>300.4</v>
       </c>
       <c r="H49" t="n">
-        <v>54.5</v>
+        <v>69.2</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-38.71</v>
+        <v>54.59</v>
       </c>
       <c r="K49" t="n">
-        <v>83.54000000000001</v>
+        <v>-2.72</v>
       </c>
       <c r="L49" t="n">
-        <v>92.08</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:11:03</t>
+          <t>06:11:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="F50" t="n">
-        <v>6.34</v>
+        <v>7.29</v>
       </c>
       <c r="G50" t="n">
-        <v>295.3</v>
+        <v>291.9</v>
       </c>
       <c r="H50" t="n">
-        <v>57</v>
+        <v>33.9</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>-46.33</v>
+        <v>-101.87</v>
       </c>
       <c r="K50" t="n">
-        <v>125.73</v>
+        <v>-27.97</v>
       </c>
       <c r="L50" t="n">
-        <v>133.99</v>
+        <v>105.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:12:55</t>
+          <t>06:13:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="F51" t="n">
-        <v>9.08</v>
+        <v>5.77</v>
       </c>
       <c r="G51" t="n">
-        <v>292.5</v>
+        <v>300</v>
       </c>
       <c r="H51" t="n">
-        <v>49.5</v>
+        <v>55</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-30.22</v>
+        <v>-89.15000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-162.93</v>
+        <v>64.97</v>
       </c>
       <c r="L51" t="n">
-        <v>165.71</v>
+        <v>110.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:14:15</t>
+          <t>06:15:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="F52" t="n">
-        <v>9.08</v>
+        <v>6.07</v>
       </c>
       <c r="G52" t="n">
-        <v>296.8</v>
+        <v>313.2</v>
       </c>
       <c r="H52" t="n">
-        <v>46.2</v>
+        <v>45.6</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-149.76</v>
+        <v>-86.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-53.56</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>159.05</v>
+        <v>112.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:18:16</t>
+          <t>06:20:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="F53" t="n">
-        <v>7.53</v>
+        <v>9.08</v>
       </c>
       <c r="G53" t="n">
-        <v>293.9</v>
+        <v>309.4</v>
       </c>
       <c r="H53" t="n">
-        <v>44.9</v>
+        <v>44.6</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-66.09999999999999</v>
+        <v>-150.39</v>
       </c>
       <c r="K53" t="n">
-        <v>-269.72</v>
+        <v>-27.9</v>
       </c>
       <c r="L53" t="n">
-        <v>277.7</v>
+        <v>152.96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:19:52</t>
+          <t>06:21:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.68</v>
+        <v>2.29</v>
       </c>
       <c r="F54" t="n">
-        <v>6.85</v>
+        <v>7.87</v>
       </c>
       <c r="G54" t="n">
-        <v>311.2</v>
+        <v>303</v>
       </c>
       <c r="H54" t="n">
-        <v>55.9</v>
+        <v>18.3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-165.68</v>
+        <v>147.69</v>
       </c>
       <c r="K54" t="n">
-        <v>-109.76</v>
+        <v>38.67</v>
       </c>
       <c r="L54" t="n">
-        <v>198.74</v>
+        <v>152.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:22:41</t>
+          <t>06:22:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="F55" t="n">
-        <v>9.08</v>
+        <v>6.35</v>
       </c>
       <c r="G55" t="n">
-        <v>310.9</v>
+        <v>281.1</v>
       </c>
       <c r="H55" t="n">
-        <v>51.3</v>
+        <v>54</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>55.52</v>
+        <v>147.34</v>
       </c>
       <c r="K55" t="n">
-        <v>-170.27</v>
+        <v>-35.58</v>
       </c>
       <c r="L55" t="n">
-        <v>179.09</v>
+        <v>151.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:28:18</t>
+          <t>06:27:12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="F56" t="n">
-        <v>9.08</v>
+        <v>4.91</v>
       </c>
       <c r="G56" t="n">
-        <v>300.4</v>
+        <v>309.4</v>
       </c>
       <c r="H56" t="n">
-        <v>54.3</v>
+        <v>67.8</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>127.73</v>
+        <v>-84.8</v>
       </c>
       <c r="K56" t="n">
-        <v>-250.1</v>
+        <v>-192.16</v>
       </c>
       <c r="L56" t="n">
-        <v>280.83</v>
+        <v>210.04</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:30:04</t>
+          <t>06:29:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="F57" t="n">
-        <v>9.08</v>
+        <v>7.52</v>
       </c>
       <c r="G57" t="n">
-        <v>292.8</v>
+        <v>304.6</v>
       </c>
       <c r="H57" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-139.41</v>
+        <v>-189.98</v>
       </c>
       <c r="K57" t="n">
-        <v>168.37</v>
+        <v>-14.79</v>
       </c>
       <c r="L57" t="n">
-        <v>218.59</v>
+        <v>190.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:32:19</t>
+          <t>06:30:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="F58" t="n">
-        <v>7.99</v>
+        <v>8.98</v>
       </c>
       <c r="G58" t="n">
-        <v>292.6</v>
+        <v>307</v>
       </c>
       <c r="H58" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-216.03</v>
+        <v>-122.44</v>
       </c>
       <c r="K58" t="n">
-        <v>151.12</v>
+        <v>166.35</v>
       </c>
       <c r="L58" t="n">
-        <v>263.64</v>
+        <v>206.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:40:54</t>
+          <t>06:39:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="F59" t="n">
-        <v>9.08</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>296</v>
+        <v>289.4</v>
       </c>
       <c r="H59" t="n">
-        <v>47.5</v>
+        <v>72</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-49.5</v>
+        <v>-21.55</v>
       </c>
       <c r="K59" t="n">
-        <v>-40.35</v>
+        <v>-74.62</v>
       </c>
       <c r="L59" t="n">
-        <v>63.86</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:42:09</t>
+          <t>06:41:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="F60" t="n">
-        <v>9.08</v>
+        <v>9.02</v>
       </c>
       <c r="G60" t="n">
-        <v>293.9</v>
+        <v>294.3</v>
       </c>
       <c r="H60" t="n">
-        <v>53</v>
+        <v>72.5</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>47.72</v>
+        <v>-45.44</v>
       </c>
       <c r="K60" t="n">
-        <v>83.27</v>
+        <v>3.25</v>
       </c>
       <c r="L60" t="n">
-        <v>95.97</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:44:25</t>
+          <t>06:43:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="F61" t="n">
-        <v>4.83</v>
+        <v>7.5</v>
       </c>
       <c r="G61" t="n">
-        <v>312.6</v>
+        <v>310.8</v>
       </c>
       <c r="H61" t="n">
-        <v>42.4</v>
+        <v>48.4</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J61" t="n">
-        <v>-40.28</v>
+        <v>-44.57</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.13</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>77.43000000000001</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:47:25</t>
+          <t>06:46:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="F62" t="n">
-        <v>6.9</v>
+        <v>7.46</v>
       </c>
       <c r="G62" t="n">
-        <v>299.1</v>
+        <v>291.9</v>
       </c>
       <c r="H62" t="n">
-        <v>48.7</v>
+        <v>30.4</v>
       </c>
       <c r="I62" t="n">
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>74.88</v>
+        <v>-95.72</v>
       </c>
       <c r="K62" t="n">
-        <v>71.89</v>
+        <v>10.46</v>
       </c>
       <c r="L62" t="n">
-        <v>103.81</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:48:40</t>
+          <t>06:49:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="F63" t="n">
-        <v>6.79</v>
+        <v>9.08</v>
       </c>
       <c r="G63" t="n">
-        <v>291.7</v>
+        <v>298.1</v>
       </c>
       <c r="H63" t="n">
-        <v>49.1</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-85.40000000000001</v>
+        <v>-66.2</v>
       </c>
       <c r="K63" t="n">
-        <v>-36.33</v>
+        <v>-17.65</v>
       </c>
       <c r="L63" t="n">
-        <v>92.8</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>06:50:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="F64" t="n">
-        <v>5.44</v>
+        <v>5.7</v>
       </c>
       <c r="G64" t="n">
-        <v>291.9</v>
+        <v>295.4</v>
       </c>
       <c r="H64" t="n">
-        <v>46.6</v>
+        <v>42.8</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.82</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-76.14</v>
+        <v>55.03</v>
       </c>
       <c r="L64" t="n">
-        <v>81.77</v>
+        <v>87.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:54:57</t>
+          <t>06:55:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2770,31 +2770,31 @@
         <v>2.96</v>
       </c>
       <c r="F65" t="n">
-        <v>8.48</v>
+        <v>9.08</v>
       </c>
       <c r="G65" t="n">
-        <v>296.3</v>
+        <v>306.5</v>
       </c>
       <c r="H65" t="n">
-        <v>52.9</v>
+        <v>82</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>-84.68000000000001</v>
+        <v>115.27</v>
       </c>
       <c r="K65" t="n">
-        <v>126.04</v>
+        <v>-20.5</v>
       </c>
       <c r="L65" t="n">
-        <v>151.84</v>
+        <v>117.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06:56:28</t>
+          <t>06:57:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="F66" t="n">
         <v>9.08</v>
       </c>
       <c r="G66" t="n">
-        <v>294.1</v>
+        <v>283.5</v>
       </c>
       <c r="H66" t="n">
-        <v>53.6</v>
+        <v>37.8</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>23</v>
+        <v>-115.08</v>
       </c>
       <c r="K66" t="n">
-        <v>201.39</v>
+        <v>-10.49</v>
       </c>
       <c r="L66" t="n">
-        <v>202.7</v>
+        <v>115.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06:57:31</t>
+          <t>06:58:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="F67" t="n">
-        <v>8.74</v>
+        <v>7.08</v>
       </c>
       <c r="G67" t="n">
-        <v>300.6</v>
+        <v>310.7</v>
       </c>
       <c r="H67" t="n">
-        <v>50.8</v>
+        <v>20.3</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>136.02</v>
+        <v>-156.45</v>
       </c>
       <c r="K67" t="n">
-        <v>54.04</v>
+        <v>-41.1</v>
       </c>
       <c r="L67" t="n">
-        <v>146.37</v>
+        <v>161.76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:01:44</t>
+          <t>07:02:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="F68" t="n">
-        <v>5.46</v>
+        <v>9.08</v>
       </c>
       <c r="G68" t="n">
-        <v>293.9</v>
+        <v>294.5</v>
       </c>
       <c r="H68" t="n">
-        <v>58.4</v>
+        <v>55</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>7.04</v>
+        <v>112.72</v>
       </c>
       <c r="K68" t="n">
-        <v>138.97</v>
+        <v>152.39</v>
       </c>
       <c r="L68" t="n">
-        <v>139.15</v>
+        <v>189.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:03:56</t>
+          <t>07:04:03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.67</v>
+        <v>2.99</v>
       </c>
       <c r="F69" t="n">
         <v>9.08</v>
       </c>
       <c r="G69" t="n">
-        <v>309.3</v>
+        <v>294</v>
       </c>
       <c r="H69" t="n">
-        <v>56.3</v>
+        <v>27.8</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>63.68</v>
+        <v>165.13</v>
       </c>
       <c r="K69" t="n">
-        <v>143.58</v>
+        <v>-43.41</v>
       </c>
       <c r="L69" t="n">
-        <v>157.06</v>
+        <v>170.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:05:56</t>
+          <t>07:06:08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="F70" t="n">
-        <v>8.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>295.6</v>
+        <v>299.7</v>
       </c>
       <c r="H70" t="n">
-        <v>49.8</v>
+        <v>38.1</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>208.48</v>
+        <v>-231.13</v>
       </c>
       <c r="K70" t="n">
-        <v>-191.3</v>
+        <v>-46.44</v>
       </c>
       <c r="L70" t="n">
-        <v>282.95</v>
+        <v>235.75</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:11:03</t>
+          <t>07:12:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.94</v>
+        <v>2.09</v>
       </c>
       <c r="F71" t="n">
         <v>7.42</v>
       </c>
       <c r="G71" t="n">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="H71" t="n">
-        <v>54.5</v>
+        <v>21.8</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>143.18</v>
+        <v>59.07</v>
       </c>
       <c r="K71" t="n">
-        <v>280.76</v>
+        <v>29.13</v>
       </c>
       <c r="L71" t="n">
-        <v>315.16</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:12:34</t>
+          <t>07:13:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="F72" t="n">
         <v>9.08</v>
       </c>
       <c r="G72" t="n">
-        <v>291.7</v>
+        <v>288.3</v>
       </c>
       <c r="H72" t="n">
-        <v>53.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-392.06</v>
+        <v>257.34</v>
       </c>
       <c r="K72" t="n">
-        <v>35.65</v>
+        <v>-76.61</v>
       </c>
       <c r="L72" t="n">
-        <v>393.68</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:13:54</t>
+          <t>07:16:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.9</v>
+        <v>2.33</v>
       </c>
       <c r="F73" t="n">
-        <v>9.08</v>
+        <v>5.83</v>
       </c>
       <c r="G73" t="n">
-        <v>301.2</v>
+        <v>315</v>
       </c>
       <c r="H73" t="n">
-        <v>57.2</v>
+        <v>35.7</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>32.52</v>
+        <v>67.25</v>
       </c>
       <c r="K73" t="n">
-        <v>245.66</v>
+        <v>194.49</v>
       </c>
       <c r="L73" t="n">
-        <v>247.8</v>
+        <v>205.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:21:02</t>
+          <t>07:26:09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="F74" t="n">
-        <v>8.039999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>307.2</v>
+        <v>297.6</v>
       </c>
       <c r="H74" t="n">
-        <v>47.8</v>
+        <v>27</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>71.65000000000001</v>
+        <v>-54.7</v>
       </c>
       <c r="K74" t="n">
-        <v>-88.8</v>
+        <v>11.63</v>
       </c>
       <c r="L74" t="n">
-        <v>114.1</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:23:02</t>
+          <t>07:28:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="F75" t="n">
-        <v>9.08</v>
+        <v>8.48</v>
       </c>
       <c r="G75" t="n">
-        <v>296.9</v>
+        <v>283.2</v>
       </c>
       <c r="H75" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-72.65000000000001</v>
+        <v>-45.25</v>
       </c>
       <c r="K75" t="n">
-        <v>26.49</v>
+        <v>-6.16</v>
       </c>
       <c r="L75" t="n">
-        <v>77.33</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:24:45</t>
+          <t>07:29:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
       <c r="F76" t="n">
-        <v>8.210000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G76" t="n">
-        <v>290.2</v>
+        <v>288.7</v>
       </c>
       <c r="H76" t="n">
-        <v>50.9</v>
+        <v>9.5</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>42.46</v>
+        <v>-41.19</v>
       </c>
       <c r="K76" t="n">
-        <v>-62.48</v>
+        <v>-27.81</v>
       </c>
       <c r="L76" t="n">
-        <v>75.54000000000001</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:29:29</t>
+          <t>07:34:13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="F77" t="n">
-        <v>8.31</v>
+        <v>7.27</v>
       </c>
       <c r="G77" t="n">
-        <v>295.6</v>
+        <v>291.9</v>
       </c>
       <c r="H77" t="n">
-        <v>55</v>
+        <v>49.9</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>87.55</v>
+        <v>56.05</v>
       </c>
       <c r="K77" t="n">
-        <v>-53.44</v>
+        <v>-23.85</v>
       </c>
       <c r="L77" t="n">
-        <v>102.57</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:31:26</t>
+          <t>07:36:32</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="F78" t="n">
-        <v>7.51</v>
+        <v>5.61</v>
       </c>
       <c r="G78" t="n">
-        <v>292.5</v>
+        <v>296.2</v>
       </c>
       <c r="H78" t="n">
-        <v>55.8</v>
+        <v>54.2</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-140.02</v>
+        <v>-51.6</v>
       </c>
       <c r="K78" t="n">
-        <v>-31.04</v>
+        <v>-51.99</v>
       </c>
       <c r="L78" t="n">
-        <v>143.42</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:33:29</t>
+          <t>07:38:38</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="F79" t="n">
-        <v>6.26</v>
+        <v>7.86</v>
       </c>
       <c r="G79" t="n">
-        <v>292.4</v>
+        <v>305.5</v>
       </c>
       <c r="H79" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>5.11</v>
+        <v>-63.07</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.2</v>
+        <v>34.8</v>
       </c>
       <c r="L79" t="n">
-        <v>97.33</v>
+        <v>72.03</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:44:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="F80" t="n">
-        <v>8.98</v>
+        <v>6.69</v>
       </c>
       <c r="G80" t="n">
-        <v>299.1</v>
+        <v>292.4</v>
       </c>
       <c r="H80" t="n">
-        <v>51.2</v>
+        <v>58.1</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>108.71</v>
+        <v>-83.77</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.52</v>
+        <v>85.14</v>
       </c>
       <c r="L80" t="n">
-        <v>136.48</v>
+        <v>119.44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:39:45</t>
+          <t>07:45:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.26</v>
+        <v>2.84</v>
       </c>
       <c r="F81" t="n">
-        <v>9.08</v>
+        <v>7.74</v>
       </c>
       <c r="G81" t="n">
-        <v>295.6</v>
+        <v>289.7</v>
       </c>
       <c r="H81" t="n">
-        <v>47.7</v>
+        <v>51.2</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-165</v>
+        <v>40.07</v>
       </c>
       <c r="K81" t="n">
-        <v>49.21</v>
+        <v>65.02</v>
       </c>
       <c r="L81" t="n">
-        <v>172.18</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:41:40</t>
+          <t>07:47:35</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="F82" t="n">
-        <v>8.25</v>
+        <v>7.93</v>
       </c>
       <c r="G82" t="n">
-        <v>300.6</v>
+        <v>296.1</v>
       </c>
       <c r="H82" t="n">
-        <v>48.6</v>
+        <v>46</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>48.12</v>
+        <v>88.17</v>
       </c>
       <c r="K82" t="n">
-        <v>123.49</v>
+        <v>56.94</v>
       </c>
       <c r="L82" t="n">
-        <v>132.53</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:45:37</t>
+          <t>07:52:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="F83" t="n">
-        <v>9.08</v>
+        <v>7.07</v>
       </c>
       <c r="G83" t="n">
-        <v>305.1</v>
+        <v>289.8</v>
       </c>
       <c r="H83" t="n">
-        <v>51.4</v>
+        <v>34.9</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>198.71</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>108.25</v>
+        <v>-116.34</v>
       </c>
       <c r="L83" t="n">
-        <v>226.29</v>
+        <v>146.52</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:46:53</t>
+          <t>07:55:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="F84" t="n">
-        <v>5.45</v>
+        <v>9.08</v>
       </c>
       <c r="G84" t="n">
-        <v>295.6</v>
+        <v>295.8</v>
       </c>
       <c r="H84" t="n">
-        <v>57.2</v>
+        <v>41.9</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>66.69</v>
+        <v>84.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-181.55</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>193.42</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:47:47</t>
+          <t>07:57:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="F85" t="n">
-        <v>8.32</v>
+        <v>9.08</v>
       </c>
       <c r="G85" t="n">
-        <v>306.9</v>
+        <v>302.8</v>
       </c>
       <c r="H85" t="n">
-        <v>51.3</v>
+        <v>57.7</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-184.39</v>
+        <v>-43.2</v>
       </c>
       <c r="K85" t="n">
-        <v>196.76</v>
+        <v>161.28</v>
       </c>
       <c r="L85" t="n">
-        <v>269.66</v>
+        <v>166.96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:51:43</t>
+          <t>08:02:42</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="F86" t="n">
-        <v>7.23</v>
+        <v>9.08</v>
       </c>
       <c r="G86" t="n">
-        <v>302</v>
+        <v>315.5</v>
       </c>
       <c r="H86" t="n">
-        <v>56</v>
+        <v>50.8</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-71.06999999999999</v>
+        <v>132.25</v>
       </c>
       <c r="K86" t="n">
-        <v>415.25</v>
+        <v>161.73</v>
       </c>
       <c r="L86" t="n">
-        <v>421.29</v>
+        <v>208.92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07:53:06</t>
+          <t>08:03:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.9</v>
+        <v>4.07</v>
       </c>
       <c r="F87" t="n">
-        <v>6.84</v>
+        <v>9.08</v>
       </c>
       <c r="G87" t="n">
-        <v>309.5</v>
+        <v>300.1</v>
       </c>
       <c r="H87" t="n">
-        <v>55.2</v>
+        <v>82.2</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>228.21</v>
+        <v>-280.56</v>
       </c>
       <c r="K87" t="n">
-        <v>-143.36</v>
+        <v>5.32</v>
       </c>
       <c r="L87" t="n">
-        <v>269.5</v>
+        <v>280.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07:54:41</t>
+          <t>08:05:50</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.33</v>
+        <v>2.95</v>
       </c>
       <c r="F88" t="n">
-        <v>9.08</v>
+        <v>8.35</v>
       </c>
       <c r="G88" t="n">
-        <v>298.7</v>
+        <v>308.4</v>
       </c>
       <c r="H88" t="n">
-        <v>49.3</v>
+        <v>57.7</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-414.25</v>
+        <v>-146.78</v>
       </c>
       <c r="K88" t="n">
-        <v>158.68</v>
+        <v>-116.97</v>
       </c>
       <c r="L88" t="n">
-        <v>443.6</v>
+        <v>187.69</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2.85</v>
       </c>
       <c r="F14" t="n">
-        <v>5.81</v>
+        <v>8.9</v>
       </c>
       <c r="G14" t="n">
-        <v>294.9</v>
+        <v>297.3</v>
       </c>
       <c r="H14" t="n">
-        <v>11.3</v>
+        <v>45</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-30.24</v>
+        <v>23.26</v>
       </c>
       <c r="K14" t="n">
-        <v>-34.42</v>
+        <v>-42.89</v>
       </c>
       <c r="L14" t="n">
-        <v>45.81</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:14</t>
+          <t>04:32:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="F15" t="n">
-        <v>5.52</v>
+        <v>9.08</v>
       </c>
       <c r="G15" t="n">
-        <v>289.1</v>
+        <v>299.6</v>
       </c>
       <c r="H15" t="n">
-        <v>49.4</v>
+        <v>39.5</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-28.05</v>
+        <v>-13.46</v>
       </c>
       <c r="K15" t="n">
-        <v>37.67</v>
+        <v>47.23</v>
       </c>
       <c r="L15" t="n">
-        <v>46.97</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:02</t>
+          <t>04:34:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="F16" t="n">
-        <v>8.460000000000001</v>
+        <v>6.22</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>295.5</v>
       </c>
       <c r="H16" t="n">
-        <v>53.7</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-48.03</v>
+        <v>-35.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.64</v>
+        <v>21.88</v>
       </c>
       <c r="L16" t="n">
-        <v>48.04</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:41:04</t>
+          <t>04:38:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="F17" t="n">
-        <v>5.08</v>
+        <v>7.49</v>
       </c>
       <c r="G17" t="n">
-        <v>301.9</v>
+        <v>294.8</v>
       </c>
       <c r="H17" t="n">
-        <v>56.8</v>
+        <v>37.3</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>11.53</v>
+        <v>-32.41</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.94</v>
+        <v>61.08</v>
       </c>
       <c r="L17" t="n">
-        <v>65.95999999999999</v>
+        <v>69.15000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:28</t>
+          <t>04:41:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="F18" t="n">
-        <v>8.130000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="G18" t="n">
         <v>301.5</v>
       </c>
       <c r="H18" t="n">
-        <v>43</v>
+        <v>55.3</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-42.21</v>
+        <v>12.82</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.63</v>
+        <v>-60.05</v>
       </c>
       <c r="L18" t="n">
-        <v>47.89</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:44:11</t>
+          <t>04:42:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.27</v>
+        <v>2.61</v>
       </c>
       <c r="F19" t="n">
-        <v>5.88</v>
+        <v>6.62</v>
       </c>
       <c r="G19" t="n">
-        <v>293.6</v>
+        <v>309.2</v>
       </c>
       <c r="H19" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>19.54</v>
       </c>
       <c r="K19" t="n">
-        <v>61.43</v>
+        <v>-56.12</v>
       </c>
       <c r="L19" t="n">
-        <v>61.48</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:48:46</t>
+          <t>04:47:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="F20" t="n">
-        <v>7.24</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>291.6</v>
+        <v>296.9</v>
       </c>
       <c r="H20" t="n">
-        <v>55.3</v>
+        <v>28.7</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-68.23</v>
+        <v>-36.04</v>
       </c>
       <c r="K20" t="n">
-        <v>84.20999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="L20" t="n">
-        <v>108.39</v>
+        <v>103.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:04</t>
+          <t>04:48:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.31</v>
+        <v>3.23</v>
       </c>
       <c r="F21" t="n">
-        <v>9.08</v>
+        <v>6.17</v>
       </c>
       <c r="G21" t="n">
-        <v>291</v>
+        <v>295.5</v>
       </c>
       <c r="H21" t="n">
-        <v>33.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-78.40000000000001</v>
+        <v>-25.05</v>
       </c>
       <c r="K21" t="n">
-        <v>-43.68</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>89.73999999999999</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:11</t>
+          <t>04:49:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.27</v>
+        <v>2.31</v>
       </c>
       <c r="F22" t="n">
-        <v>9.08</v>
+        <v>6.03</v>
       </c>
       <c r="G22" t="n">
-        <v>298.1</v>
+        <v>297.6</v>
       </c>
       <c r="H22" t="n">
-        <v>49.7</v>
+        <v>68.2</v>
       </c>
       <c r="I22" t="n">
         <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>76.51000000000001</v>
+        <v>-38.88</v>
       </c>
       <c r="K22" t="n">
-        <v>-53.45</v>
+        <v>-81.89</v>
       </c>
       <c r="L22" t="n">
-        <v>93.33</v>
+        <v>90.65000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:55:24</t>
+          <t>04:53:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.32</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>5.6</v>
+        <v>9.08</v>
       </c>
       <c r="G23" t="n">
-        <v>309.4</v>
+        <v>308.9</v>
       </c>
       <c r="H23" t="n">
-        <v>76.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-113.65</v>
+        <v>73</v>
       </c>
       <c r="K23" t="n">
-        <v>42.49</v>
+        <v>163.92</v>
       </c>
       <c r="L23" t="n">
-        <v>121.33</v>
+        <v>179.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:45</t>
+          <t>04:55:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="F24" t="n">
-        <v>7.25</v>
+        <v>5.45</v>
       </c>
       <c r="G24" t="n">
-        <v>290.8</v>
+        <v>282.6</v>
       </c>
       <c r="H24" t="n">
-        <v>43.9</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-54.31</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>120.43</v>
+        <v>-90.87</v>
       </c>
       <c r="L24" t="n">
-        <v>132.11</v>
+        <v>121.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:57:31</t>
+          <t>04:57:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="F25" t="n">
-        <v>6.26</v>
+        <v>6.66</v>
       </c>
       <c r="G25" t="n">
-        <v>301.9</v>
+        <v>297.8</v>
       </c>
       <c r="H25" t="n">
-        <v>57.1</v>
+        <v>53</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-248.78</v>
+        <v>-141.99</v>
       </c>
       <c r="K25" t="n">
-        <v>151.79</v>
+        <v>-51.01</v>
       </c>
       <c r="L25" t="n">
-        <v>291.43</v>
+        <v>150.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:00:53</t>
+          <t>05:01:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="F26" t="n">
-        <v>9.08</v>
+        <v>5.69</v>
       </c>
       <c r="G26" t="n">
-        <v>304</v>
+        <v>299.5</v>
       </c>
       <c r="H26" t="n">
-        <v>40.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-35.38</v>
+        <v>-169.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-209.21</v>
+        <v>-6.93</v>
       </c>
       <c r="L26" t="n">
-        <v>212.18</v>
+        <v>169.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:02:52</t>
+          <t>05:04:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="F27" t="n">
-        <v>5.74</v>
+        <v>5.31</v>
       </c>
       <c r="G27" t="n">
-        <v>297.6</v>
+        <v>301.9</v>
       </c>
       <c r="H27" t="n">
-        <v>79.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-206.39</v>
+        <v>54.86</v>
       </c>
       <c r="K27" t="n">
-        <v>24.66</v>
+        <v>-170.42</v>
       </c>
       <c r="L27" t="n">
-        <v>207.86</v>
+        <v>179.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:03:51</t>
+          <t>05:06:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="F28" t="n">
-        <v>6.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>285.8</v>
+        <v>301.5</v>
       </c>
       <c r="H28" t="n">
-        <v>21.3</v>
+        <v>43</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>96.81</v>
+        <v>-106.11</v>
       </c>
       <c r="K28" t="n">
-        <v>-218.93</v>
+        <v>-81.06</v>
       </c>
       <c r="L28" t="n">
-        <v>239.37</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:14:36</t>
+          <t>05:16:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="F29" t="n">
-        <v>8.31</v>
+        <v>6.22</v>
       </c>
       <c r="G29" t="n">
-        <v>295.7</v>
+        <v>293.6</v>
       </c>
       <c r="H29" t="n">
-        <v>31</v>
+        <v>24.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-42.31</v>
+        <v>7.9</v>
       </c>
       <c r="K29" t="n">
-        <v>0.92</v>
+        <v>35.97</v>
       </c>
       <c r="L29" t="n">
-        <v>42.32</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:16:50</t>
+          <t>05:17:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="F30" t="n">
-        <v>4.56</v>
+        <v>7.56</v>
       </c>
       <c r="G30" t="n">
-        <v>297.3</v>
+        <v>291.6</v>
       </c>
       <c r="H30" t="n">
-        <v>19.2</v>
+        <v>55.3</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>42.13</v>
+        <v>-24.77</v>
       </c>
       <c r="K30" t="n">
-        <v>17.04</v>
+        <v>38.76</v>
       </c>
       <c r="L30" t="n">
-        <v>45.45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:18:43</t>
+          <t>05:18:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="F31" t="n">
-        <v>4.91</v>
+        <v>9.08</v>
       </c>
       <c r="G31" t="n">
-        <v>303.7</v>
+        <v>291</v>
       </c>
       <c r="H31" t="n">
-        <v>35.5</v>
+        <v>33.3</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-40.95</v>
+        <v>-28.72</v>
       </c>
       <c r="K31" t="n">
-        <v>11.48</v>
+        <v>-22.27</v>
       </c>
       <c r="L31" t="n">
-        <v>42.52</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:23:03</t>
+          <t>05:23:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="F32" t="n">
         <v>9.08</v>
       </c>
       <c r="G32" t="n">
-        <v>285.3</v>
+        <v>298.1</v>
       </c>
       <c r="H32" t="n">
-        <v>54</v>
+        <v>49.7</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>30.91</v>
+        <v>53.81</v>
       </c>
       <c r="K32" t="n">
-        <v>94.81</v>
+        <v>-35.57</v>
       </c>
       <c r="L32" t="n">
-        <v>99.72</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:44</t>
+          <t>05:25:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="F33" t="n">
-        <v>7.04</v>
+        <v>5.91</v>
       </c>
       <c r="G33" t="n">
-        <v>308.1</v>
+        <v>309.4</v>
       </c>
       <c r="H33" t="n">
-        <v>58.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-37.21</v>
+        <v>-52.23</v>
       </c>
       <c r="K33" t="n">
-        <v>-54.13</v>
+        <v>15.68</v>
       </c>
       <c r="L33" t="n">
-        <v>65.69</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:25:58</t>
+          <t>05:26:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="F34" t="n">
-        <v>8.99</v>
+        <v>7.58</v>
       </c>
       <c r="G34" t="n">
-        <v>313.4</v>
+        <v>290.8</v>
       </c>
       <c r="H34" t="n">
-        <v>37.3</v>
+        <v>43.9</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.13</v>
+        <v>-15.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-24.25</v>
+        <v>58.93</v>
       </c>
       <c r="L34" t="n">
-        <v>48.61</v>
+        <v>60.94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:29:53</t>
+          <t>05:31:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="F35" t="n">
-        <v>5.65</v>
+        <v>6.61</v>
       </c>
       <c r="G35" t="n">
-        <v>311.3</v>
+        <v>301.9</v>
       </c>
       <c r="H35" t="n">
-        <v>76</v>
+        <v>57.1</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-115.67</v>
+        <v>-153.7</v>
       </c>
       <c r="K35" t="n">
-        <v>71.79000000000001</v>
+        <v>93.62</v>
       </c>
       <c r="L35" t="n">
-        <v>136.14</v>
+        <v>179.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:32:16</t>
+          <t>05:33:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="F36" t="n">
-        <v>5.31</v>
+        <v>9.08</v>
       </c>
       <c r="G36" t="n">
-        <v>313.5</v>
+        <v>304</v>
       </c>
       <c r="H36" t="n">
-        <v>78.8</v>
+        <v>40.3</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-68.16</v>
+        <v>0.34</v>
       </c>
       <c r="K36" t="n">
-        <v>64.62</v>
+        <v>-106.02</v>
       </c>
       <c r="L36" t="n">
-        <v>93.92</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:33:01</t>
+          <t>05:34:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="F37" t="n">
-        <v>7.1</v>
+        <v>6.12</v>
       </c>
       <c r="G37" t="n">
-        <v>294.7</v>
+        <v>297.6</v>
       </c>
       <c r="H37" t="n">
-        <v>44.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-123.08</v>
+        <v>-104.07</v>
       </c>
       <c r="K37" t="n">
-        <v>-61.89</v>
+        <v>2.64</v>
       </c>
       <c r="L37" t="n">
-        <v>137.76</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:37:44</t>
+          <t>05:38:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="F38" t="n">
-        <v>4.93</v>
+        <v>6.77</v>
       </c>
       <c r="G38" t="n">
-        <v>303.8</v>
+        <v>285.8</v>
       </c>
       <c r="H38" t="n">
-        <v>45.5</v>
+        <v>21.3</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>46.89</v>
+        <v>99.72</v>
       </c>
       <c r="K38" t="n">
-        <v>84.56</v>
+        <v>-157.34</v>
       </c>
       <c r="L38" t="n">
-        <v>96.69</v>
+        <v>186.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:40:07</t>
+          <t>05:39:31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="F39" t="n">
-        <v>2.7</v>
+        <v>8.57</v>
       </c>
       <c r="G39" t="n">
-        <v>293.5</v>
+        <v>295.7</v>
       </c>
       <c r="H39" t="n">
-        <v>71.59999999999999</v>
+        <v>31</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-111.17</v>
+        <v>-139.02</v>
       </c>
       <c r="K39" t="n">
-        <v>18.23</v>
+        <v>-8.27</v>
       </c>
       <c r="L39" t="n">
-        <v>112.65</v>
+        <v>139.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:41:19</t>
+          <t>05:41:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="F40" t="n">
-        <v>4.74</v>
+        <v>4.82</v>
       </c>
       <c r="G40" t="n">
-        <v>296.9</v>
+        <v>297.3</v>
       </c>
       <c r="H40" t="n">
-        <v>10.4</v>
+        <v>19.2</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-170.35</v>
+        <v>146.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.279999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="L40" t="n">
-        <v>170.55</v>
+        <v>150.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:45:06</t>
+          <t>05:47:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="F41" t="n">
-        <v>3.81</v>
+        <v>5.24</v>
       </c>
       <c r="G41" t="n">
-        <v>286.3</v>
+        <v>303.7</v>
       </c>
       <c r="H41" t="n">
-        <v>57</v>
+        <v>35.5</v>
       </c>
       <c r="I41" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-170.9</v>
+        <v>-118.85</v>
       </c>
       <c r="K41" t="n">
-        <v>-119.42</v>
+        <v>18.38</v>
       </c>
       <c r="L41" t="n">
-        <v>208.49</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:46:20</t>
+          <t>05:49:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="F42" t="n">
-        <v>5.76</v>
+        <v>9.08</v>
       </c>
       <c r="G42" t="n">
-        <v>296.8</v>
+        <v>285.3</v>
       </c>
       <c r="H42" t="n">
-        <v>73.09999999999999</v>
+        <v>54</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>169.47</v>
+        <v>142.47</v>
       </c>
       <c r="K42" t="n">
-        <v>92.34</v>
+        <v>223.61</v>
       </c>
       <c r="L42" t="n">
-        <v>192.99</v>
+        <v>265.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:49:00</t>
+          <t>05:51:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="F43" t="n">
-        <v>8.93</v>
+        <v>7.32</v>
       </c>
       <c r="G43" t="n">
-        <v>285.3</v>
+        <v>308.1</v>
       </c>
       <c r="H43" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-121.39</v>
+        <v>-69.05</v>
       </c>
       <c r="K43" t="n">
-        <v>124.37</v>
+        <v>-160.67</v>
       </c>
       <c r="L43" t="n">
-        <v>173.79</v>
+        <v>174.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:57:19</t>
+          <t>06:02:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="F44" t="n">
-        <v>5.28</v>
+        <v>9.08</v>
       </c>
       <c r="G44" t="n">
-        <v>295.5</v>
+        <v>313.4</v>
       </c>
       <c r="H44" t="n">
-        <v>54.5</v>
+        <v>37.3</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.76</v>
+        <v>-21.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.07</v>
+        <v>-17.62</v>
       </c>
       <c r="L44" t="n">
-        <v>41.24</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:58:27</t>
+          <t>06:04:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>6.02</v>
       </c>
       <c r="G45" t="n">
-        <v>310.3</v>
+        <v>311.3</v>
       </c>
       <c r="H45" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>25.92</v>
+        <v>-47.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.84</v>
+        <v>26.98</v>
       </c>
       <c r="L45" t="n">
-        <v>45.04</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:00:28</t>
+          <t>06:05:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="F46" t="n">
-        <v>8.65</v>
+        <v>5.64</v>
       </c>
       <c r="G46" t="n">
-        <v>305.2</v>
+        <v>313.5</v>
       </c>
       <c r="H46" t="n">
-        <v>53</v>
+        <v>78.8</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-48.24</v>
+        <v>-25.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-7</v>
+        <v>24.42</v>
       </c>
       <c r="L46" t="n">
-        <v>48.74</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:05:02</t>
+          <t>06:08:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="F47" t="n">
-        <v>7.24</v>
+        <v>7.48</v>
       </c>
       <c r="G47" t="n">
-        <v>294.8</v>
+        <v>294.7</v>
       </c>
       <c r="H47" t="n">
-        <v>25.5</v>
+        <v>44.1</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-26.62</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>19.4</v>
+        <v>-50.89</v>
       </c>
       <c r="L47" t="n">
-        <v>32.94</v>
+        <v>85.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:05:54</t>
+          <t>06:10:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="n">
-        <v>5.61</v>
+        <v>5.25</v>
       </c>
       <c r="G48" t="n">
-        <v>297.3</v>
+        <v>303.8</v>
       </c>
       <c r="H48" t="n">
-        <v>96.2</v>
+        <v>45.5</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-49.68</v>
+        <v>26.21</v>
       </c>
       <c r="K48" t="n">
-        <v>20.13</v>
+        <v>31.11</v>
       </c>
       <c r="L48" t="n">
-        <v>53.61</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:07:26</t>
+          <t>06:11:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="F49" t="n">
-        <v>5.82</v>
+        <v>2.78</v>
       </c>
       <c r="G49" t="n">
-        <v>300.4</v>
+        <v>293.5</v>
       </c>
       <c r="H49" t="n">
-        <v>69.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>54.59</v>
+        <v>-47.26</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.72</v>
+        <v>5.27</v>
       </c>
       <c r="L49" t="n">
-        <v>54.66</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:11:07</t>
+          <t>06:15:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.01</v>
+        <v>2.53</v>
       </c>
       <c r="F50" t="n">
-        <v>7.29</v>
+        <v>5.07</v>
       </c>
       <c r="G50" t="n">
-        <v>291.9</v>
+        <v>296.9</v>
       </c>
       <c r="H50" t="n">
-        <v>33.9</v>
+        <v>10.4</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-101.87</v>
+        <v>-103.53</v>
       </c>
       <c r="K50" t="n">
-        <v>-27.97</v>
+        <v>-16.1</v>
       </c>
       <c r="L50" t="n">
-        <v>105.63</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>06:17:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.41</v>
+        <v>3.32</v>
       </c>
       <c r="F51" t="n">
-        <v>5.77</v>
+        <v>4.18</v>
       </c>
       <c r="G51" t="n">
-        <v>300</v>
+        <v>286.3</v>
       </c>
       <c r="H51" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-89.15000000000001</v>
+        <v>-54.62</v>
       </c>
       <c r="K51" t="n">
-        <v>64.97</v>
+        <v>-63.14</v>
       </c>
       <c r="L51" t="n">
-        <v>110.31</v>
+        <v>83.48999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:15:36</t>
+          <t>06:18:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="F52" t="n">
-        <v>6.07</v>
+        <v>6.13</v>
       </c>
       <c r="G52" t="n">
-        <v>313.2</v>
+        <v>296.8</v>
       </c>
       <c r="H52" t="n">
-        <v>45.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-86.33</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>72.90000000000001</v>
+        <v>29.52</v>
       </c>
       <c r="L52" t="n">
-        <v>112.99</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:20:10</t>
+          <t>06:21:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="F53" t="n">
         <v>9.08</v>
       </c>
       <c r="G53" t="n">
-        <v>309.4</v>
+        <v>285.3</v>
       </c>
       <c r="H53" t="n">
-        <v>44.6</v>
+        <v>58.7</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-150.39</v>
+        <v>-77.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.9</v>
+        <v>100.07</v>
       </c>
       <c r="L53" t="n">
-        <v>152.96</v>
+        <v>126.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:21:00</t>
+          <t>06:24:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="F54" t="n">
-        <v>7.87</v>
+        <v>5.55</v>
       </c>
       <c r="G54" t="n">
-        <v>303</v>
+        <v>295.5</v>
       </c>
       <c r="H54" t="n">
-        <v>18.3</v>
+        <v>54.5</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>147.69</v>
+        <v>-10.14</v>
       </c>
       <c r="K54" t="n">
-        <v>38.67</v>
+        <v>-154.15</v>
       </c>
       <c r="L54" t="n">
-        <v>152.67</v>
+        <v>154.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:22:51</t>
+          <t>06:25:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="F55" t="n">
-        <v>6.35</v>
+        <v>6.81</v>
       </c>
       <c r="G55" t="n">
-        <v>281.1</v>
+        <v>310.3</v>
       </c>
       <c r="H55" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>147.34</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-35.58</v>
+        <v>-127.03</v>
       </c>
       <c r="L55" t="n">
-        <v>151.57</v>
+        <v>160.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:27:12</t>
+          <t>06:30:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="F56" t="n">
-        <v>4.91</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>309.4</v>
+        <v>305.2</v>
       </c>
       <c r="H56" t="n">
-        <v>67.8</v>
+        <v>53</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-84.8</v>
+        <v>-212.57</v>
       </c>
       <c r="K56" t="n">
-        <v>-192.16</v>
+        <v>-64.8</v>
       </c>
       <c r="L56" t="n">
-        <v>210.04</v>
+        <v>222.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:29:23</t>
+          <t>06:32:40</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.4</v>
+        <v>3.46</v>
       </c>
       <c r="F57" t="n">
-        <v>7.52</v>
+        <v>7.55</v>
       </c>
       <c r="G57" t="n">
-        <v>304.6</v>
+        <v>294.8</v>
       </c>
       <c r="H57" t="n">
-        <v>44.4</v>
+        <v>25.5</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-189.98</v>
+        <v>-55</v>
       </c>
       <c r="K57" t="n">
-        <v>-14.79</v>
+        <v>77.42</v>
       </c>
       <c r="L57" t="n">
-        <v>190.55</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:30:06</t>
+          <t>06:34:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="F58" t="n">
-        <v>8.98</v>
+        <v>5.89</v>
       </c>
       <c r="G58" t="n">
-        <v>307</v>
+        <v>297.3</v>
       </c>
       <c r="H58" t="n">
-        <v>52.2</v>
+        <v>96.2</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-122.44</v>
+        <v>-144.6</v>
       </c>
       <c r="K58" t="n">
-        <v>166.35</v>
+        <v>55.27</v>
       </c>
       <c r="L58" t="n">
-        <v>206.55</v>
+        <v>154.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:39:11</t>
+          <t>06:45:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="F59" t="n">
-        <v>8.640000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="G59" t="n">
-        <v>289.4</v>
+        <v>300.4</v>
       </c>
       <c r="H59" t="n">
-        <v>72</v>
+        <v>69.2</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.55</v>
+        <v>34.56</v>
       </c>
       <c r="K59" t="n">
-        <v>-74.62</v>
+        <v>-4.49</v>
       </c>
       <c r="L59" t="n">
-        <v>77.67</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:41:34</t>
+          <t>06:46:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.76</v>
+        <v>3.09</v>
       </c>
       <c r="F60" t="n">
-        <v>9.02</v>
+        <v>7.69</v>
       </c>
       <c r="G60" t="n">
-        <v>294.3</v>
+        <v>291.9</v>
       </c>
       <c r="H60" t="n">
-        <v>72.5</v>
+        <v>33.9</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.44</v>
+        <v>-47.22</v>
       </c>
       <c r="K60" t="n">
-        <v>3.25</v>
+        <v>-21.03</v>
       </c>
       <c r="L60" t="n">
-        <v>45.55</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:43:30</t>
+          <t>06:48:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="F61" t="n">
-        <v>7.5</v>
+        <v>6.13</v>
       </c>
       <c r="G61" t="n">
-        <v>310.8</v>
+        <v>300</v>
       </c>
       <c r="H61" t="n">
-        <v>48.4</v>
+        <v>55</v>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.57</v>
+        <v>-32.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.390000000000001</v>
+        <v>24.76</v>
       </c>
       <c r="L61" t="n">
-        <v>45.55</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:46:55</t>
+          <t>06:53:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="F62" t="n">
-        <v>7.46</v>
+        <v>6.45</v>
       </c>
       <c r="G62" t="n">
-        <v>291.9</v>
+        <v>313.2</v>
       </c>
       <c r="H62" t="n">
-        <v>30.4</v>
+        <v>45.6</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.72</v>
+        <v>-61.55</v>
       </c>
       <c r="K62" t="n">
-        <v>10.46</v>
+        <v>50.72</v>
       </c>
       <c r="L62" t="n">
-        <v>96.29000000000001</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:49:03</t>
+          <t>06:54:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="F63" t="n">
         <v>9.08</v>
       </c>
       <c r="G63" t="n">
-        <v>298.1</v>
+        <v>309.4</v>
       </c>
       <c r="H63" t="n">
-        <v>73.90000000000001</v>
+        <v>44.6</v>
       </c>
       <c r="I63" t="n">
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-66.2</v>
+        <v>-70.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-17.65</v>
+        <v>-27.43</v>
       </c>
       <c r="L63" t="n">
-        <v>68.51000000000001</v>
+        <v>75.45999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:50:58</t>
+          <t>06:55:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="F64" t="n">
-        <v>5.7</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>295.4</v>
+        <v>303</v>
       </c>
       <c r="H64" t="n">
-        <v>42.8</v>
+        <v>18.3</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-68.45999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="K64" t="n">
-        <v>55.03</v>
+        <v>9.26</v>
       </c>
       <c r="L64" t="n">
-        <v>87.84</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06:55:52</t>
+          <t>07:00:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="F65" t="n">
-        <v>9.08</v>
+        <v>6.75</v>
       </c>
       <c r="G65" t="n">
-        <v>306.5</v>
+        <v>281.1</v>
       </c>
       <c r="H65" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>115.27</v>
+        <v>106.63</v>
       </c>
       <c r="K65" t="n">
-        <v>-20.5</v>
+        <v>-24.86</v>
       </c>
       <c r="L65" t="n">
-        <v>117.07</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06:57:04</t>
+          <t>07:02:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.97</v>
+        <v>2.34</v>
       </c>
       <c r="F66" t="n">
-        <v>9.08</v>
+        <v>5.26</v>
       </c>
       <c r="G66" t="n">
-        <v>283.5</v>
+        <v>309.4</v>
       </c>
       <c r="H66" t="n">
-        <v>37.8</v>
+        <v>67.8</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>-115.08</v>
+        <v>-26.71</v>
       </c>
       <c r="K66" t="n">
-        <v>-10.49</v>
+        <v>-106.8</v>
       </c>
       <c r="L66" t="n">
-        <v>115.56</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06:58:19</t>
+          <t>07:04:59</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="F67" t="n">
-        <v>7.08</v>
+        <v>7.88</v>
       </c>
       <c r="G67" t="n">
-        <v>310.7</v>
+        <v>304.6</v>
       </c>
       <c r="H67" t="n">
-        <v>20.3</v>
+        <v>44.4</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-156.45</v>
+        <v>-98.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-41.1</v>
+        <v>-20.78</v>
       </c>
       <c r="L67" t="n">
-        <v>161.76</v>
+        <v>100.86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:02:58</t>
+          <t>07:08:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="F68" t="n">
         <v>9.08</v>
       </c>
       <c r="G68" t="n">
-        <v>294.5</v>
+        <v>307</v>
       </c>
       <c r="H68" t="n">
-        <v>55</v>
+        <v>52.2</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>112.72</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>152.39</v>
+        <v>148.2</v>
       </c>
       <c r="L68" t="n">
-        <v>189.55</v>
+        <v>175.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:04:03</t>
+          <t>07:10:19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.99</v>
+        <v>3.27</v>
       </c>
       <c r="F69" t="n">
-        <v>9.08</v>
+        <v>8.98</v>
       </c>
       <c r="G69" t="n">
-        <v>294</v>
+        <v>289.4</v>
       </c>
       <c r="H69" t="n">
-        <v>27.8</v>
+        <v>72</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>165.13</v>
+        <v>-10.9</v>
       </c>
       <c r="K69" t="n">
-        <v>-43.41</v>
+        <v>-235.37</v>
       </c>
       <c r="L69" t="n">
-        <v>170.74</v>
+        <v>235.62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:06:08</t>
+          <t>07:11:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="F70" t="n">
-        <v>8.800000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G70" t="n">
-        <v>299.7</v>
+        <v>294.3</v>
       </c>
       <c r="H70" t="n">
-        <v>38.1</v>
+        <v>72.5</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-231.13</v>
+        <v>-145.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-46.44</v>
+        <v>-1.57</v>
       </c>
       <c r="L70" t="n">
-        <v>235.75</v>
+        <v>145.31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:12:31</t>
+          <t>07:16:42</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="F71" t="n">
-        <v>7.42</v>
+        <v>7.84</v>
       </c>
       <c r="G71" t="n">
-        <v>289</v>
+        <v>310.8</v>
       </c>
       <c r="H71" t="n">
-        <v>21.8</v>
+        <v>48.4</v>
       </c>
       <c r="I71" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>59.07</v>
+        <v>-169.74</v>
       </c>
       <c r="K71" t="n">
-        <v>29.13</v>
+        <v>-69.75</v>
       </c>
       <c r="L71" t="n">
-        <v>65.86</v>
+        <v>183.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:13:35</t>
+          <t>07:17:48</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
       <c r="F72" t="n">
-        <v>9.08</v>
+        <v>7.79</v>
       </c>
       <c r="G72" t="n">
-        <v>288.3</v>
+        <v>291.9</v>
       </c>
       <c r="H72" t="n">
-        <v>8.699999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>257.34</v>
+        <v>-251.1</v>
       </c>
       <c r="K72" t="n">
-        <v>-76.61</v>
+        <v>11.04</v>
       </c>
       <c r="L72" t="n">
-        <v>268.5</v>
+        <v>251.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:16:01</t>
+          <t>07:19:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>5.83</v>
+        <v>9.08</v>
       </c>
       <c r="G73" t="n">
-        <v>315</v>
+        <v>298.1</v>
       </c>
       <c r="H73" t="n">
-        <v>35.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>67.25</v>
+        <v>-159.36</v>
       </c>
       <c r="K73" t="n">
-        <v>194.49</v>
+        <v>-72.53</v>
       </c>
       <c r="L73" t="n">
-        <v>205.79</v>
+        <v>175.09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:26:09</t>
+          <t>07:30:22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="F74" t="n">
-        <v>8.880000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="G74" t="n">
-        <v>297.6</v>
+        <v>295.4</v>
       </c>
       <c r="H74" t="n">
-        <v>27</v>
+        <v>42.8</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-54.7</v>
+        <v>-34.04</v>
       </c>
       <c r="K74" t="n">
-        <v>11.63</v>
+        <v>30.35</v>
       </c>
       <c r="L74" t="n">
-        <v>55.93</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:28:15</t>
+          <t>07:32:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="F75" t="n">
-        <v>8.48</v>
+        <v>9.08</v>
       </c>
       <c r="G75" t="n">
-        <v>283.2</v>
+        <v>306.5</v>
       </c>
       <c r="H75" t="n">
-        <v>48.1</v>
+        <v>82</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>-45.25</v>
+        <v>44.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.16</v>
+        <v>-12.19</v>
       </c>
       <c r="L75" t="n">
-        <v>45.67</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:29:32</t>
+          <t>07:33:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="F76" t="n">
         <v>9.08</v>
       </c>
       <c r="G76" t="n">
-        <v>288.7</v>
+        <v>283.5</v>
       </c>
       <c r="H76" t="n">
-        <v>9.5</v>
+        <v>37.8</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J76" t="n">
-        <v>-41.19</v>
+        <v>-44.95</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.81</v>
+        <v>-7.79</v>
       </c>
       <c r="L76" t="n">
-        <v>49.7</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:34:13</t>
+          <t>07:38:33</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.48</v>
+        <v>3.02</v>
       </c>
       <c r="F77" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
       <c r="G77" t="n">
-        <v>291.9</v>
+        <v>310.7</v>
       </c>
       <c r="H77" t="n">
-        <v>49.9</v>
+        <v>20.3</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>56.05</v>
+        <v>-80.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.85</v>
+        <v>-33.72</v>
       </c>
       <c r="L77" t="n">
-        <v>60.91</v>
+        <v>87.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:36:32</t>
+          <t>07:40:51</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="F78" t="n">
-        <v>5.61</v>
+        <v>9.08</v>
       </c>
       <c r="G78" t="n">
-        <v>296.2</v>
+        <v>294.5</v>
       </c>
       <c r="H78" t="n">
-        <v>54.2</v>
+        <v>55</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-51.6</v>
+        <v>-63.1</v>
       </c>
       <c r="K78" t="n">
-        <v>-51.99</v>
+        <v>42.54</v>
       </c>
       <c r="L78" t="n">
-        <v>73.25</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:38:38</t>
+          <t>07:42:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="F79" t="n">
-        <v>7.86</v>
+        <v>9.08</v>
       </c>
       <c r="G79" t="n">
-        <v>305.5</v>
+        <v>302.4</v>
       </c>
       <c r="H79" t="n">
-        <v>80</v>
+        <v>76.5</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>-63.07</v>
+        <v>47.68</v>
       </c>
       <c r="K79" t="n">
-        <v>34.8</v>
+        <v>43.11</v>
       </c>
       <c r="L79" t="n">
-        <v>72.03</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:44:45</t>
+          <t>07:47:26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.55</v>
+        <v>2.53</v>
       </c>
       <c r="F80" t="n">
-        <v>6.69</v>
+        <v>7.95</v>
       </c>
       <c r="G80" t="n">
-        <v>292.4</v>
+        <v>300.4</v>
       </c>
       <c r="H80" t="n">
-        <v>58.1</v>
+        <v>52.6</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-83.77</v>
+        <v>-113.35</v>
       </c>
       <c r="K80" t="n">
-        <v>85.14</v>
+        <v>-43.02</v>
       </c>
       <c r="L80" t="n">
-        <v>119.44</v>
+        <v>121.24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:45:46</t>
+          <t>07:49:19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="F81" t="n">
-        <v>7.74</v>
+        <v>7.76</v>
       </c>
       <c r="G81" t="n">
-        <v>289.7</v>
+        <v>289</v>
       </c>
       <c r="H81" t="n">
-        <v>51.2</v>
+        <v>21.8</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>40.07</v>
+        <v>35.85</v>
       </c>
       <c r="K81" t="n">
-        <v>65.02</v>
+        <v>8.24</v>
       </c>
       <c r="L81" t="n">
-        <v>76.38</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:47:35</t>
+          <t>07:51:10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="F82" t="n">
-        <v>7.93</v>
+        <v>9.08</v>
       </c>
       <c r="G82" t="n">
-        <v>296.1</v>
+        <v>288.3</v>
       </c>
       <c r="H82" t="n">
-        <v>46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>88.17</v>
+        <v>110.42</v>
       </c>
       <c r="K82" t="n">
-        <v>56.94</v>
+        <v>-33.62</v>
       </c>
       <c r="L82" t="n">
-        <v>104.96</v>
+        <v>115.43</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:52:41</t>
+          <t>07:54:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="F83" t="n">
-        <v>7.07</v>
+        <v>6.19</v>
       </c>
       <c r="G83" t="n">
-        <v>289.8</v>
+        <v>315</v>
       </c>
       <c r="H83" t="n">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>89.06999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-116.34</v>
+        <v>118.32</v>
       </c>
       <c r="L83" t="n">
-        <v>146.52</v>
+        <v>135.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:55:15</t>
+          <t>07:57:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="F84" t="n">
         <v>9.08</v>
       </c>
       <c r="G84" t="n">
-        <v>295.8</v>
+        <v>297.6</v>
       </c>
       <c r="H84" t="n">
-        <v>41.9</v>
+        <v>27</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>84.42</v>
+        <v>-162.56</v>
       </c>
       <c r="K84" t="n">
-        <v>-77.18000000000001</v>
+        <v>22.86</v>
       </c>
       <c r="L84" t="n">
-        <v>114.38</v>
+        <v>164.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:57:22</t>
+          <t>07:57:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="F85" t="n">
-        <v>9.08</v>
+        <v>8.76</v>
       </c>
       <c r="G85" t="n">
-        <v>302.8</v>
+        <v>283.2</v>
       </c>
       <c r="H85" t="n">
-        <v>57.7</v>
+        <v>48.1</v>
       </c>
       <c r="I85" t="n">
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-43.2</v>
+        <v>-136.77</v>
       </c>
       <c r="K85" t="n">
-        <v>161.28</v>
+        <v>-30.69</v>
       </c>
       <c r="L85" t="n">
-        <v>166.96</v>
+        <v>140.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:02:42</t>
+          <t>08:03:39</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="F86" t="n">
         <v>9.08</v>
       </c>
       <c r="G86" t="n">
-        <v>315.5</v>
+        <v>288.7</v>
       </c>
       <c r="H86" t="n">
-        <v>50.8</v>
+        <v>9.5</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>132.25</v>
+        <v>-125.27</v>
       </c>
       <c r="K86" t="n">
-        <v>161.73</v>
+        <v>-127.02</v>
       </c>
       <c r="L86" t="n">
-        <v>208.92</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:03:28</t>
+          <t>08:04:24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.07</v>
+        <v>2.54</v>
       </c>
       <c r="F87" t="n">
-        <v>9.08</v>
+        <v>7.55</v>
       </c>
       <c r="G87" t="n">
-        <v>300.1</v>
+        <v>291.9</v>
       </c>
       <c r="H87" t="n">
-        <v>82.2</v>
+        <v>49.9</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-280.56</v>
+        <v>146.52</v>
       </c>
       <c r="K87" t="n">
-        <v>5.32</v>
+        <v>-61.71</v>
       </c>
       <c r="L87" t="n">
-        <v>280.61</v>
+        <v>158.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:05:50</t>
+          <t>08:06:20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="F88" t="n">
-        <v>8.35</v>
+        <v>5.89</v>
       </c>
       <c r="G88" t="n">
-        <v>308.4</v>
+        <v>296.2</v>
       </c>
       <c r="H88" t="n">
-        <v>57.7</v>
+        <v>54.2</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-146.78</v>
+        <v>-102.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-116.97</v>
+        <v>-155.62</v>
       </c>
       <c r="L88" t="n">
-        <v>187.69</v>
+        <v>186.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>34.32</v>
+        <v>34.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-56.77</v>
+        <v>-57.68</v>
       </c>
       <c r="L14" t="n">
-        <v>66.33</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>45.56</v>
+        <v>48.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.12</v>
+        <v>-10.85</v>
       </c>
       <c r="L15" t="n">
-        <v>46.67</v>
+        <v>50.04</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.99</v>
+        <v>-58.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.02</v>
+        <v>-9.41</v>
       </c>
       <c r="L16" t="n">
-        <v>56.72</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-72.38</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.16</v>
+        <v>-31.85</v>
       </c>
       <c r="L17" t="n">
-        <v>78.8</v>
+        <v>80.53</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-74.04000000000001</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.47</v>
+        <v>-47.55</v>
       </c>
       <c r="L18" t="n">
-        <v>87.41</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.73</v>
+        <v>-18.38</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.72</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>77.76000000000001</v>
+        <v>80.61</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-104.32</v>
+        <v>-116.84</v>
       </c>
       <c r="K20" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="L20" t="n">
-        <v>104.34</v>
+        <v>116.86</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>43.44</v>
+        <v>49.73</v>
       </c>
       <c r="K21" t="n">
-        <v>-74.89</v>
+        <v>-85.73</v>
       </c>
       <c r="L21" t="n">
-        <v>86.58</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-79.38</v>
+        <v>-87.64</v>
       </c>
       <c r="K22" t="n">
-        <v>13.09</v>
+        <v>14.45</v>
       </c>
       <c r="L22" t="n">
-        <v>80.45</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>144.08</v>
+        <v>158.52</v>
       </c>
       <c r="K23" t="n">
-        <v>138.43</v>
+        <v>152.31</v>
       </c>
       <c r="L23" t="n">
-        <v>199.8</v>
+        <v>219.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-59.28</v>
+        <v>-65.12</v>
       </c>
       <c r="K24" t="n">
-        <v>-156.19</v>
+        <v>-171.57</v>
       </c>
       <c r="L24" t="n">
-        <v>167.06</v>
+        <v>183.51</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>119.07</v>
+        <v>146.67</v>
       </c>
       <c r="K25" t="n">
-        <v>24.17</v>
+        <v>29.77</v>
       </c>
       <c r="L25" t="n">
-        <v>121.5</v>
+        <v>149.66</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-45.36</v>
+        <v>-53.57</v>
       </c>
       <c r="K26" t="n">
-        <v>-224.19</v>
+        <v>-264.78</v>
       </c>
       <c r="L26" t="n">
-        <v>228.73</v>
+        <v>270.15</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-191.3</v>
+        <v>-229.07</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.39</v>
+        <v>-18.42</v>
       </c>
       <c r="L27" t="n">
-        <v>191.92</v>
+        <v>229.81</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>54.53</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-160.36</v>
+        <v>-194.41</v>
       </c>
       <c r="L28" t="n">
-        <v>169.37</v>
+        <v>205.34</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>38.25</v>
+        <v>37.43</v>
       </c>
       <c r="K29" t="n">
-        <v>43.61</v>
+        <v>42.68</v>
       </c>
       <c r="L29" t="n">
-        <v>58.01</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.23</v>
+        <v>-10.66</v>
       </c>
       <c r="K30" t="n">
-        <v>13.17</v>
+        <v>15.21</v>
       </c>
       <c r="L30" t="n">
-        <v>16.08</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.33</v>
+        <v>-6.1</v>
       </c>
       <c r="K31" t="n">
-        <v>77.67</v>
+        <v>74.78</v>
       </c>
       <c r="L31" t="n">
-        <v>77.93000000000001</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>10.75</v>
+        <v>11.58</v>
       </c>
       <c r="K32" t="n">
-        <v>59.96</v>
+        <v>64.59</v>
       </c>
       <c r="L32" t="n">
-        <v>60.92</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.90000000000001</v>
+        <v>-77.89</v>
       </c>
       <c r="K33" t="n">
-        <v>35.94</v>
+        <v>36.88</v>
       </c>
       <c r="L33" t="n">
-        <v>83.98</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.4</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-42.85</v>
+        <v>-49.03</v>
       </c>
       <c r="L34" t="n">
-        <v>43.66</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.93000000000001</v>
+        <v>-80.5</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.57</v>
+        <v>-11.34</v>
       </c>
       <c r="L35" t="n">
-        <v>68.59999999999999</v>
+        <v>81.29000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-25.68</v>
+        <v>-31.45</v>
       </c>
       <c r="K36" t="n">
-        <v>3.58</v>
+        <v>4.39</v>
       </c>
       <c r="L36" t="n">
-        <v>25.93</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-70.67</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.45</v>
+        <v>-4.05</v>
       </c>
       <c r="L37" t="n">
-        <v>70.76000000000001</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-108</v>
+        <v>-127.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-25.78</v>
+        <v>-30.4</v>
       </c>
       <c r="L38" t="n">
-        <v>111.04</v>
+        <v>130.94</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>41.12</v>
+        <v>51.42</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.28</v>
+        <v>-117.89</v>
       </c>
       <c r="L39" t="n">
-        <v>102.86</v>
+        <v>128.61</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-113.11</v>
+        <v>-131.74</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="L40" t="n">
-        <v>113.11</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.42</v>
+        <v>-9.1</v>
       </c>
       <c r="K41" t="n">
-        <v>148.39</v>
+        <v>181.96</v>
       </c>
       <c r="L41" t="n">
-        <v>148.57</v>
+        <v>182.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>131.54</v>
+        <v>165.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-82.5</v>
+        <v>-103.83</v>
       </c>
       <c r="L42" t="n">
-        <v>155.27</v>
+        <v>195.4</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-195.06</v>
+        <v>-228.79</v>
       </c>
       <c r="K43" t="n">
-        <v>90.20999999999999</v>
+        <v>105.81</v>
       </c>
       <c r="L43" t="n">
-        <v>214.91</v>
+        <v>252.07</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.31</v>
+        <v>-6.3</v>
       </c>
       <c r="K44" t="n">
-        <v>70.7</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>70.98</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-20.63</v>
+        <v>-23.08</v>
       </c>
       <c r="K45" t="n">
-        <v>38.75</v>
+        <v>43.35</v>
       </c>
       <c r="L45" t="n">
-        <v>43.9</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>52.31</v>
+        <v>55.36</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.8</v>
+        <v>-13.55</v>
       </c>
       <c r="L46" t="n">
-        <v>53.86</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-50.33</v>
+        <v>-56.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.93</v>
+        <v>-35.64</v>
       </c>
       <c r="L47" t="n">
-        <v>59.6</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>32.99</v>
+        <v>36.25</v>
       </c>
       <c r="K48" t="n">
-        <v>52.28</v>
+        <v>57.45</v>
       </c>
       <c r="L48" t="n">
-        <v>61.82</v>
+        <v>67.93000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-23.43</v>
+        <v>-26.67</v>
       </c>
       <c r="K49" t="n">
-        <v>57.96</v>
+        <v>65.98</v>
       </c>
       <c r="L49" t="n">
-        <v>62.52</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-36.18</v>
+        <v>-39.79</v>
       </c>
       <c r="K50" t="n">
-        <v>-100.47</v>
+        <v>-110.51</v>
       </c>
       <c r="L50" t="n">
-        <v>106.79</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>93.83</v>
+        <v>104.92</v>
       </c>
       <c r="K51" t="n">
-        <v>9.24</v>
+        <v>10.34</v>
       </c>
       <c r="L51" t="n">
-        <v>94.29000000000001</v>
+        <v>105.42</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>67.08</v>
+        <v>72.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-75.95</v>
+        <v>-82.56999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>101.33</v>
+        <v>110.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>110.76</v>
+        <v>134.07</v>
       </c>
       <c r="K53" t="n">
-        <v>30.34</v>
+        <v>36.73</v>
       </c>
       <c r="L53" t="n">
-        <v>114.84</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.21</v>
+        <v>-55.74</v>
       </c>
       <c r="K54" t="n">
-        <v>145.46</v>
+        <v>161.49</v>
       </c>
       <c r="L54" t="n">
-        <v>153.88</v>
+        <v>170.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-63.66</v>
+        <v>-68.01000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-130.94</v>
+        <v>-139.9</v>
       </c>
       <c r="L55" t="n">
-        <v>145.59</v>
+        <v>155.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>102.86</v>
+        <v>116.17</v>
       </c>
       <c r="K56" t="n">
-        <v>185.79</v>
+        <v>209.83</v>
       </c>
       <c r="L56" t="n">
-        <v>212.36</v>
+        <v>239.84</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-26.83</v>
+        <v>-30.81</v>
       </c>
       <c r="K57" t="n">
-        <v>190.93</v>
+        <v>219.3</v>
       </c>
       <c r="L57" t="n">
-        <v>192.81</v>
+        <v>221.45</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>113.45</v>
+        <v>143.24</v>
       </c>
       <c r="K58" t="n">
-        <v>70.75</v>
+        <v>89.33</v>
       </c>
       <c r="L58" t="n">
-        <v>133.7</v>
+        <v>168.81</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.51</v>
+        <v>-29.51</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.16</v>
+        <v>-42.02</v>
       </c>
       <c r="L59" t="n">
-        <v>47.86</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>27.5</v>
+        <v>29.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.06</v>
+        <v>-37.13</v>
       </c>
       <c r="L60" t="n">
-        <v>44.56</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.25</v>
+        <v>-55.4</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.52</v>
+        <v>-13.28</v>
       </c>
       <c r="L61" t="n">
-        <v>53.73</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>23.97</v>
+        <v>27.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.51</v>
+        <v>-50.16</v>
       </c>
       <c r="L62" t="n">
-        <v>50.55</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-93.69</v>
+        <v>-91.92</v>
       </c>
       <c r="K63" t="n">
-        <v>71.28</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>117.72</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>7.12</v>
+        <v>8.23</v>
       </c>
       <c r="K64" t="n">
-        <v>60.51</v>
+        <v>69.88</v>
       </c>
       <c r="L64" t="n">
-        <v>60.93</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-85.11</v>
+        <v>-98.15000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-58.49</v>
+        <v>-67.45</v>
       </c>
       <c r="L65" t="n">
-        <v>103.28</v>
+        <v>119.09</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-65.64</v>
+        <v>-73.41</v>
       </c>
       <c r="K66" t="n">
-        <v>63.25</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>91.15000000000001</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-57.2</v>
+        <v>-70.65000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-40.79</v>
+        <v>-50.38</v>
       </c>
       <c r="L67" t="n">
-        <v>70.26000000000001</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.56</v>
+        <v>-73.08</v>
       </c>
       <c r="K68" t="n">
-        <v>119.19</v>
+        <v>137.02</v>
       </c>
       <c r="L68" t="n">
-        <v>135.08</v>
+        <v>155.29</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>34.96</v>
+        <v>43.04</v>
       </c>
       <c r="K69" t="n">
-        <v>100.37</v>
+        <v>123.58</v>
       </c>
       <c r="L69" t="n">
-        <v>106.28</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-79.29000000000001</v>
+        <v>-92.81</v>
       </c>
       <c r="K70" t="n">
-        <v>125.04</v>
+        <v>146.35</v>
       </c>
       <c r="L70" t="n">
-        <v>148.06</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>125.44</v>
+        <v>144.72</v>
       </c>
       <c r="K71" t="n">
-        <v>181.52</v>
+        <v>209.43</v>
       </c>
       <c r="L71" t="n">
-        <v>220.65</v>
+        <v>254.57</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-139.18</v>
+        <v>-175.7</v>
       </c>
       <c r="K72" t="n">
-        <v>-62.44</v>
+        <v>-78.83</v>
       </c>
       <c r="L72" t="n">
-        <v>152.55</v>
+        <v>192.57</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>99.13</v>
+        <v>122.31</v>
       </c>
       <c r="K73" t="n">
-        <v>143.2</v>
+        <v>176.68</v>
       </c>
       <c r="L73" t="n">
-        <v>174.17</v>
+        <v>214.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>25.87</v>
+        <v>28.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.16</v>
+        <v>-46.81</v>
       </c>
       <c r="L74" t="n">
-        <v>50.31</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>55.71</v>
+        <v>57.3</v>
       </c>
       <c r="K75" t="n">
-        <v>15.74</v>
+        <v>16.19</v>
       </c>
       <c r="L75" t="n">
-        <v>57.89</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-38.69</v>
+        <v>-39.42</v>
       </c>
       <c r="K76" t="n">
-        <v>42.88</v>
+        <v>43.69</v>
       </c>
       <c r="L76" t="n">
-        <v>57.76</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-30.57</v>
+        <v>-34.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.15</v>
+        <v>-52.45</v>
       </c>
       <c r="L77" t="n">
-        <v>56.19</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>55.36</v>
+        <v>59.29</v>
       </c>
       <c r="K78" t="n">
-        <v>41.5</v>
+        <v>44.45</v>
       </c>
       <c r="L78" t="n">
-        <v>69.19</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.11</v>
+        <v>-56.77</v>
       </c>
       <c r="K79" t="n">
-        <v>52.15</v>
+        <v>55.73</v>
       </c>
       <c r="L79" t="n">
-        <v>74.43000000000001</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>44.18</v>
+        <v>45.92</v>
       </c>
       <c r="K80" t="n">
-        <v>-135.23</v>
+        <v>-140.55</v>
       </c>
       <c r="L80" t="n">
-        <v>142.27</v>
+        <v>147.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-64.12</v>
+        <v>-77.02</v>
       </c>
       <c r="K81" t="n">
-        <v>26.7</v>
+        <v>32.08</v>
       </c>
       <c r="L81" t="n">
-        <v>69.45</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>48.25</v>
+        <v>55.43</v>
       </c>
       <c r="K82" t="n">
-        <v>73.51000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="L82" t="n">
-        <v>87.93000000000001</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.86</v>
+        <v>-3.17</v>
       </c>
       <c r="K83" t="n">
-        <v>-145.53</v>
+        <v>-161.28</v>
       </c>
       <c r="L83" t="n">
-        <v>145.55</v>
+        <v>161.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-50.82</v>
+        <v>-63.61</v>
       </c>
       <c r="K84" t="n">
-        <v>96.39</v>
+        <v>120.66</v>
       </c>
       <c r="L84" t="n">
-        <v>108.97</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>86.13</v>
+        <v>97.48</v>
       </c>
       <c r="K85" t="n">
-        <v>142.99</v>
+        <v>161.84</v>
       </c>
       <c r="L85" t="n">
-        <v>166.92</v>
+        <v>188.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>68.54000000000001</v>
+        <v>85.31</v>
       </c>
       <c r="K86" t="n">
-        <v>135.58</v>
+        <v>168.75</v>
       </c>
       <c r="L86" t="n">
-        <v>151.92</v>
+        <v>189.08</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>102.61</v>
+        <v>119.25</v>
       </c>
       <c r="K87" t="n">
-        <v>-177.7</v>
+        <v>-206.51</v>
       </c>
       <c r="L87" t="n">
-        <v>205.2</v>
+        <v>238.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-216.09</v>
+        <v>-254.29</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.05</v>
+        <v>-28.3</v>
       </c>
       <c r="L88" t="n">
-        <v>217.42</v>
+        <v>255.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-08.xlsx
+++ b/output/2024-06-08.xlsx
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.66</v>
+        <v>-10.78</v>
       </c>
       <c r="K30" t="n">
-        <v>15.21</v>
+        <v>15.39</v>
       </c>
       <c r="L30" t="n">
-        <v>18.57</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="31">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-56.18</v>
+        <v>-56.36</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.64</v>
+        <v>-35.75</v>
       </c>
       <c r="L47" t="n">
-        <v>66.53</v>
+        <v>66.73999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>36.25</v>
+        <v>36.3</v>
       </c>
       <c r="K48" t="n">
-        <v>57.45</v>
+        <v>57.53</v>
       </c>
       <c r="L48" t="n">
-        <v>67.93000000000001</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="49">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>8.23</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>69.88</v>
+        <v>73.19</v>
       </c>
       <c r="L64" t="n">
-        <v>70.36</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="65">
